--- a/data/ERGA_UNIFIED_DATA.xlsx
+++ b/data/ERGA_UNIFIED_DATA.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ΒΑΣΗ ΕΡΓΩΝ" sheetId="1" state="visible" r:id="rId1"/>
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -90,6 +90,27 @@
       <name val="Arial"/>
       <family val="2"/>
       <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="161"/>
+      <family val="2"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="161"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="161"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -225,7 +246,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -245,9 +266,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -261,9 +279,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -314,6 +329,89 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -321,62 +419,16 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Κανονικό" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -739,75 +791,75 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:X26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="5" customWidth="1" style="35" min="1" max="1"/>
-    <col width="14" customWidth="1" style="35" min="2" max="2"/>
-    <col width="22" customWidth="1" style="35" min="3" max="3"/>
-    <col width="45" customWidth="1" style="35" min="4" max="4"/>
-    <col width="12" customWidth="1" style="35" min="5" max="5"/>
-    <col width="22" customWidth="1" style="35" min="6" max="6"/>
-    <col width="15" customWidth="1" style="35" min="7" max="7"/>
-    <col width="18" customWidth="1" style="35" min="8" max="8"/>
-    <col width="20" customWidth="1" style="35" min="9" max="9"/>
-    <col width="28" customWidth="1" style="35" min="10" max="10"/>
-    <col width="16" customWidth="1" style="35" min="11" max="11"/>
-    <col width="30" customWidth="1" style="35" min="12" max="12"/>
-    <col width="55" customWidth="1" style="35" min="13" max="13"/>
-    <col width="35" customWidth="1" style="35" min="14" max="14"/>
-    <col width="12" customWidth="1" style="35" min="15" max="17"/>
-    <col width="35" customWidth="1" style="35" min="18" max="18"/>
-    <col width="22" customWidth="1" style="35" min="19" max="19"/>
-    <col width="55" customWidth="1" style="35" min="20" max="20"/>
-    <col width="40" customWidth="1" style="35" min="21" max="21"/>
-    <col width="22" customWidth="1" style="35" min="22" max="24"/>
-    <col width="16" customWidth="1" style="35" min="25" max="25"/>
-    <col width="18" customWidth="1" style="35" min="26" max="26"/>
-    <col width="14" customWidth="1" style="35" min="27" max="27"/>
-    <col width="20" customWidth="1" style="35" min="28" max="28"/>
-    <col width="18" customWidth="1" style="35" min="29" max="29"/>
-    <col width="13" customWidth="1" style="35" min="30" max="31"/>
+    <col width="5" customWidth="1" style="62" min="1" max="1"/>
+    <col width="14" customWidth="1" style="62" min="2" max="2"/>
+    <col width="22" customWidth="1" style="62" min="3" max="3"/>
+    <col width="45" customWidth="1" style="62" min="4" max="4"/>
+    <col width="12" customWidth="1" style="62" min="5" max="5"/>
+    <col width="22" customWidth="1" style="62" min="6" max="6"/>
+    <col width="15" customWidth="1" style="62" min="7" max="7"/>
+    <col width="18" customWidth="1" style="62" min="8" max="8"/>
+    <col width="20" customWidth="1" style="62" min="9" max="9"/>
+    <col width="28" customWidth="1" style="62" min="10" max="10"/>
+    <col width="16" customWidth="1" style="62" min="11" max="11"/>
+    <col width="30" customWidth="1" style="62" min="12" max="12"/>
+    <col width="55" customWidth="1" style="62" min="13" max="13"/>
+    <col width="59.44140625" customWidth="1" style="62" min="14" max="14"/>
+    <col width="12" customWidth="1" style="62" min="15" max="17"/>
+    <col width="35" customWidth="1" style="62" min="18" max="18"/>
+    <col width="22" customWidth="1" style="62" min="19" max="19"/>
+    <col width="55" customWidth="1" style="62" min="20" max="20"/>
+    <col width="40" customWidth="1" style="62" min="21" max="21"/>
+    <col width="22" customWidth="1" style="62" min="22" max="24"/>
+    <col width="16" customWidth="1" style="64" min="25" max="25"/>
+    <col width="18" customWidth="1" style="62" min="26" max="26"/>
+    <col width="14" customWidth="1" style="62" min="27" max="27"/>
+    <col width="20" customWidth="1" style="62" min="28" max="28"/>
+    <col width="18" customWidth="1" style="62" min="29" max="29"/>
+    <col width="13" customWidth="1" style="62" min="30" max="31"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.95" customHeight="1" s="35">
+    <row r="1" ht="21.9" customHeight="1" s="62">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ΕΝΟΠΟΙΗΜΕΝΗ ΒΑΣΗ ΣΙΔΗΡΟΔΡΟΜΙΚΩΝ ΕΡΓΩΝ  |  ERGA_2 + DETAIL_DATA</t>
         </is>
       </c>
-      <c r="C1" s="39" t="inlineStr">
+      <c r="C1" s="32" t="inlineStr">
         <is>
           <t>Ημερομηνία Ενημέρωσης:</t>
         </is>
       </c>
-      <c r="D1" s="45" t="n">
+      <c r="D1" s="64" t="n">
         <v>46240</v>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" s="35">
-      <c r="A2" s="34" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="62">
+      <c r="A2" s="61" t="inlineStr">
         <is>
           <t>🔗  ΚΟΙΝΕΣ ΣΤΗΛΕΣ (ERGA_2 + detail_data)</t>
         </is>
       </c>
-      <c r="G2" s="38" t="inlineStr">
+      <c r="G2" s="65" t="inlineStr">
         <is>
           <t>🗺️  ERGA_2  –  Κείμενα χάρτη (σύντομα)</t>
         </is>
       </c>
-      <c r="R2" s="36" t="inlineStr">
+      <c r="R2" s="63" t="inlineStr">
         <is>
           <t>📋  detail_data  –  Αναλυτικές πληροφορίες (popup)</t>
         </is>
       </c>
-      <c r="AD2" s="37" t="inlineStr">
+      <c r="W2" s="66" t="inlineStr">
         <is>
           <t>📍  ΓΕΩΓΡΑΦΙΚΑ</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="36" customHeight="1" s="35">
+    <row r="3" ht="36" customHeight="1" s="62">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>ID</t>
@@ -903,7 +955,7 @@
       </c>
       <c r="S3" s="4" t="inlineStr">
         <is>
-          <t>Φάση Έργου</t>
+          <t>Φάση Κύριου Υποέργου</t>
         </is>
       </c>
       <c r="T3" s="4" t="inlineStr">
@@ -918,141 +970,106 @@
 Άμεσες Ενέργειες</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
-        <is>
-          <t>Π/Υ Ένταξης Πράξης (ΔΔ)</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>Νομικές Δεσμεύσεις (ΔΔ)</t>
-        </is>
-      </c>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>Πληρωμές / Δαπάνες (ΔΔ)</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="inlineStr">
+      <c r="V3" s="47" t="inlineStr">
         <is>
           <t>Ημ/νία Ένταξης Πράξης</t>
         </is>
       </c>
-      <c r="Z3" s="4" t="inlineStr">
-        <is>
-          <t>Ημ/νία Ολοκλήρωσης
-(detail)</t>
-        </is>
-      </c>
-      <c r="AA3" s="4" t="inlineStr">
-        <is>
-          <t>Ποσοστό Χρημ. (%)</t>
-        </is>
-      </c>
-      <c r="AB3" s="4" t="inlineStr">
-        <is>
-          <t>Πρόσκληση CEF</t>
-        </is>
-      </c>
-      <c r="AC3" s="4" t="inlineStr">
-        <is>
-          <t>Επιλέξιμη ΔΔ</t>
-        </is>
-      </c>
-      <c r="AD3" s="5" t="inlineStr">
+      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>Γεωγρ. Πλάτος</t>
         </is>
       </c>
-      <c r="AE3" s="5" t="inlineStr">
+      <c r="X3" s="5" t="inlineStr">
         <is>
           <t>Γεωγρ. Μήκος</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1" s="35">
-      <c r="A4" s="9" t="n">
+    <row r="4" ht="60" customHeight="1" s="62">
+      <c r="A4" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>ΕΠ ΥΜΕΠΕΡΑΑ</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
-        <is>
-          <t>Διακοπτό-Ροδοδάφνη</t>
-        </is>
-      </c>
-      <c r="D4" s="46" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
+        <is>
+          <t>ΔΙΑΚΟΠΤΟ-ΡΟΔΟΔΑΦΝΗ</t>
+        </is>
+      </c>
+      <c r="D4" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">ΚΑΤΑΣΚΕΥΗ ΝΕΑΣ ΔΙΠΛΗΣ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΓΡΑΜΜΗΣ ΣΤΟ ΤΜΗΜΑ ΔΙΑΚΟΠΤΟ-ΡΟΔΟΔΑΦΝΗ, ΦΑΣΗ Β'  </t>
         </is>
       </c>
-      <c r="E4" s="43" t="inlineStr">
+      <c r="E4" s="36" t="inlineStr">
         <is>
           <t>Κεντρικό</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.
-(ΕΡΓΟΣΕ ΑΕ)</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.
+</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>ΕΠ ΥΜΕΠΕΡΑΑ 2014-2020</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
-        <is>
-          <t>39.302.718,72 € (Συγχρηματοδοτούμενη δαπάνη)</t>
-        </is>
-      </c>
-      <c r="I4" s="10" t="inlineStr">
-        <is>
-          <t>272.464.553 € (Αθροιστικά συμβάσεις 715, 715-1, 715-2, 715-3)</t>
-        </is>
-      </c>
-      <c r="J4" s="10" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>39.302.718,72 € (Συγχρηματοδοτούμενη Δημόσια δαπάνη)</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>272.464.553 €, χωρίς Φ.Π.Α. (Αρχική Σύμβαση και τρείς Σ.Σ.Ε.)</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>ΜΕΤΚΑ Α.Ε.</t>
         </is>
       </c>
-      <c r="K4" s="10" t="inlineStr">
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>11.09.2014</t>
         </is>
       </c>
-      <c r="L4" s="10" t="inlineStr">
-        <is>
-          <t>16.09.2024 (Προθεσμία περαίωσης εργασιών)</t>
-        </is>
-      </c>
-      <c r="M4" s="46" t="inlineStr">
-        <is>
-          <t>Η πράξη αφορά στην ολοκλήρωση της κατασκευής των έργων υποδομής και επιδομής σιδηροδρομικής γραμμής με σηματοδότηση, τηλεδιοίκηση και τηλεπικοινωνίες στο τμήμα Διακοπτό-Ροδοδάφνη μήκους 16χλμ περίπου, στον Νομό Αχαΐας.</t>
-        </is>
-      </c>
-      <c r="N4" s="46" t="inlineStr">
-        <is>
-          <t>Το έργο Διακοπτό–Ροδοδάφνη έχει ουσιαστικά ολοκληρωθεί ως σιδηροδρομικό υποσύστημα, με περαίωση του μεγαλύτερου μέρους των συμβάσεων και εκκρεμότητα μόνο για την έγκριση λειτουργίας από τη ΡΑΣ για την υποδομή. Παραμένει ατελές λόγω των αντιπλημμυρικών έργων στον Ελαιώνα και των τεχνικών παρεμβάσεων στον Βουραϊκό, που μεταφέρονται σε νέα εργολαβία και ξεχωριστή υλοποίηση. Οι μελέτες για τα αντιπλημμυρικά βρίσκονται σε εξέλιξη και η έναρξη κατασκευής τοποθετείται μετά το 2027, ανάλογα με τις απαλλοτριώσεις. Το έργο εισέρχεται σε φάση διοικητικής και περιβαλλοντικής ολοκλήρωσης με στόχο την πλήρη λειτουργικοποίηση του άξονα.</t>
-        </is>
-      </c>
-      <c r="O4" s="43" t="n"/>
-      <c r="P4" s="43" t="n"/>
-      <c r="Q4" s="43" t="n"/>
-      <c r="R4" s="10" t="n">
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>16.09.2024 (Ημερομομηνία περαίωσης εργασιών)</t>
+        </is>
+      </c>
+      <c r="M4" s="39" t="inlineStr">
+        <is>
+          <t>Η πράξη αφορά στην ολοκλήρωση της κατασκευής των έργων υποδομής και επιδομής σιδηροδρομικής γραμμής με σηματοδότηση, τηλεδιοίκηση και τηλεπικοινωνίες στο τμήμα Διακοπτό-Ροδοδάφνη μήκους 16χλμ περίπου.</t>
+        </is>
+      </c>
+      <c r="N4" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Οι εργασίες έχουν περατωθεί και εκκρεμεί η υποβολή φακέλου στη ΡΑΣ για έγκριση θέσης σε λειτουργία του υποσυστήματος «Υποδομή». 
+Η πράξη είναι ημιτελής λόγω της εκκρεμότητας κατασκευής των έργων διευθέτησης τμημάτων του Βουραϊκού ποταμού, καθώς  και των αντιπλημμυρικών έργων ανάντη και κατάντη της σιδηροδρομικής γραμμής στην περιοχή του Ελαιώνα.  </t>
+        </is>
+      </c>
+      <c r="O4" s="36" t="n"/>
+      <c r="P4" s="36" t="n"/>
+      <c r="Q4" s="36" t="n"/>
+      <c r="R4" s="9" t="n">
         <v>5003002</v>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="9" t="inlineStr">
         <is>
           <t>Ολοκληρωμένο
 φυσικό αντικείμενο</t>
         </is>
       </c>
-      <c r="T4" s="46" t="inlineStr">
+      <c r="T4" s="39" t="inlineStr">
         <is>
           <t>Ολοκληρώνεται μετά το 2023 ως ημιτελές  
 Αντικείμενο:  Η πράξη αφορά στην ολοκλήρωση της κατασκευής των έργων υποδομής και επιδομής σιδηροδρομικής γραμμής με σηματοδότηση, τηλεδιοίκηση και τηλεπικοινωνίες στο τμήμα Διακοπτό-Ροδοδάφνη μήκους 16χλμ περίπου, στον Νομό Αχαΐας.
@@ -1073,141 +1090,120 @@
 Στις 29.07.2026 εντάχθηκε στο ΤΠΑ ΥΠΥΜΕ 2026-2030 η πράξη «ΟΛΟΚΛΗΡΩΣΗ ΚΑΤΑΣΚΕΥΗΣ ΝΕΑΣ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΓΡΑΜΜΗΣ ΚΙΑΤΟ - ΡΟΔΟΔΑΦΝΗ (Τ.Ε. 2005ΣΕ07870002) ΜΕ (ΠΚ 2022ΣΕ07840005)», συνολικής δαπάνης 4.379.838,72 ευρώ. Η Πράξη περιλαμβάνει την αποπληρωμή των συμβάσεων που αφορούν στην κατασκευή της νέας διπλής σιδηροδρομικής γραμμής κανονικού εύρους υψηλών ταχυτήτων στο τμήμα Σ.Σ. Κιάτου  – περιοχή Διακοπτού, συνολικού μήκους 54,4 χλμ. περίπου, με σηματοδότηση, τηλεδιοίκηση και τηλεπικοινωνίες καθώς και την ολοκλήρωση των φυτοτεχνικών εργασιών προς εφαρμογή των προβλεπόμενων στους εγκεκριμένους Περιβαλλοντικούς Όρους.</t>
         </is>
       </c>
-      <c r="U4" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Υποβολή φακέλου στη ΡΑΣ για έγκριση θέσης σε λειτουργία του υποσυστήματος «Υποδομή».
-2. Έγκριση θέσης σε λειτουργία του υποσυστήματος «Υποδομή» από τη ΡΑΣ
-3. Διενέργεια Προσωρινής Παραλαβής του έργου
-4. Κατασκευή έργων διευθέτησης τμημάτων του Βουραϊκού και των αντιπλημμυρικών έργων ανάντη και κατάντη της σιδηροδρομικής γραμμής στην περιοχή του Ελαιώνα </t>
-        </is>
-      </c>
-      <c r="V4" s="10" t="inlineStr">
-        <is>
-          <t>39.302.718,72 €</t>
-        </is>
-      </c>
-      <c r="W4" s="10" t="inlineStr">
-        <is>
-          <t>39.302.718,72 €</t>
-        </is>
-      </c>
-      <c r="X4" s="10" t="inlineStr">
-        <is>
-          <t>33.605.300,92 €</t>
-        </is>
-      </c>
-      <c r="Y4" s="10" t="inlineStr">
+      <c r="U4" s="39" t="inlineStr">
+        <is>
+          <t>1. Υποβολή φακέλου στη ΡΑΣ και έγκριση θέσης σε λειτουργία του υποσυστήματος «Υποδομή».
+2. Κατασκευή έργων διευθέτησης τμημάτων του Βουραϊκού. Η κατασκευή των έργων διευθέτησης τμημάτων του Βουραϊκού θα περιληφθεί σε εργολαβία "σκούπα", η οποία πρόκειται να προκηρυχθεί και για την οποία η ΣΕ ΜΑΕ συντάσσει τα Τεύχη Δημοπράτησης. 
+3. Κατασκευή των αντιπλημμυρικών έργων ανάντη και κατάντη της σιδηροδρομικής γραμμής στην περιοχή του Ελαιώνα. Η ΕΥΔΕ/ΚΣΕΣΠ, η οποία είναι η αρμόδια Υπηρεσία της ΓΓΥ/ΥΠΥΜΕ για το παράλληλο οδικό έργο της ΟΛΥΜΠΙΑΣ ΟΔΟΥ θα αναλάβει την υλοποίηση των εν λόγω έργων.</t>
+        </is>
+      </c>
+      <c r="V4" s="9" t="inlineStr">
         <is>
           <t>21.12.2016</t>
         </is>
       </c>
-      <c r="Z4" s="10" t="inlineStr">
-        <is>
-          <t>16.09.2024</t>
-        </is>
-      </c>
-      <c r="AA4" s="43" t="n"/>
-      <c r="AB4" s="10" t="n"/>
-      <c r="AC4" s="10" t="n"/>
-      <c r="AD4" s="43" t="n">
+      <c r="W4" s="36" t="n">
         <v>38.22968269416733</v>
       </c>
-      <c r="AE4" s="43" t="n">
+      <c r="X4" s="36" t="n">
         <v>22.12596469269695</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1" s="35">
-      <c r="A5" s="9" t="n">
+    <row r="5" ht="60" customHeight="1" s="62">
+      <c r="A5" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>ΕΠ ΥΜΕΠΕΡΑΑ</t>
         </is>
       </c>
-      <c r="C5" s="42" t="inlineStr">
-        <is>
-          <t>Νέος Παντελεήμονας</t>
-        </is>
-      </c>
-      <c r="D5" s="46" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
+        <is>
+          <t>ΝΕΟΣ ΠΑΝΤΕΛΕΗΜΟΝΑΣ</t>
+        </is>
+      </c>
+      <c r="D5" s="39" t="inlineStr">
         <is>
           <t>ΚΑΤΑΣΚΕΥΗ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΣΤΑΣΗΣ ΣΤΟ ΝΕΟ ΠΑΝΤΕΛΕΗΜΟΝΑ ΠΙΕΡΙΑΣ</t>
         </is>
       </c>
-      <c r="E5" s="43" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>Κεντρικό</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.
-(ΕΡΓΟΣΕ ΑΕ)</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.
+</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>ΕΠ ΥΜΕΠΕΡΑΑ 2014-2020</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>126.284,65 € (Συγχρηματοδοτούμενη δαπάνη)</t>
-        </is>
-      </c>
-      <c r="I5" s="10" t="inlineStr">
-        <is>
-          <t>1.112.183,57 € (Αθροιστικά συμβάσεις 752/2021 &amp; 752-1/2024)</t>
-        </is>
-      </c>
-      <c r="J5" s="10" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>126.284,65 € (Συγχρηματοδοτούμενη Δημόσια Δαπάνη)</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>1.112.183,57 €, χωρίς Φ.Π.Α. (Αρχική Σύμβαση και 1η Σ.Σ.Ε.)</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>SOLIS Α.Ε.</t>
         </is>
       </c>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>19.02.2021</t>
         </is>
       </c>
-      <c r="L5" s="10" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>09.03.2026 (Εγκεκριμένη παράταση)</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>Κατασκευή αποβαθρών, στεγάστρων, ανελκυστήρων &amp; Η/Μ εγκαταστάσεων</t>
-        </is>
-      </c>
-      <c r="N5" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Η νέα Σιδηροδρομική Στάση Νέου Παντελεήμονα έχει ουσιαστικά ολοκληρωθεί κατασκευαστικά, με τις εργασίες να έχουν περατωθεί και να εκκρεμεί μόνο η οριστική βεβαίωση περαίωσης μετά την αποκατάσταση μικρών ελλείψεων. Το βασικό ζήτημα αφορά τις συνοδευτικές παρεμβάσεις σηματοδότησης σε τεχνικά δωμάτια γειτονικών σταθμών, οι οποίες δεν έχουν ακόμη υλοποιηθεί. Εξετάζεται είτε η εκτέλεσή τους από υφιστάμενο ανάδοχο είτε η ανάθεση νέας σύντομης σύμβασης. Συνολικά, το έργο βρίσκεται στο τελικό διοικητικό στάδιο πριν την πλήρη ολοκλήρωσή του. Πρόοδος υλοποίησης: Σ752/2021: 90,68% (10ος λογαριασμός/27.05.2026) -  Σ752-1/2024: 76,70% (3ος λογαριασμός/27.05.2026) </t>
-        </is>
-      </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Η πράξη αφορά στην κατασκευή νέας Σιδηροδρομικής Στάσης στην Παραλία Νέου Παντελεήμονα Πιερίας. </t>
+        </is>
+      </c>
+      <c r="N5" s="39" t="inlineStr">
+        <is>
+          <t>Οι εργασίες της εργολαβίας έχουν ολοκληρωθεί και εκκρεμεί η έκδοση βεβαίωσης περαίωσης μετά την αποκατάσταση επουσιωδών ελλείψεων.
+Η πράξη είναι ημιτελής διότι δεν έχουν ακόμη υλοποιηθεί οι αναγκαίες παρεμβάσεις στα τεχνικά δωμάτια των σταθμών Νέων Πόρων και Λεπτοκαρυάς, για τις απαραίτητες προσαρμογές του υφιστάμενου συστήματος σηματοδότησης στη λειτουργία της νέας στάσης, οι οποίες προβλέπονται σε ξεχωριστό υποέργο. 
+Πρόκειται να ανατεθεί νέα σύμβαση με κλειστή διαδικασία πρόσκλησης σε τρεις οικονομικούς φορείς με πόρους από τον Τακτικό Προϋπολογισμό της ΣΕ ΜΑΕ. Η διάρκεια εκτιμάται σε 3-4 μήνες από την υπογραφή της σύμβασης.</t>
+        </is>
+      </c>
+      <c r="O5" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve"> Σ752/2021: </t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="43" t="inlineStr">
         <is>
           <t>Σ752-1/2024:</t>
         </is>
       </c>
-      <c r="Q5" s="43" t="n"/>
-      <c r="R5" s="10" t="inlineStr">
+      <c r="Q5" s="36" t="n"/>
+      <c r="R5" s="9" t="inlineStr">
         <is>
           <t>5002311</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>Σε εξέλιξη</t>
-        </is>
-      </c>
-      <c r="T5" s="46" t="inlineStr">
+      <c r="S5" s="9" t="inlineStr">
+        <is>
+          <t>Ολοκληρωμένο
+φυσικό αντικείμενο</t>
+        </is>
+      </c>
+      <c r="T5" s="39" t="inlineStr">
         <is>
           <t>Ολοκληρώνεται μετά το 2023 ως ημιτελές.  
 Αντικείμενο: Η Πράξη αφορά στην κατασκευή νέας Σιδηροδρομικής Στάσης στην Παραλία Νέου Παντελεήμονα Πιερίας με στόχο την εξυπηρέτηση του κοινού, κυρίως κατά τους καλοκαιρινούς μήνες. Περιλαμβάνεται η κατασκευή αποβαθρών, στεγάστρων και κλιμακοστασίου με ανελκυστήρα, καθώς επίσης η διαμόρφωση του περιβάλλοντος χώρου και οι απαιτούμενες ηλεκτρομηχανολογικές εγκαταστάσεις. Στην Πράξη περιλαμβάνεται το Υ/Ε 2: Εργασίες αποκατάστασης δικτύων ΟΚΩ, το Υ/Ε 3: Εργασίες σηματοδότησης -τηλεδιοίκησης της Σιδηροδρομικής Στάσης οι οποίες αφορούν σε μικρής κλίμακας εργασίες για τις απαραίτητες προσαρμογές του υφιστάμενου συστήματος σηματοδότησης στη λειτουργία της νέας στάσης, το Υ/Ε 4: Oι επιμερισμένες στο παρόν έργο λειτουργικές δαπάνες της ΕΡΓΟΣΕ για την περίοδο υλοποίησης της πράξης, καθώς και το Υ/Ε5 που αφορά στην 1η Συμπληρωματική Σύμβαση Εργασιών
@@ -1221,130 +1217,105 @@
 Πρόκειται να ανατεθεί νέα σύμβαση με κλειστή διαδικασία πρόσκλησης σε τρεις οικονομικούς φορείς. Έχει συνταχθεί αίτημα για χρηματοδότηση από τον Τακτικό Προϋπολογισμό της ΣΕ ΜΑΕ που θα εγκριθεί από το Δ.Σ. Η διάρκεια εκτιμάται σε 3-4 μήνες από την υπογραφή της σύμβασης.</t>
         </is>
       </c>
-      <c r="U5" s="10" t="inlineStr">
+      <c r="U5" s="9" t="inlineStr">
         <is>
           <t>Υλοποίηση των εργασιών  σηματοδότησης - τηλεδιοίκησης της Σιδηροδρομικής Στάσης</t>
         </is>
       </c>
-      <c r="V5" s="10" t="inlineStr">
-        <is>
-          <t>126.284,65 €</t>
-        </is>
-      </c>
-      <c r="W5" s="10" t="inlineStr">
-        <is>
-          <t>126.284,65 €</t>
-        </is>
-      </c>
-      <c r="X5" s="10" t="inlineStr">
-        <is>
-          <t>126.284,65 €</t>
-        </is>
-      </c>
-      <c r="Y5" s="10" t="inlineStr">
+      <c r="V5" s="9" t="inlineStr">
         <is>
           <t>02.10.2017</t>
         </is>
       </c>
-      <c r="Z5" s="10" t="inlineStr">
-        <is>
-          <t>09.03.2026</t>
-        </is>
-      </c>
-      <c r="AA5" s="43" t="n"/>
-      <c r="AB5" s="10" t="n"/>
-      <c r="AC5" s="10" t="n"/>
-      <c r="AD5" s="43" t="n">
+      <c r="W5" s="36" t="n">
         <v>39.99363560257166</v>
       </c>
-      <c r="AE5" s="43" t="n">
+      <c r="X5" s="36" t="n">
         <v>22.61228176007982</v>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1" s="35">
+    <row r="6" ht="60" customHeight="1" s="62">
       <c r="A6" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>ΕΠ ΥΜΕΠΕΡΑΑ</t>
         </is>
       </c>
-      <c r="C6" s="47" t="inlineStr">
-        <is>
-          <t>Υπολειπόμενες εργασίες Σ.Σ. Αθηνών - Β' Φάση</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="C6" s="40" t="inlineStr">
+        <is>
+          <t>ΥΠΟΛΕΙΠΟΜΕΝΕΣ ΕΡΓΑΣΙΕΣ ΣΤΟ Σ.Σ. ΑΘΗΝΩΝ - Β' ΦΑΣΗ</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>ΥΠΟΛΕΙΠΟΜΕΝΕΣ ΕΡΓΑΣΙΕΣ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΥΠΟΔΟΜΗΣ, ΕΠΙΔΟΜΗΣ, ΗΛΕΚΤΡΟΚΙΝΗΣΗΣ ΣΤΟ Σ.Σ. ΑΘΗΝΩΝ ΚΑΙ ΣΥΝΔΕΣΗ ΤΟΥ ΜΕ ΜΕΤΡΟ - Β΄ ΦΑΣΗ Σ.Σ. ΑΘΗΝΩΝ</t>
         </is>
       </c>
-      <c r="E6" s="41" t="inlineStr">
+      <c r="E6" s="34" t="inlineStr">
         <is>
           <t>Κεντρικό</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.
-(ΕΡΓΟΣΕ ΑΕ)</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.
+</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>ΕΠ ΥΜΕΠΕΡΑΑ 2014-2020</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>4.794.827,87 € (Συγχρηματοδοτούμενη δαπάνη)</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>31.527.128,59 €</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>4.794.827,87 € (Συγχρηματοδοτούμενη Δημόσια Δαπάνη)</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>31.527.128,59 € (χωρίς Φ.Π.Α.)</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Κ/Ξ ΣΙΔΗΡΟΔΡΟΜΙΚΑ ΕΡΓΑ Α.Τ.Ε. – INTRAKOM ΚΑΤΑΣΚΕΥΕΣ Α.Ε.</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>11.07.2022</t>
         </is>
       </c>
-      <c r="L6" s="8" t="inlineStr">
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>11.09.2026</t>
         </is>
       </c>
-      <c r="M6" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Το έργο της Β’ φάσης ανάπτυξης του Κεντρικού Σιδηροδρομικού Σταθμού Αθηνών αφορά στην ολοκλήρωση κατασκευής νέων ηλεκτροκινούμενων γραμμών (Nο 1 έως 3), αποβαθρών (Nο 1 έως 6), υπόγειων διαβάσεων, άνω πεζοδιαβάσεων, Η/Μ εγκαταστάσεων κλπ για την επικοινωνία του συνόλου των αποβαθρών του σιδηροδρομικού σταθμού και τη σύνδεσή του με τον Σταθμό «Λαρίσης» της Ελληνικό Μετρό Α.Ε..</t>
-        </is>
-      </c>
-      <c r="N6" s="44" t="inlineStr">
-        <is>
-          <t>Το έργο της Β’ φάσης αναβάθμισης του Κεντρικού Σιδηροδρομικού Σταθμού Αθηνών και της σύνδεσής του με τον Σταθμό «Λαρίσης» του Μετρό αφορά την ολοκλήρωση των υποδομών των νέων ηλεκτροκινούμενων γραμμών, των αποβαθρών, των υπόγειων και άνω πεζοδιαβάσεων και των απαιτούμενων Η/Μ εγκαταστάσεων.
-Η σύμβαση, συνολικού ύψους 31,53 εκατ. € χωρίς ΦΠΑ, υπογράφηκε στις 11.7.2022, με συμβατική προθεσμία ολοκλήρωσης την 11.9.2026. Ανάδοχος είναι η Κ/Ξ ΣΙΔΗΡΟΔΡΟΜΙΚΑ ΕΡΓΑ Α.Τ.Ε. – INTRAKOM ΚΑΤΑΣΚΕΥΕΣ Α.Ε. Η υλοποίηση παρουσιάζει σημαντική καθυστέρηση, καθώς η πρόοδος ανέρχεται  σε 38,12% 
-Έχουν ολοκληρωθεί η κατεδάφιση του κτιρίου ΟΠΑΠ και οι σκυροδετήσεις της Μεγάλης Υπόγειας Διάβασης, ενώ βρίσκονται σε εξέλιξη εκσκαφές και σκυροδετήσεις στις νότιες αποβάθρες. Έχει επίσης εγκριθεί η αρχιτεκτονική μελέτη της Μικρής Υπόγειας Διάβασης. Για τη συνέχιση της υπόγειας σύνδεσης με το Μετρό, αντί της μετεγκατάστασης του παρακείμενου καταστήματος εστίασης, επιλέχθηκε η εξωτερική ενίσχυση του υφιστάμενου κτιρίου.</t>
-        </is>
-      </c>
-      <c r="O6" s="41" t="n"/>
-      <c r="P6" s="41" t="n"/>
-      <c r="Q6" s="41" t="n"/>
-      <c r="R6" s="8" t="n">
+      <c r="M6" s="37" t="inlineStr">
+        <is>
+          <t>Η πράξη αφορά στην ολοκλήρωση κατασκευής νέων ηλεκτροκινούμενων γραμμών (Nο 1 έως 3), αποβαθρών (Nο 1 έως 6), υπόγειων διαβάσεων, άνω πεζοδιαβάσεων, Η/Μ εγκαταστάσεων κλπ για την επικοινωνία του συνόλου των αποβαθρών του σιδηροδρομικού σταθμού και τη σύνδεσή του με τον Σταθμό «Λαρίσης» της Ελληνικό Μετρό Α.Ε.</t>
+        </is>
+      </c>
+      <c r="N6" s="37" t="inlineStr">
+        <is>
+          <t>Η σύμβαση παρουσιάζει ποσοστό υλοποίησης περίπου 38,1%. Σύμφωνα με τις εκτιμήσεις της Διαχειριστικής Αρχής υπάρχει σημαντική αβεβαιότητα για την ολοκλήρωση του έργου μέχρι τον Φεβρουάριο 2027.</t>
+        </is>
+      </c>
+      <c r="O6" s="34" t="n"/>
+      <c r="P6" s="34" t="n"/>
+      <c r="Q6" s="34" t="n"/>
+      <c r="R6" s="7" t="n">
         <v>5085313</v>
       </c>
-      <c r="S6" s="8" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>Σε εξέλιξη</t>
         </is>
       </c>
-      <c r="T6" s="44" t="inlineStr">
+      <c r="T6" s="37" t="inlineStr">
         <is>
           <t>Ολοκληρώνεται μετά το 2023 ως ημιτελές.  
 Αντικείμενο: Το έργο της Β’ φάσης ανάπτυξης του Κεντρικού Σιδηροδρομικού Σταθμού Αθηνών αφορά στην ολοκλήρωση κατασκευής νέων ηλεκτροκινούμενων γραμμών (Nο 1 έως 3), αποβαθρών (Nο 1 έως 6), υπόγειων διαβάσεων, άνω πεζοδιαβάσεων, Η/Μ εγκαταστάσεων κλπ για την επικοινωνία του συνόλου των αποβαθρών του σιδηροδρομικού σταθμού και τη σύνδεσή του με τον Σταθμό «Λαρίσης» της Ελληνικό Μετρό Α.Ε..
@@ -1360,471 +1331,415 @@
 Σύμφωνα με την Τελική Έκθεση του ΕΠ ΥΜΕΠΕΡΑΑ 2014-2020, η έναρξη των κατασκευαστικών εργασιών καθυστέρησε λόγω μη έγκαιρης παράδοσης του χώρου στον ανάδοχο, εκκρεμοτήτων δικτύων και υλικών του ΟΣΕ, καθώς και της καθυστέρησης πρόσληψης προσωπικού από την ΕΦΑΠΑ για εκσκαφές. Επιπλέον, καθυστερήσεις προέκυψαν από την αδειοδότηση καθαίρεσης του κτιρίου ΟΠΑΠ, την ενίσχυση όμορου καταστήματος EVEREST και αλλαγές στο σχεδιασμό των πεζοδιαβάσεων για συμμόρφωση με τις τεχνικές προδιαγραφές διαλειτουργικότητας. Ως αποτέλεσμα, η πρόοδος των εργασιών ανέρχεται μόλις στο ~38% του οικονομικού αντικειμένου, με συμβατική προθεσμία έως τον Σεπτέμβριο 2026, διατηρώντας σημαντική αβεβαιότητα για την ολοκλήρωση του έργου μέχρι τον Φεβρουάριο 2027, σύμφωνα με τις εκτιμήσεις της Διαχειριστικής Αρχής.</t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>Επίσπευση εργασιών για να τηρηθεί ο όρος του "ημιτελούς" έργου 
-(καταληκτική προθεσμία ολοκλήρωσης έως 15-2-2027, διαφορετικά θα πρέπει να επιστραφεί η ενωσιακή συνδρομή που έχει δαπανηθεί για την υλοποίηση της πράξης)</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>4.794.827,87 €</t>
-        </is>
-      </c>
-      <c r="W6" s="8" t="inlineStr">
-        <is>
-          <t>4.794.827,87 €</t>
-        </is>
-      </c>
-      <c r="X6" s="8" t="inlineStr">
-        <is>
-          <t>3.845.658,70 €</t>
-        </is>
-      </c>
-      <c r="Y6" s="8" t="inlineStr">
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Επίσπευση εργασιών για να τηρηθεί ο όρος του "ημιτελούς" έργου </t>
+        </is>
+      </c>
+      <c r="V6" s="7" t="inlineStr">
         <is>
           <t>27.07.2021</t>
         </is>
       </c>
-      <c r="Z6" s="8" t="inlineStr">
-        <is>
-          <t>11.09.2026</t>
-        </is>
-      </c>
-      <c r="AA6" s="41" t="n"/>
-      <c r="AB6" s="8" t="n"/>
-      <c r="AC6" s="8" t="n"/>
-      <c r="AD6" s="41" t="n">
+      <c r="W6" s="34" t="n">
         <v>37.99848960132894</v>
       </c>
-      <c r="AE6" s="41" t="n">
+      <c r="X6" s="34" t="n">
         <v>23.72067259435195</v>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1" s="35">
+    <row r="7" ht="60" customHeight="1" s="62">
       <c r="A7" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>ΜΕΤΑΦΟΡΕΣ</t>
         </is>
       </c>
-      <c r="C7" s="40" t="inlineStr">
-        <is>
-          <t>Σιδ συνδ 6ου ΠΡΟΒΛΗΤΑ</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΣΔ ΣΥΝΔΕΣΗ 6ΟΥ ΠΡΟΒΛΗΤΑ </t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>ΣΙΔΗΡΟΔΡΟΜΙΚΗ ΣΥΝΔΕΣΗ 6ου ΠΡΟΒΛΗΤΑ ΤΟΥ ΛΙΜΕΝΑ ΘΕΣΣΑΛΟΝΙΚΗΣ</t>
         </is>
       </c>
-      <c r="E7" s="41" t="inlineStr">
+      <c r="E7" s="34" t="inlineStr">
         <is>
           <t>Κεντρικό (Core)</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.
-(ΕΡΓΟΣΕ ΑΕ)</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>Π-ΜΕΤ 2021-2027</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>53.500.000,00 €, χωρίς ΦΠΑ</t>
-        </is>
-      </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>61.307.854 € (συνολική δημόσια δαπάνη)</t>
-        </is>
-      </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>Υπό εξέλιξη Ανταγωνιστικός Διάλογος (εκτίμηση ολοκλήρωσης 3ο τρίμηνο 2026)</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="n"/>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t>H ολοκλήρωση του διαγωνισμού εκτιμάται στο 3ο τρίμηνο του 2026.</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>Μελέτη-κατασκευή νέας σιδ. γραμμής σύνδεσης 6ου Προβλήτα ΟΛΘ με υφιστάμενο δίκτυο &amp; Προαστιακός Δυτ. Θεσ/νίκης</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t>Αναμονή υποβολής συμπληρωματικών στοιχείων για ένταξη (παράταση έως 18.05.2026)</t>
-        </is>
-      </c>
-      <c r="O7" s="41" t="n"/>
-      <c r="P7" s="41" t="n"/>
-      <c r="Q7" s="41" t="n"/>
-      <c r="R7" s="8" t="n">
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.
+</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Πρόγραμμα «ΜΕΤΑΦΟΡΕΣ» 2021-2027 </t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>51.552.750,00 € (Συγχρηματοδοτούμενη Δημόσια Δαπάνη σύμφωνα με το αίτημα χρηματοδότησης που υποβλήθηκε από τη ΣΕ ΜΑΕ)</t>
+        </is>
+      </c>
+      <c r="I7" s="52" t="inlineStr">
+        <is>
+          <t>53.500.000 € 
+(προϋπολογισμός δημοπράτησης - μαζί με Προαστιακό Δυτικής Θεσσαλονίκης)</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>Εκτίμηση: τέλη Νοεμβρίου 2026</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>4 έτη από την υπογραφή της  σύμβασης</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Η πράξη αφορά στην κατασκευή νέας σιδηροδρομικής γραμμής για τη σύνδεση του 6ου Προβλήτα του Οργανισμού Λιμένος Θεσσαλονίκης (ΟΛΘ) με την υφιστάμενη Σιδηροδρομική Γραμμή. </t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>Σε εξέλιξη διαγωνισμός με τη διαδικασία Ανταγωνιστικού Διαλόγου για τη σύναψη σύμβασης "Μελέτη - Κατασκευή" μαζί με την κατασκευή του Προαστιακού Δυτικής Θεσσαλονίκης.
+Φάση Β.ΙΙ Διαγωνισμού:  καταληκτική ημερομηνία ηλεκτρονικής υποβολής προσφορών 28.08.2026 και ημερομηνία ηλεκτρονικής αποσφράγισης των προσφορών 04.09.2026. 
+Η ΣΕ ΜΑΕ έχει υποβάλει αίτημα χρηματοδότησης στη Διαχειριστική Αρχή, το οποίο είναι σε φάση αξιολόγησης.</t>
+        </is>
+      </c>
+      <c r="O7" s="34" t="n"/>
+      <c r="P7" s="34" t="n"/>
+      <c r="Q7" s="34" t="n"/>
+      <c r="R7" s="7" t="n">
         <v>6050689</v>
       </c>
-      <c r="S7" s="8" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>Σε διαδικασία ανάθεσης</t>
         </is>
       </c>
-      <c r="T7" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Το έργο αφορά στην κατασκευή νέας σιδηροδρομικής γραμμής για τη σύνδεση του 6ου Προβλήτα του Οργανισμού Λιμένος Θεσσαλονίκης (ΟΛΘ) με την υφιστάμενη Σιδηροδρομική Γραμμή. Πιο συγκεκριμένα, αφορά στη μελέτη και κατασκευή:
-- των έργων υποδομής, όπως χωματουργικές εργασίες, τεχνικά αντιστήριξης, γέφυρα νέας ΣΓ, τεχνικά υδραυλικών έργων κτλ,
-- ~2 km επιδομής μονής σιδηροδρομικής γραμμής επί χωματουργικού και επί γέφυρας (από τη θέση
-σύνδεσης με την υφισ. ΣΓ έως την είσοδο στο νέο επιλιμένιο ΣΣ),
-- έργων αποκατάστασης οδικού δικτύου, μετατοπίσεις αγωγών ΟΚΩ, κατασκευή δικτύων αποχέτευσης – αποστράγγισης του συνόλου των σιδ/κων και οδικών έργων, 
-- σιδηροδρομικών Η/Μ συστημάτων συμβατών με της υφιστάμενης ΣΓ,
-- ανισοπεδοποίησης του σιδηροδρομικού και οδικού δικτύου στην περιοχή Μυτηληνάκια και των κλάδων του κόμβου της Λεωφ. Δενδροποτάμου
-Σύμβαση: "ΕΡΓΑ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΣΥΝΔΕΣΗΣ ΤΟΥ 6ΟΥ ΠΡΟΒΛΗΤΑ ΛΙΜΕΝΑ ΘΕΣΣΑΛΟΝΙΚΗΣ &amp; ΚΑΤΑΣΚΕΥΗ ΠΡΟΑΣΤΙΑΚΟΥ ΔΥΤΙΚΗΣ ΘΕΣΣΑΛΟΝΙΚΗΣ" (ΑΔ: 5301)
-Σε εξέλιξη διαγωνισμός με τη διαδικασία Ανταγωνιστικού Διαλόγου για τη σύναψη σύμβασης "Μελέτη - Κατασκευή"
-Προϋπολογισμός δημοπράτησης: 53.500.000,00 €, χωρίς ΦΠΑ (μαζί με το έργο Προαστιακού Σιδηροδρόμου Δυτικής Θεσσαλονίκης)
-Δημοσίευση Διαγωνισμού: 3.12.2021
-Α΄ Φάση Διαγωνισμού (Οριστικοποίηση προεπιλεγέντων για συμμετοχή στη διαδικασία): Ολοκληρώθηκε Απρίλιο 2022
-Β.Ι Φάση Διαγωνισμού (Διεξαγωγή Διαλόγου):  Με τις από 21.05.2025 Αποφάσεις του Δ.Σ. της ΕΡΓΟΣΕ εγκρίθηκαν τα αποτελέσματα του Διαλόγου και κηρύχθηκε το πέρας αυτού και εγκρίθηκε ο σχεδιασμός/σύνθεση λύσεων για το έργο.
-Στις 22.10.2025 εκδόθηκε η Τροποποίηση της ΑΕΠΟ. 
-Στις 03.04.2026 εντάχθηκε στο ΤΠΑ ΥΠΥΜΕ 2026-2030 η πράξη "Κάλυψη της δαπάνης απαλλοτριώσεων για τη Σιδηροδρομική Σύνδεση του 6ου Προβλήτα Λιμένα Θεσσαλονίκης &amp; την κατασκευή Προαστιακού Δυτικής Θεσσαλονίκης" με συνολική επιλέξιμη δημόσια δαπάνη 11.015.600,00 €. Στις 04.05.2026 και στις 19.05.2026 εκδόθηκαν οι Αποφάσεις κήρυξης κατεπείγουσας αναγκαστικής απαλλοτρίωσης ακινήτων, με διάγραμμα οριζοντιογραφίας (επί ορθοφωτοχάρτη) που απαιτούνται για το Τμήμα 1 «Σιδηροδρομική Σύνδεση του 6ου Προβλήτα Λιμένα Θεσσαλονίκης» τόσο για την κατασκευή της Σιδηροδρομικής Γραμμής , όσο και για την κατασκευή του παράλληλου και κάθετου οδικού δικτύου.
-Β.II Φάση Διαγωνισμού: Στις 07.05.2026 εγκρίθηκε από το ΔΣ της ΣΕ ΜΑΕ η Πρόσκληση της Β.ΙΙ Φάσης. Καταληκτική ημερομηνία ηλεκτρονικής υποβολής προσφορών: 28.08.2026 (σε συνέχεια της από 10.07.2026 απόφασης μετάθεσης των ημερομηνιών της διαγωνιστικής διαδικασίας) και ημερομηνία ηλεκτρονικής αποσφράγισης των προσφορών: 04.09.2026. 
-H υπογραφή της σύμβασης εκτιμάται τέλη Νοεμβρίου του 2026. 
-Στις 23.12.2025 υποβλήθηκε από τον δικαιούχο "ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.", αίτηση χρηματοδότησης  για την Πράξη "ΣΙΔΗΡΟΔΡΟΜΙΚΗ ΣΥΝΔΕΣΗ ΤΟΥ  6ου ΠΡΟΒΛΗΤΑ ΤΟΥ ΛΙΜΕΝΑ ΘΕΣΣΑΛΟΝΙΚΗΣ" με κωδικό MIS 6050689 και συνολική δημόσια δαπάνη 61.307.854,00 € και συγχρηματοδοτούμενη δημόσια δαπάνη 51.552.750,00 €. 
-Στις 17.02.2026 η ΕΥΔ ΜΕΤΑΦΟΡΕΣ απέστειλε έγγραφο για την υποβολή συμπληρωματικών στοιχείων, τα οποία υποβλήθηκαν από τη ΣΕ ΜΑΕ στις 29.06.2026.  Στις 15.07.2026 η ΕΥΔ ΜΕΤΑΦΟΡΕΣ απέστειλε νέο έγγραφο υποβολής πρόσθετων συμπληρωματικών και διευκρινιστικών στοιχείων με καταληκτική ημερομηνία υποβολής την 28.07.2026. Η ΣΕΜΑΕ με το από 27.07.2026 έγγραφό της, ζήτησε την παράταση της ανωτέρω προθεσμίας έως στις 31.08.2026. </t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>1.Κήρυξη απαλλοτριώσεων
-2. Ένταξη στο Πρόγραμμα "ΜΕΤΑΦΟΡΕΣ" 2021-2027
-3. Προέγκριση τευχών δημοπράτησης Β.ΙΙ σταδίου από Δ.Α.</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="n"/>
-      <c r="W7" s="8" t="n"/>
-      <c r="X7" s="8" t="n"/>
-      <c r="Y7" s="8" t="n"/>
-      <c r="Z7" s="8" t="n"/>
-      <c r="AA7" s="41" t="n"/>
-      <c r="AB7" s="8" t="n"/>
-      <c r="AC7" s="8" t="n"/>
-      <c r="AD7" s="41" t="n">
+      <c r="T7" s="37" t="inlineStr">
+        <is>
+          <t>Η πράξη αφορά στην κατασκευή νέας σιδηροδρομικής γραμμής για τη σύνδεση του 6ου Προβλήτα του Οργανισμού Λιμένος Θεσσαλονίκης (ΟΛΘ) με την υφιστάμενη Σιδηροδρομική Γραμμή. 
+Η ΣΕ ΜΑΕ έχει υποβάλει αίτημα χρηματοδότησης στη Διαχειριστική Αρχή, το οποίο είναι σε φάση αξιολόγησης.</t>
+        </is>
+      </c>
+      <c r="U7" s="7" t="inlineStr">
+        <is>
+          <t>Ένταξη της πράξης στο Πρόγραμμα "ΜΕΤΑΦΟΡΕΣ" 2021-2027</t>
+        </is>
+      </c>
+      <c r="V7" s="48" t="n"/>
+      <c r="W7" s="34" t="n">
         <v>40.62090965560449</v>
       </c>
-      <c r="AE7" s="41" t="n">
+      <c r="X7" s="34" t="n">
         <v>22.92685023557468</v>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1" s="35">
-      <c r="A8" s="9" t="n">
+    <row r="8" ht="60" customHeight="1" s="62">
+      <c r="A8" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>ΜΕΤΑΦΟΡΕΣ</t>
         </is>
       </c>
-      <c r="C8" s="42" t="inlineStr">
-        <is>
-          <t>Προαστιακός Δυτ. Θεσ/νίκης</t>
-        </is>
-      </c>
-      <c r="D8" s="46" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
+        <is>
+          <t>ΠΡΟΑΣΤΙΑΚΟΣ ΔΥΤ. ΘΕΣΣΑΛΟΝΙΚΗΣ</t>
+        </is>
+      </c>
+      <c r="D8" s="39" t="inlineStr">
         <is>
           <t>ΠΡΟΑΣΤΙΑΚΟΣ ΣΙΔΗΡΟΔΡΟΜΟΣ ΔΥΤΙΚΗΣ ΘΕΣΣΑΛΟΝΙΚΗΣ</t>
         </is>
       </c>
-      <c r="E8" s="43" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>Κεντρικό (Core)</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε. 
-(ΕΡΓΟΣΕ ΑΕ)</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>Π-ΜΕΤ 2021-2027</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>23.861.246 € (συνολική δημόσια δαπάνη)</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>53.500.000 € (προϋπολογισμός δημοπράτησης - κοινό έργο με 6ο προβλήτα)</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.
+</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Πρόγραμμα «ΜΕΤΑΦΟΡΕΣ» 2021-2027 </t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>19.596.750,00 € (Συγχρηματοδοτούμενη Δημόσια Δαπάνη σύμφωνα με το αίτημα χρηματοδότησης που υποβλήθηκε από τη ΣΕ ΜΑΕ)</t>
+        </is>
+      </c>
+      <c r="I8" s="53" t="inlineStr">
+        <is>
+          <t>53.500.000 € 
+(προϋπολογισμός δημοπράτησης - μαζί με τη ΣΔ σύνδεση 6ου προβλήτα)</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K8" s="10" t="n"/>
-      <c r="L8" s="10" t="n"/>
-      <c r="M8" s="10" t="inlineStr">
-        <is>
-          <t>Ανάπτυξη προαστιακού επί 19,5χλμ υφιστάμενων/νέων γραμμών (3 κλάδοι, 7 στάσεις)</t>
-        </is>
-      </c>
-      <c r="N8" s="10" t="inlineStr">
-        <is>
-          <t>Στάδιο Β.ΙΙ Διαγωνισμού - Αναμονή στοιχείων ένταξης (Λήξη παράτασης 10.05.2026)</t>
-        </is>
-      </c>
-      <c r="O8" s="43" t="n"/>
-      <c r="P8" s="43" t="n"/>
-      <c r="Q8" s="43" t="n"/>
-      <c r="R8" s="10" t="inlineStr">
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>Εκτίμηση: τέλη Νοεμβρίου 2026</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>4 έτη από την υπογραφή της  σύμβασης</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>Η πράξη αφορά στην  ανάπτυξη του Προαστιακού Σιδηροδρόμου στη Δυτική Θεσσαλονίκη επί υφιστάμενων ΣΓ (εν λειτουργία και εκτός λειτουργίας), καθώς και επί νέων τμημάτων ΣΓ. Το δίκτυο του Προαστιακού, μορφής «Υ» συνολικού μήκους 19,5χλμ., θα αποτελείται από δύο κλάδους από τα δυτικά και από ενιαίο κλάδο προς τα ανατολικά, εξυπηρετώντας συνολικά επτά στάσεις.</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>Σε εξέλιξη διαγωνισμός με τη διαδικασία Ανταγωνιστικού Διαλόγου για τη σύναψη σύμβασης "Μελέτη - Κατασκευή" μαζί με τη σιδηροδρομική σύνδεση του 6ου Προβλήτα του Λιμένα Θεσσαλονίκης.
+Φάση Β.ΙΙ Διαγωνισμού:  καταληκτική ημερομηνία ηλεκτρονικής υποβολής προσφορών 28.08.2026 και ημερομηνία ηλεκτρονικής αποσφράγισης των προσφορών 04.09.2026. 
+Η ΣΕ ΜΑΕ έχει υποβάλει αίτημα χρηματοδότησης στη Διαχειριστική Αρχή, το οποίο είναι σε φάση αξιολόγησης.</t>
+        </is>
+      </c>
+      <c r="O8" s="36" t="n"/>
+      <c r="P8" s="36" t="n"/>
+      <c r="Q8" s="36" t="n"/>
+      <c r="R8" s="9" t="inlineStr">
         <is>
           <t>6050645</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="9" t="inlineStr">
         <is>
           <t>Σε διαδικασία ανάθεσης</t>
         </is>
       </c>
-      <c r="T8" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Το έργο αφορά στην  ανάπτυξη του Προαστιακού Σιδηροδρόμου στη Δυτική Θεσσαλονίκη επί υφιστάμενων ΣΓ (εν λειτουργία και εκτός λειτουργίας), καθώς και επί νέων τμημάτων ΣΓ. 
-Το ανάπτυγμα του δικτύου του Προαστιακού, μορφής «Υ» συνολικού μήκους 19,5χλμ., θα αποτελείται από δύο κλάδους από τα δυτικά, κλάδος από ΤΧ1 προς Σίνδο (περ. 6,5χλμ) &amp; προς Αγχίαλο – Διαβατά (περ. 7,3χλμ) ) και από ενιαίο κλάδο προς τα ανατολικά από ΤΧ1 - Νέο Σ.Σ. Θεσσαλονίκης (περ. 5,5χλμ), εξυπηρετώντας συνολικά επτά στάσεις.
-Πιο συγκεκριμένα το έργο αφορά στη μελέτη και κατασκευή:
- - των έργων που απαιτούνται για την λειτουργία των νέων Σιδ. Στάσεων, 
- - των έργων υποδομής και επιδομής,
- - των απαραίτητων οδικών έργων για την πρόσβαση των ΣΣτ και τη διαμόρφωση των χώρων στάθμευσης,
- - των απαραίτητων υδραυλικών έργων στις περιοχές των ΣΣτ και κατά μήκος των νέων τμημάτων ΣΓ,
- - των έργων προσαρμογής και επέκτασης του υφιστάμενου συστήματος σηματοδότησης και ηλεκτροκίνησης
-Σύμβαση: "ΕΡΓΑ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΣΥΝΔΕΣΗΣ ΤΟΥ 6ΟΥ ΠΡΟΒΛΗΤΑ ΛΙΜΕΝΑ ΘΕΣΣΑΛΟΝΙΚΗΣ &amp; ΚΑΤΑΣΚΕΥΗ ΠΡΟΑΣΤΙΑΚΟΥ ΔΥΤΙΚΗΣ ΘΕΣΣΑΛΟΝΙΚΗΣ" (ΑΔ: 5301)
-Σε εξέλιξη διαγωνισμός με τη διαδικασία Ανταγωνιστικού Διαλόγου για τη σύναψη σύμβασης "Μελέτη - Κατασκευή"
-Προϋπολογισμός δημοπράτησης: 53.500.000,00 €, χωρίς ΦΠΑ (μαζί με το έργο Σ/Δ Σύνδεσης 6ου Προβλήτα Λιμένα Θεσσαλονίκης)
-Δημοσίευση Διαγωνισμού: 3.12.2021
-Α΄ Φάση Διαγωνισμού (Οριστικοποίηση προεπιλεγέντων για συμμετοχή στη διαδικασία): Ολοκληρώθηκε Απρίλιο 2022
-Β.Ι Φάση Διαγωνισμού (Διεξαγωγή Διαλόγου): Με τις από 21.05.2025 Αποφάσεις του Δ.Σ. της ΕΡΓΟΣΕ εγκρίθηκαν τα αποτελέσματα του Διαλόγου και κηρύχθηκε το πέρας αυτού και εγκρίθηκε ο σχεδιασμός/σύνθεση λύσεων για το έργο.
-Στις 20.11.2025 εκδόθηκε η Τροποποίηση της ΑΕΠΟ. 
-Στις 03.04.2026 εντάχθηκε στο ΤΠΑ ΥΠΥΜΕ 2026-2030 η πράξη "Κάλυψη της δαπάνης απαλλοτριώσεων για τη Σιδηροδρομική Σύνδεση του 6ου Προβλήτα Λιμένα Θεσσαλονίκης &amp; την κατασκευή Προαστιακού Δυτικής Θεσσαλονίκης" με συνολική επιλέξιμη δημόσια δαπάνη 11.015.600,00 €. Στις 04.05.2026 και στις 22.05.2026 εκδόθηκαν οι Αποφάσεις κήρυξης κατεπείγουσας αναγκαστικής απαλλοτρίωσης ακινήτων, με διάγραμμα οριζοντιογραφίας (επί ορθοφωτοχάρτη) που απαιτούνται για το Τμήμα 2 «Κατασκευή Προαστιακού Δυτικής Θεσσαλονίκης».
-Β.II Φάση Διαγωνισμού: Στις 07.05.2026 εγκρίθηκε από το ΔΣ της ΣΕ ΜΑΕ η Πρόσκληση της Β.ΙΙ Φάσης. Καταληκτική ημερομηνία ηλεκτρονικής υποβολής προσφορών: 28.08.2026 (σε συνέχεια της από 10.07.2026 απόφασης μετάθεσης των ημερομηνιών της διαγωνιστικής διαδικασίας) και ημερομηνία ηλεκτρονικής αποσφράγισης των προσφορών: 04.09.2026. 
-Η υπογραφή της σύμβασης εκτιμάται τέλη Νοεμβρίου του 2026.
-Στις 24.11.2025 υποβλήθηκε από τον δικαιούχο "ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε." αίτηση χρηματοδότησης  για την Πράξη "Κατασκευή Προαστιακού Δυτικής Θεσσαλονίκης" με κωδικό MIS 6050645 και συνολική δημόσια δαπάνη 23.861.246 ευρώ και συγχρηματοδοτούμενη δημόσια δαπάνη 19.596.750,00€. 
-Στις 17.02.2026 η ΕΥΔ ΜΕΤΑΦΟΡΕΣ απέστειλε έγγραφο για την υποβολή συμπληρωματικών στοιχείων, τα οποία υποβλήθηκαν από τη ΣΕ ΜΑΕ στις 29.06.2026. Στις 15.07.2026 η ΕΥΔ ΜΕΤΑΦΟΡΕΣ απέστειλε νέο έγγραφο υποβολής πρόσθετων συμπληρωματικών και διευκρινιστικών στοιχείων με καταληκτική ημερομηνία υποβολής την 28.07.2026. Η ΣΕΜΑΕ με το από 27.07.2026 έγγραφό της, ζήτησε την παράταση της ανωτέρω προθεσμίας έως στις 31.08.2026. </t>
-        </is>
-      </c>
-      <c r="U8" s="10" t="inlineStr">
-        <is>
-          <t>1.Κήρυξη απαλλοτριώσεων
-2. Ένταξη στο Πρόγραμμα "ΜΕΤΑΦΟΡΕΣ" 2021-2027
-3. Προέγκριση τευχών δημοπράτησης Β.ΙΙ σταδίου από Δ.Α.</t>
-        </is>
-      </c>
-      <c r="V8" s="10" t="n"/>
-      <c r="W8" s="10" t="n"/>
-      <c r="X8" s="10" t="n"/>
-      <c r="Y8" s="10" t="n"/>
-      <c r="Z8" s="10" t="n"/>
-      <c r="AA8" s="43" t="n"/>
-      <c r="AB8" s="10" t="n"/>
-      <c r="AC8" s="10" t="n"/>
-      <c r="AD8" s="43" t="n">
+      <c r="T8" s="39" t="inlineStr">
+        <is>
+          <t>Η πράξη αφορά στην  ανάπτυξη του Προαστιακού Σιδηροδρόμου στη Δυτική Θεσσαλονίκη επί υφιστάμενων ΣΓ (εν λειτουργία και εκτός λειτουργίας), καθώς και επί νέων τμημάτων ΣΓ. Το δίκτυο του Προαστιακού, μορφής «Υ» συνολικού μήκους 19,5χλμ., θα αποτελείται από δύο κλάδους από τα δυτικά και από ενιαίο κλάδο προς τα ανατολικά, εξυπηρετώντας συνολικά επτά στάσεις.
+Η ΣΕ ΜΑΕ έχει υποβάλει αίτημα χρηματοδότησης στη Διαχειριστική Αρχή, το οποίο είναι σε φάση αξιολόγησης.</t>
+        </is>
+      </c>
+      <c r="U8" s="9" t="inlineStr">
+        <is>
+          <t>Ένταξη στο Πρόγραμμα "ΜΕΤΑΦΟΡΕΣ" 2021-2027</t>
+        </is>
+      </c>
+      <c r="V8" s="49" t="n"/>
+      <c r="W8" s="36" t="n">
         <v>40.66031160608279</v>
       </c>
-      <c r="AE8" s="43" t="n">
+      <c r="X8" s="36" t="n">
         <v>22.93222773211583</v>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1" s="35">
+    <row r="9" ht="60" customHeight="1" s="62">
       <c r="A9" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>ΜΕΤΑΦΟΡΕΣ</t>
         </is>
       </c>
-      <c r="C9" s="47" t="inlineStr">
-        <is>
-          <t>Eγκατάσταση συστημάτων ΣΓ Αλεξανδρούπολη - Πύθιο - Ορμένιο</t>
-        </is>
-      </c>
-      <c r="D9" s="44" t="inlineStr">
+      <c r="C9" s="40" t="inlineStr">
+        <is>
+          <t>ΕΓΚΑΤΑΣΤΑΣΗ ΣΥΣΤΗΜΑΤΩΝ ΑΛΕΞΑΝΔΡΟΥΠΟΛΗ - ΠΥΘΙΟ - ΟΡΜΕΝΙΟ</t>
+        </is>
+      </c>
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>ΕΓΚΑΤΑΣΤΑΣΗ ΣΥΣΤΗΜΑΤΩΝ (ΗΛΕΚΤΡΟΚΙΝΗΣΗ, ΣΗΜΑΤΟΔΟΤΗΣΗ, ΤΗΛΕΔΙΟΙΚΗΣΗ ΜΕ ETCS-LEVEL 1 &amp; GSM-R) ΣΤΗΝ ΑΝΑΒΑΘΜΙΣΜΕΝΗ ΜΟΝΗ ΣΙΔ/ΚΗ ΓΡΑΜΜΗ ΑΛΕΞΑΝΔΡΟΥΠΟΛΗ-ΠΥΘΙΟ-ΟΡΜΕΝΙΟ</t>
         </is>
       </c>
-      <c r="E9" s="41" t="n"/>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.
+</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Πρόγραμμα «ΜΕΤΑΦΟΡΕΣ» 2021-2027 (Δράση 12.1)</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>230.000.000,00 (εκτιμώμενος προϋπολογισμός)
+Δεν έχει υποβληθεί αίτημα χρηματοδότησης.
+Αναμένεται η έκδοση Πρόσκλησης από τη Δ.Α.</t>
+        </is>
+      </c>
+      <c r="I9" s="53" t="inlineStr">
+        <is>
+          <t>~720.000.000 € 
+(π/ϋ οριστικής λύσης Β.Ι Φάσης Ανταγωνιστικού διαλόγου για το σύνολο του έργου Αλεξανδούπολη - Πύθιο - Ορμένιο)</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>Πρόγραμμα «ΜΕΤΑΦΟΡΕΣ» 2021-2027</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>230 εκ. ευρώ.</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>Εξασφαλίστηκε χρηματοδότηση ~545,5 εκ.€ από CEF 21-27. Συνολικός ΠΥ ~780 εκ.€</t>
-        </is>
-      </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="8" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Εκτίμηση: τέλη Φεβρουαρίου 2027</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>4 έτη από την υπογραφή της σύμβασης</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
-        <is>
-          <t>Εγκατάσταση συστημάτων ηλεκτροκίνησης, σηματοδότησης, ETCS-Level 1 &amp; GSM-R σε 178 χλμ.</t>
-        </is>
-      </c>
-      <c r="N9" s="44" t="inlineStr">
-        <is>
-          <t>Υπό δημοπράτηση (Στάδιο Β.Ι ολοκληρώθηκε, αναμονή πρόσκλησης χρηματοδότησης).Το έργο περιλαμβάνεται στη Δράση 12.1 «Σιδηροδρομικά έργα ΔΕΔ-Μ διττής χρήσης» της νέας Προτεραιότητας 12</t>
-        </is>
-      </c>
-      <c r="O9" s="41" t="n"/>
-      <c r="P9" s="41" t="n"/>
-      <c r="Q9" s="41" t="n"/>
-      <c r="R9" s="8" t="inlineStr">
-        <is>
-          <t>Ανταγωνιστικός Διάλογος</t>
-        </is>
-      </c>
-      <c r="S9" s="8" t="n"/>
-      <c r="T9" s="44" t="inlineStr">
-        <is>
-          <t>Το έργο αφορά στην εγκατάσταση ηλεκτροκίνησης και συστημάτων σηματοδότησης, τηλεδιοίκησης με ETCS–Level 1 και GSM-R στο σύνολο της γραμμής Αλεξανδρούπολη - Πύθιο - Ορμένιο, συνολικού μήκους ~ 178 χλμ. 
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Η πράξη αφορά στην εγκατάσταση ηλεκτροκίνησης και συστημάτων σηματοδότησης, τηλεδιοίκησης, ETCS–Level 1 και GSM-R στο σύνολο της γραμμής Αλεξανδρούπολη - Πύθιο - Ορμένιο. 
+</t>
+        </is>
+      </c>
+      <c r="N9" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Το αντικείμενο περιλαμβάνεται στην υπό ανάθεση σύμβαση «Μελέτη – Κατασκευή» του έργου «ΑΝΑΒΑΘΜΙΣΗ ΜΕ ΔΙΠΛΑΣΙΑΣΜΟ ΤΗΣ ΥΦΙΣΤΑΜΕΝΗΣ ΜΟΝΗΣ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΓΡΑΜΜΗΣ ΑΛΕΞΑΝΔΡΟΥΠΟΛΗ – ΠΥΘΙΟ – ΟΡΜΕΝΙΟ», η οποία βρίσκεται σε φάση δημοπράτησης με τη διαδικασία του Ανταγωνιστικού Διαλόγου.
+Η Φάση Β.Ι του Ανταγωνιστικού Διαλόγου ολοκληρώθηκε στις 5-12-2024. Στις 27-1-2025 εγκρίθηκε η βέλτιστη λύση (π/ϋ 720 εκ €) και απεστάλησαν στη Διαχειριστική Αρχή, στο πλαίσιο των ενταγμένων δράσεων στο CEF II,  για προέγκριση τα Τεύχη για τη Β.ΙΙ Φάση. Η Δ.Α. έχει αποστείλει έγγραφο με παρατηρήσεις και αναμένεται η επανυποβολή των Τευχών από τη ΣΕ ΜΑΕ.  </t>
+        </is>
+      </c>
+      <c r="O9" s="34" t="n"/>
+      <c r="P9" s="34" t="n"/>
+      <c r="Q9" s="34" t="n"/>
+      <c r="R9" s="7" t="n"/>
+      <c r="S9" s="9" t="inlineStr">
+        <is>
+          <t>Σε διαδικασία ανάθεσης</t>
+        </is>
+      </c>
+      <c r="T9" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Η πράξη αφορά στην εγκατάσταση ηλεκτροκίνησης και συστημάτων σηματοδότησης, τηλεδιοίκησης, ETCS–Level 1 και GSM-R στο σύνολο της γραμμής Αλεξανδρούπολη - Πύθιο - Ορμένιο. 
 Η προτεινόμενη πράξη έχει εκτιμώμενο π/ϋ ~ 230 εκ. € και περιλαμβάνεται στο αντικείμενο της σύμβασης «Μελέτη – Κατασκευή» του έργου «ΑΝΑΒΑΘΜΙΣΗ ΜΕ ΔΙΠΛΑΣΙΑΣΜΟ ΤΗΣ ΥΦΙΣΤΑΜΕΝΗΣ ΜΟΝΗΣ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΓΡΑΜΜΗΣ ΑΛΕΞΑΝΔΡΟΥΠΟΛΗ – ΠΥΘΙΟ – ΟΡΜΕΝΙΟ», η οποία βρίσκεται σε φάση δημοπράτησης με τη διαδικασία του Ανταγωνιστικού Διαλόγου, και συνολικό προϋπολογισμό (μετά την έγκριση της βέλτιστης λύσης) ~720 εκ. €. Ο συνολικός π/ϋ του έργου ανέρχεται σε ~780 εκ. € (~720 εκ. € για την εργολαβία, ~50 εκ. για απαλλοτριώσεις και ~10 εκ. € για Τεχνικό Σύμβουλο] και μέρος του, ύψους ~545,5 εκ.€ , που αφορά σε εργασίες υποδομής/επιδομής ΣΓ και οδοποιΐας, συγχρηματοδοτείται από  το CEF 2021-2027, στο πλαίσιο 2 ενταγμένων δράσεων για τα 2 επιμέρους τμήματα του άξονα Αλεξανδρούπολη – Πύθιο και Πύθιο – Ορμένιο. 
 Ο Ανταγωνιστικός Διάλογος έχει προχωρήσει, με την ολοκλήρωση του σταδίου Β.Ι στις 5-12-2024. Στις 27-1-2025 εγκρίθηκε η βέλτιστη λύση (προϋπολογισμού 720 εκ €) και απεστάλησαν στο πλαίσιο των ενταγμένων πράξεων στο CEF II στην ΕΥΔ / ΜΕΤΑΦΟΡΕΣ για προέγκριση τα Τεύχη για το Β.ΙΙ στάδιο, κατά το οποίο θα προσκληθούν οι προεπιλεγέντες για υποβολή δεσμευτικής προσφοράς, ώστε να επιλεγεί ο ανάδοχος. Η Δ.Α. έχει αποστείλει έγγραφο με παρατηρήσεις και αναμένεται η επανυποβολή των Τευχών στη Δ.Α.  
 H υπογραφή της σύμβασης εκτιμάται τέλη Φεβρουαρίου 2027. Διάρκεια κατασκευής 4 έτη.
-Στις 03.04.2026 υποβλήθηκε στην ΕΥΔ ΜΕΤΑΦΟΡΕΣ έντυπο εξειδίκευσης της Δράσης, στις 08.07.2026 εγκρίθηκε η 6η Εξειδίκευση του Προγράμματος "ΜΕΤΑΦΟΡΕΣ" 2021-2027 και αναμένεται η έκδοση της σχετικής πρόσκλησης για την υποβολή πρότασης χρηματοδότησης.</t>
-        </is>
-      </c>
-      <c r="U9" s="44" t="inlineStr">
+Στις 03.04.2026 υποβλήθηκε στην ΕΥΔ ΜΕΤΑΦΟΡΕΣ έντυπο εξειδίκευσης της Δράσης, στις 08.07.2026 εγκρίθηκε η 6η Εξειδίκευση του Προγράμματος "ΜΕΤΑΦΟΡΕΣ" 2021-2027 και αναμένεται η έκδοση της σχετικής πρόσκλησης για την υποβολή πρότασης χρηματοδότησης.
+</t>
+        </is>
+      </c>
+      <c r="U9" s="37" t="inlineStr">
         <is>
           <t>1. ΄Εκδοση πρόσκλησης από την ΕΥΔ ΜΕΤΑΦΟΡΕΣ για την υποβολή πρότασης χρηματοδότησης 
 2. Ένταξη στο Πρόγραμμα "ΜΕΤΑΦΟΡΕΣ" 2021-2027</t>
         </is>
       </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
-          <t>230 εκ. ευρώ.</t>
-        </is>
-      </c>
-      <c r="W9" s="8" t="n"/>
-      <c r="X9" s="8" t="n"/>
-      <c r="Y9" s="8" t="n"/>
-      <c r="Z9" s="8" t="n"/>
-      <c r="AA9" s="41" t="n"/>
-      <c r="AB9" s="8" t="n"/>
-      <c r="AC9" s="8" t="n"/>
-      <c r="AD9" s="41" t="n">
+      <c r="V9" s="48" t="n"/>
+      <c r="W9" s="34" t="n">
         <v>41.26256578347363</v>
       </c>
-      <c r="AE9" s="41" t="n">
+      <c r="X9" s="34" t="n">
         <v>26.32621391998375</v>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1" s="35">
-      <c r="A10" s="9" t="n">
+    <row r="10" ht="60" customHeight="1" s="62">
+      <c r="A10" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>ΜΕΤΑΦΟΡΕΣ</t>
         </is>
       </c>
-      <c r="C10" s="42" t="inlineStr">
-        <is>
-          <t>Μέστη-Αλεξανδρούπολη</t>
-        </is>
-      </c>
-      <c r="D10" s="46" t="inlineStr">
-        <is>
-          <t>ΚΑΤΑΣΚΕΥΗ ΤΗΣ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΓΡΑΜΜΗΣ ΜΕΤΑΞΥ ΜΕΣΤΗΣ-ΑΛΕΞΑΝΔΡΟΥΠΟΛΗΣ &amp; σύνδεση ΒΙΠΕ</t>
-        </is>
-      </c>
-      <c r="E10" s="43" t="n"/>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>Δρομολογείται διαγωνισμός</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
+        <is>
+          <t>ΜΕΣΤΗ - ΑΛΕΞΑΝΔΡΟΥΠΟΛΗ</t>
+        </is>
+      </c>
+      <c r="D10" s="39" t="inlineStr">
+        <is>
+          <t>ΚΑΤΑΣΚΕΥΗ ΤΗΣ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΓΡΑΜΜΗΣ ΜΕΤΑΞΥ ΜΕΣΤΗΣ-ΑΛΕΞΑΝΔΡΟΥΠΟΛΗΣ</t>
+        </is>
+      </c>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.
+</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>Πρόγραμμα «ΜΕΤΑΦΟΡΕΣ» 2021-2027 (Δράση 12.1)</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>210.000.000 € (Εκτιμώμενος προϋπολογισμός)</t>
-        </is>
-      </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>210000000</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="inlineStr">
-        <is>
-          <t>Δρομολογείται διαγωνισμός</t>
-        </is>
-      </c>
-      <c r="K10" s="10" t="n"/>
-      <c r="L10" s="10" t="inlineStr">
-        <is>
-          <t>3 έτη από τη συμβασιοποίηση</t>
-        </is>
-      </c>
-      <c r="M10" s="10" t="inlineStr">
-        <is>
-          <t>Κατασκευή 33,8χλμ νέας γραμμής, σταθμών, γεφυρών &amp; σηράγγων (Διττής χρήσης)</t>
-        </is>
-      </c>
-      <c r="N10" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Η προτεινόμενη πράξη έχει εκτιμώμενο π/υ ~ 210 εκ. €. Έχουν εκπονηθεί και εγκριθεί οι οριστικές μελέτες. Έχουν συνταχθεί σχέδια Τευχών Δημοπράτησης και υπάρχουν εγκεκριμένοι Περιβαλλοντικοί Όροι σε ισχύ. 
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>Δεν έχει υποβληθεί αίτημα χρηματοδότησης.
+Αναμένεται η έκδοση Πρόσκλησης από τη Δ.Α.</t>
+        </is>
+      </c>
+      <c r="I10" s="53" t="inlineStr">
+        <is>
+          <t>210.000.000,00 
+(εκτιμώμενος προϋπολογισμός)</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>Προγραμματίζεται η δημοπράτηση με ανοιχτό μειοδοτικό διαγωνισμό εντός 6 μηνών μετά την εξασφάλιση της χρηματοδότησης</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>3 έτη από την υπογραφή της σύμβασης</t>
+        </is>
+      </c>
+      <c r="M10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Η πράξη αφορά στην κατασκευή παραλλαγής της υφιστάμενης  Σ/Γ μήκους 33,8 χλμ (εργασιες υποδομής και επιδομής), συμπεριλαμβανομένου του κλάδου προς τη Βιομηχανική Περιοχή Αλεξανδρούπολης. </t>
+        </is>
+      </c>
+      <c r="N10" s="39" t="inlineStr">
+        <is>
+          <t>Έχουν εκπονηθεί και εγκριθεί οι οριστικές μελέτες. Έχουν συνταχθεί σχέδια Τευχών Δημοπράτησης και υπάρχουν εγκεκριμένοι Περιβαλλοντικοί Όροι σε ισχύ. 
 Δρομολογείται άμεσα η ανάθεση  εκπόνησης Ανάλυσης Κόστους Οφέλους (πιθανώς για τον ευρύτερο άξονα Θεσσαλονίκη - Αλεξανδρούπολη/ Σύνορα). 
-Αναμένεται η οριστικοποποίηση του Κτηματολογίου, η κήρυξη των απαλλοτριώσεων και η ανάθεση της σύνταξης έκθεσης εκτίμησης της αποζημίωσης σε ανεξάρτητο πιστοποιημένο εκτιμητή. </t>
-        </is>
-      </c>
-      <c r="O10" s="43" t="n"/>
-      <c r="P10" s="43" t="n"/>
-      <c r="Q10" s="43" t="n"/>
-      <c r="R10" s="10" t="inlineStr">
-        <is>
-          <t>- (Υπό έκδοση μετά την ένταξη)</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="n"/>
-      <c r="T10" s="46" t="inlineStr">
+Αναμένεται η οριστικοποποίηση του Κτηματολογίου και η κήρυξη των απαλλοτριώσεων.</t>
+        </is>
+      </c>
+      <c r="O10" s="36" t="n"/>
+      <c r="P10" s="36" t="n"/>
+      <c r="Q10" s="36" t="n"/>
+      <c r="R10" s="9" t="n"/>
+      <c r="S10" s="9" t="inlineStr">
+        <is>
+          <t>Σε ωρίμανση</t>
+        </is>
+      </c>
+      <c r="T10" s="39" t="inlineStr">
         <is>
           <t>Το έργο αφορά στην κατασκευή παραλλαγής της υφιστάμενης  Σ/Γ μήκους 33,8 χλμ, συμπεριλαμβανομένου του κλάδου προς τη Βιομηχανική Περιοχή Αλεξανδρούπολης. 
 Ειδικότερα περιλαμβάνει:
@@ -1838,96 +1753,100 @@
 Στις 03.04.2026 υποβλήθηκε στην ΕΥΔ ΜΕΤΑΦΟΡΕΣ έντυπο εξειδίκευσης της Δράσης, στις 08.07.2026 εγκρίθηκε η 6η Εξειδίκευση του Προγράμματος "ΜΕΤΑΦΟΡΕΣ" 2021-2027 και αναμένεται η έκδοση της σχετικής πρόσκλησης για την υποβολή πρότασης χρηματοδότησης.</t>
         </is>
       </c>
-      <c r="U10" s="46" t="inlineStr">
+      <c r="U10" s="39" t="inlineStr">
         <is>
           <t>1. ΄Εκδοση πρόσκλησης από την ΕΥΔ ΜΕΤΑΦΟΡΕΣ για την υποβολή πρότασης χρηματοδότησης 
 2. Ένταξη στο Πρόγραμμα "ΜΕΤΑΦΟΡΕΣ" 2021-2027</t>
         </is>
       </c>
-      <c r="V10" s="10" t="inlineStr">
-        <is>
-          <t>210.000.000 € (Εκτιμώμενος προϋπολογισμός)</t>
-        </is>
-      </c>
-      <c r="W10" s="10" t="n"/>
-      <c r="X10" s="10" t="n"/>
-      <c r="Y10" s="10" t="n"/>
-      <c r="Z10" s="10" t="n"/>
-      <c r="AA10" s="43" t="n"/>
-      <c r="AB10" s="10" t="n"/>
-      <c r="AC10" s="10" t="n"/>
-      <c r="AD10" s="43" t="n">
+      <c r="V10" s="49" t="n"/>
+      <c r="W10" s="36" t="n">
         <v>40.96246629760246</v>
       </c>
-      <c r="AE10" s="43" t="n">
+      <c r="X10" s="36" t="n">
         <v>25.83616535699013</v>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1" s="35">
+    <row r="11" ht="60" customHeight="1" s="62">
       <c r="A11" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>ΜΕΤΑΦΟΡΕΣ</t>
         </is>
       </c>
-      <c r="C11" s="40" t="inlineStr">
-        <is>
-          <t>Ίασμος-Πολύανθος</t>
-        </is>
-      </c>
-      <c r="D11" s="44" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>ΙΑΣΜΟΣ - ΠΟΛΥΑΝΘΟΣ</t>
+        </is>
+      </c>
+      <c r="D11" s="37" t="inlineStr">
         <is>
           <t>ΚΑΤΑΣΚΕΥΗ ΤΗΣ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΓΡΑΜΜΗΣ ΜΕΤΑΞΥ ΙΑΣΜΟΥ-ΠΟΛΥΑΝΘΟΥ</t>
         </is>
       </c>
-      <c r="E11" s="41" t="n"/>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>ΕΡΓΟΣΕ Α.Ε. (Προγραμματίζεται διαγωνισμός)</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.
+</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>Πρόγραμμα «ΜΕΤΑΦΟΡΕΣ» 2021-2027 (Δράση 12.1)</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>40.000.000 € (Εκτιμώμενος προϋπολογισμός)</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>40000000</t>
-        </is>
-      </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>ΕΡΓΟΣΕ Α.Ε. (Προγραμματίζεται διαγωνισμός)</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="n"/>
-      <c r="L11" s="8" t="n"/>
-      <c r="M11" s="8" t="inlineStr">
-        <is>
-          <t>Νέα βελτιωμένη χάραξη 7,04χλμ, γέφυρα Κομψάτου (350μ), νέοι Σ.Σ. Ίασμου-Πολύανθου.Το έργο περιλαμβάνεται στη Δράση 12.1 «Σιδηροδρομικά έργα ΔΕΔ-Μ διττής χρήσης» της νέας Προτεραιότητας 12 «Ανάπτυξη ανθεκτικών αμυντικών υποδομών και προμήθειες για την ενίσχυση της πολιτικής ετοιμότητας και ασφάλειας – Ταμείο Συνοχής</t>
-        </is>
-      </c>
-      <c r="N11" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Η προτεινόμενη πράξη έχει εκτιμώμενο π/υ ~ 40 εκ. €. Έχουν εκπονηθεί και εγκριθεί οι οριστικές μελέτες. Έχουν συνταχθεί σχέδια Τευχών Δημοπράτησης και υπάρχουν εγκεκριμένοι Περιβαλλοντικοί Όροι σε ισχύ. 
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>Δεν έχει υποβληθεί αίτημα χρηματοδότησης.
+Αναμένεται η έκδοση Πρόσκλησης από τη Δ.Α.</t>
+        </is>
+      </c>
+      <c r="I11" s="52" t="inlineStr">
+        <is>
+          <t>40.000.000,00 
+(εκτιμώμενος προϋπολογισμός)</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Προγραμματίζεται η δημοπράτηση με ανοιχτό μειοδοτικό διαγωνισμό εντός 6 μηνών μετά την εξασφάλιση της χρηματοδότησης</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>2 έτη από την  υπογραφή της σύμβασης</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>Η πράξη αφορά στην κατασκευή της νέας, αναβαθμισμένης γραμμής που περιλαμβάνει την υποδομή - με τη νέα γέφυρα του ποταμού Κομψάτου, μήκους 350 μ. και επιδομή.</t>
+        </is>
+      </c>
+      <c r="N11" s="37" t="inlineStr">
+        <is>
+          <t>Έχουν εκπονηθεί και εγκριθεί οι οριστικές μελέτες. Έχουν συνταχθεί σχέδια Τευχών Δημοπράτησης και υπάρχουν εγκεκριμένοι Περιβαλλοντικοί Όροι σε ισχύ. 
 Δρομολογείται άμεσα η ανάθεση  εκπόνησης Ανάλυσης Κόστους Οφέλους (πιθανώς για τον ευρύτερο άξονα Θεσσαλονίκη - Αλεξανδρούπολη/ Σύνορα). 
-Αναμένεται η οριστικοποποίηση του Κτηματολογίου, η κήρυξη των απαλλοτριώσεων και η ανάθεση της σύνταξης έκθεσης εκτίμησης της αποζημίωσης σε ανεξάρτητο πιστοποιημένο εκτιμητή. </t>
-        </is>
-      </c>
-      <c r="O11" s="41" t="n"/>
-      <c r="P11" s="41" t="n"/>
-      <c r="Q11" s="41" t="n"/>
-      <c r="R11" s="8" t="n"/>
-      <c r="S11" s="8" t="n"/>
-      <c r="T11" s="44" t="inlineStr">
+Αναμένεται η οριστικοποποίηση του Κτηματολογίου και η κήρυξη των απαλλοτριώσεων.</t>
+        </is>
+      </c>
+      <c r="O11" s="34" t="n"/>
+      <c r="P11" s="34" t="n"/>
+      <c r="Q11" s="34" t="n"/>
+      <c r="R11" s="7" t="n"/>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>Σε ωρίμανση</t>
+        </is>
+      </c>
+      <c r="T11" s="37" t="inlineStr">
         <is>
           <t>Το έργο αφορά στην κατασκευή σε νέα βελτιωμένη χάραξη Σ/Γ μήκους 7,04 χλμ. 
 Ειδικότερα  περιλαμβάνει:
@@ -1941,118 +1860,108 @@
 Στις 03.04.2026 υποβλήθηκε στην ΕΥΔ ΜΕΤΑΦΟΡΕΣ έντυπο εξειδίκευσης της Δράσης, στις 08.07.2026 εγκρίθηκε η 6η Εξειδίκευση του Προγράμματος "ΜΕΤΑΦΟΡΕΣ" 2021-2027 και αναμένεται η έκδοση της σχετικής πρόσκλησης για την υποβολή πρότασης χρηματοδότησης.</t>
         </is>
       </c>
-      <c r="U11" s="44" t="inlineStr">
+      <c r="U11" s="37" t="inlineStr">
         <is>
           <t>1. ΄Εκδοση πρόσκλησης από την ΕΥΔ ΜΕΤΑΦΟΡΕΣ για την υποβολή πρότασης χρηματοδότησης 
 2. Ένταξη στο Πρόγραμμα "ΜΕΤΑΦΟΡΕΣ" 2021-2027</t>
         </is>
       </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t>40.000.000 € (Εκτιμώμενος προϋπολογισμός)</t>
-        </is>
-      </c>
-      <c r="W11" s="8" t="n"/>
-      <c r="X11" s="8" t="n"/>
-      <c r="Y11" s="8" t="n"/>
-      <c r="Z11" s="8" t="n"/>
-      <c r="AA11" s="41" t="n"/>
-      <c r="AB11" s="8" t="n"/>
-      <c r="AC11" s="8" t="n"/>
-      <c r="AD11" s="41" t="n">
+      <c r="V11" s="48" t="n"/>
+      <c r="W11" s="34" t="n">
         <v>41.13366749906856</v>
       </c>
-      <c r="AE11" s="41" t="n">
+      <c r="X11" s="34" t="n">
         <v>25.20612223303816</v>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1" s="35">
+    <row r="12" ht="60" customHeight="1" s="62">
       <c r="A12" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>ΜΕΤΑΦΟΡΕΣ</t>
         </is>
       </c>
-      <c r="C12" s="47" t="inlineStr">
-        <is>
-          <t>GSM-R  Τιθορέα-Δομοκός, Θεσσαλονίκη-Ειδομένη, Κιάτο-Πάτρα</t>
-        </is>
-      </c>
-      <c r="D12" s="44" t="inlineStr">
+      <c r="C12" s="40" t="inlineStr">
+        <is>
+          <t>GSM-R  ΚΙΑΤΟ - ΡΙΟ, ΤΙΘΟΡΕΑ - ΔΟΜΟΚΟΣ, ΘΕΣΣΑΛΟΝΙΚΗ  – ΕΙΔΟΜΕΝΗ, ΠΑΛΑΙΟΦΑΡΣΑΛΟΣ - ΚΑΛΑΜΠΑΚΑ ΚΑΙ ΛΑΡΙΣΑ - ΒΟΛΟΣ</t>
+        </is>
+      </c>
+      <c r="D12" s="37" t="inlineStr">
         <is>
           <t>ΠΡΟΜΗΘΕΙΑ ΣΥΣΤΗΜΑΤΟΣ GSM-R ΜΕ ΣΥΝΑΦΕΙΣ ΥΠΗΡΕΣΙΕΣ ΓΙΑ ΤΑ ΤΜΗΜΑΤΑ ΓΡΑΜΜΗΣ ΚΙΑΤΟ - ΡΙΟ, ΤΙΘΟΡΕΑ - ΔΟΜΟΚΟΣ, ΘΕΣΣΑΛΟΝΙΚΗ  – ΕΙΔΟΜΕΝΗ, ΠΑΛΑΙΟΦΑΡΣΑΛΟΣ - ΚΑΛΑΜΠΑΚΑ ΚΑΙ ΛΑΡΙΣΑ - ΒΟΛΟΣ</t>
         </is>
       </c>
-      <c r="E12" s="41" t="inlineStr">
-        <is>
-          <t>Τιθορέα - Λιανοκλάδι-Δομοκός : Κεντρικό (Core), 
-Θεσ/κη - Ειδομένη : Κεντρικό (Core),
-Κιάτο-Πάτρα : Κεντρικό (Core)</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.
-(ΕΡΓΟΣΕ ΑΕ)</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="E12" s="34" t="inlineStr">
+        <is>
+          <t>Τιθορέα - Δομοκός: Κεντρικό (Core), 
+Θεσ/κη - Ειδομένη: Κεντρικό (Core),
+Κιάτο - Ρίο: Κεντρικό (Core),
+Παλαιοφάρσαλος - Καλαμπακα: Κεντρικό (Core), 
+Λάρισα - Βόλος: Συνολικό (Comprehensive)</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.
+</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>Πρόγραμμα «ΜΕΤΑΦΟΡΕΣ» 2021-2027</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>45.000.000 € (Εκτιμώμενος προϋπολογισμός)</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>45.000.000 €</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 45.974.884,50 € (Συγχρηματοδοτούμενη Δημόσια Δαπάνη σύμφωνα με το αίτημα χρηματοδότησης που υποβλήθηκε από τη ΣΕ ΜΑΕ)</t>
+        </is>
+      </c>
+      <c r="I12" s="52" t="inlineStr">
+        <is>
+          <t>45.000.000 € 
+(εκτιμώμενος προϋπολογισμός)</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t>Εκτίμηση: 4ο τρίμηνο 2026</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t>3 έτη από τη συμβασιοποίηση</t>
-        </is>
-      </c>
-      <c r="M12" s="44" t="inlineStr">
-        <is>
-          <t>Η πράξη έχει ως αντικείμενο τη μελέτη εφαρμογής, προμήθεια και εγκατάσταση εξοπλισμού GSM-R για τα τμήματα του άξονα ΠΑΘΕΠ Τιθορέα – Δομοκός, Θεσσαλονίκη – Ειδομένη και Κιάτο – Ρίο, καθώς και για τα τμήματα Παλαιοφάρσαλος - Καλαμπάκα και Λάρισα - Βόλος.
-Η υποβληθείσα για χρηματοδότηση πρόταση περιλαμβάνει 4 Υποέργα:
-- Υ/Ε 1: Προμήθεια συστήματος GSM-R με συναφείς υπηρεσίες για τα τμήματα γραμμής Κιάτο - Ρίο, Τιθορέα - Δομοκός, Θεσσαλονίκη  – Ειδομένη, Παλαιοφάρσαλος - Καλαμπάκα και Λάρισα - Βόλος
-- Υ/Ε 2: Απαιτούμενες συνδέσεις, αναβαθμίσεις και μετατοπίσεις δικτύων ΟΚΩ
-- Υ/Ε 3: Έγκριση τεχνικής λύσης εξοπλισμού ERTMS με τις ΤΠΔ από τον Οργανισμό Σιδηροδρόμων της Ε.Ε. (ERA)
-- Υ/Ε 4: Λειτουργικά έξοδα της ΕΕΣΥΠ (μη επιλέξιμες δαπάνες)</t>
-        </is>
-      </c>
-      <c r="N12" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Στις 10.07.2026 υποβλήθηκε από τον δικαιούχο "ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε." αίτηση χρηματοδότησης για την Πράξη με κωδικό MIS 6054603 και συνολική δημόσια δαπάνη 57.463.025,47 ευρώ και συγχρηματοδοτούμενη δημόσια δαπάνη 45.974.884,50 €. </t>
-        </is>
-      </c>
-      <c r="O12" s="41" t="n"/>
-      <c r="P12" s="41" t="n"/>
-      <c r="Q12" s="41" t="n"/>
-      <c r="R12" s="8" t="n"/>
-      <c r="S12" s="8" t="inlineStr">
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Εκτίμηση: 1ο τρίμηνο 2027</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>3 έτη από την υπογραφή της σύμβασης</t>
+        </is>
+      </c>
+      <c r="M12" s="37" t="inlineStr">
+        <is>
+          <t>Η πράξη έχει ως αντικείμενο τη μελέτη εφαρμογής, προμήθεια και εγκατάσταση εξοπλισμού GSM-R για τα τμήματα του άξονα ΠΑΘΕΠ Τιθορέα – Δομοκός, Θεσσαλονίκη – Ειδομένη και Κιάτο – Πάτρα.</t>
+        </is>
+      </c>
+      <c r="N12" s="37" t="inlineStr">
+        <is>
+          <t>Σύμφωνα με την από 16.06.2025 Απόφαση της Κυβερνητικής Επιτροπής Συμβάσεων Στρατηγικής Σημασίας, το έργο έχει ενταχθεί στο Αναπτυξιακό Πρόγραμμα Συμβάσεων Στρατηγικής Σημασίας του Ν.4799/2021 και έχει περιέλθει στις αρμοδιότητες της Ελληνικής Εταιρείας Συμμετοχών και Περιουσίας (ΕΕΣΥΠ) ΑΕ για την ωρίμανση, διενέργεια διαγωνισμών και εκτέλεση των συμβάσεων υλοποίησής του. Στις 03.02.2026 υπογράφηκε η προβλεπόμενη στο άρθρο 5β του Ν. 3986/2011 Σύμβαση μεταξύ του ΥΠΥΜΕ, της ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ ΜΑΕ και της ΕΕΣΥΠ ΑΕ.
+Η ΣΕ ΜΑΕ έχει υποβάλει αίτημα χρηματοδότησης στη Διαχειριστική Αρχή, το οποίο είναι σε φάση αξιολόγησης.</t>
+        </is>
+      </c>
+      <c r="O12" s="34" t="n"/>
+      <c r="P12" s="34" t="n"/>
+      <c r="Q12" s="34" t="n"/>
+      <c r="R12" s="7" t="n">
+        <v>6054603</v>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>Σε ωρίμανση</t>
         </is>
       </c>
-      <c r="T12" s="44" t="inlineStr">
+      <c r="T12" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">Η πράξη έχει ως αντικείμενο τη μελέτη εφαρμογής, προμήθεια και εγκατάσταση εξοπλισμού GSM-R για τα τμήματα του άξονα ΠΑΘΕΠ Τιθορέα – Δομοκός, Θεσσαλονίκη – Ειδομένη και Κιάτο – Ρίο, καθώς και για τα τμήματα Παλαιοφάρσαλος - Καλαμπάκα και Λάρισα - Βόλος.
 Η υποβληθείσα για χρηματοδότηση πρόταση περιλαμβάνει 4 Υποέργα:
@@ -2071,109 +1980,107 @@
 </t>
         </is>
       </c>
-      <c r="U12" s="44" t="inlineStr">
-        <is>
-          <t>1. Υποβολή αίτησης για ένταξη του έργου στο Πρόγραμμα ΜΕΤΑΦΟΡΕΣ 2021-2027.
-2. Αποστολή τευχών δημοπράτησης στη Διαχειριστική Αρχή για προέγκριση δημοπράτησης.</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="n"/>
-      <c r="W12" s="8" t="n"/>
-      <c r="X12" s="8" t="n"/>
-      <c r="Y12" s="8" t="n"/>
-      <c r="Z12" s="8" t="n"/>
-      <c r="AA12" s="41" t="n"/>
-      <c r="AB12" s="8" t="n"/>
-      <c r="AC12" s="8" t="n"/>
-      <c r="AD12" s="41" t="n">
+      <c r="U12" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-  Ένταξη στο Πρόγραμμα "ΜΕΤΑΦΟΡΕΣ" 2021-2027
+- Αποστολή τευχών δημοπράτησης στη Διαχειριστική Αρχή για προέγκριση δημοπράτησης. </t>
+        </is>
+      </c>
+      <c r="V12" s="48" t="n"/>
+      <c r="W12" s="34" t="n">
         <v>38.16802309317018</v>
       </c>
-      <c r="AE12" s="41" t="n">
+      <c r="X12" s="34" t="n">
         <v>22.32814018832298</v>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1" s="35">
+    <row r="13" ht="60" customHeight="1" s="62">
       <c r="A13" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>ΜΕΤΑΦΟΡΕΣ</t>
         </is>
       </c>
-      <c r="C13" s="40" t="inlineStr">
-        <is>
-          <t>Θεσ/νίκη-Ειδομένη</t>
-        </is>
-      </c>
-      <c r="D13" s="44" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>ΘΕΣΣΑΛΟΝΙΚΗ - ΕΙΔΟΜΕΝΗ</t>
+        </is>
+      </c>
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t>ΕΓΚΑΤΑΣΤΑΣΗ ΣΥΣΤΗΜΑΤΟΣ ΣΗΜΑΤΟΔΟΤΗΣΗΣ ΚΑΙ ETCS – LEVEL 1 ΣΤΗ ΜΟΝΗ ΣΙΔΗΡΟΔΡΟΜΙΚΗ ΓΡΑΜΜΗ ΘΕΣΣΑΛΟΝΙΚΗ – ΕΙΔΟΜΕΝΗ (ΜΕΣΩ ΤΗΣ ΝΕΑΣ  ΠΑΡΑΛΛΑΓΗΣ ΣΤΟ ΤΜΗΜΑ ΠΟΛΥΚΑΣΤΡΟ – ΕΙΔΟΜΕΝΗ) ΚΑΙ ΑΝΤΙΚΑΤΑΣΤΑΣΗ 37 ΑΛΛΑΓΩΝ ΤΡΟΧΙΑΣ ΓΙΑ ΤΙΣ ΑΝΑΓΚΕΣ ΤΗΣ ΣΗΜΑΤΟΔΟΤΗΣΗΣ- Β' ΦΑΣΗ</t>
         </is>
       </c>
-      <c r="E13" s="41" t="inlineStr">
+      <c r="E13" s="34" t="inlineStr">
         <is>
           <t>Κεντρικό (Core)</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε. 
-(ΕΡΓΟΣΕ ΑΕ)</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.
+</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>Πρόγραμμα «ΜΕΤΑΦΟΡΕΣ» 2021-2027 (Phasing)</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>38.577.292,81 € (Συγχρηματοδοτούμενη δαπάνη)</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>40973034.12</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>38.577.292,81 € (Συγχρηματοδοτούμενη Δημόσια Δαπάνη)</t>
+        </is>
+      </c>
+      <c r="I13" s="52" t="inlineStr">
+        <is>
+          <t>40.973.034,12 € 
+(χωρίς Φ.Π.Α.)</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>ΚΟΙΝΟΠΡΑΞΙΑ ΑΒΑΞ ΑΕ - ALSTOM Transport SA</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>11.03.2022</t>
         </is>
       </c>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t>15.05.2026 (Αιτούμενη παράταση)</t>
-        </is>
-      </c>
-      <c r="M13" s="8" t="inlineStr">
-        <is>
-          <t>Σηματοδότηση &amp; ETCS L1 σε 70,5χλμ γραμμής, αντικατάσταση 37 αλλαγών τροχιάς</t>
-        </is>
-      </c>
-      <c r="N13" s="44" t="inlineStr">
-        <is>
-          <t>Η πράξη βρίσκεται σε προχωρημένο στάδιο υλοποίησης, με ολοκληρωμένη εγκατάσταση συστημάτων σηματοδότησης και ETCS L1 και ποσοστό προόδου περίπου 97,81%. Η χρηματοδότηση έχει ήδη υποστεί phasing από το ΕΠ ΥΜΕΠΕΡΑΑ 2014–2020, ενώ το έργο εισέρχεται σε φάση ολοκλήρωσης και λειτουργικής σταθεροποίησης. Παράλληλα, βρίσκονται σε εξέλιξη παρεμβάσεις αντιμετώπισης πλημμυρικών προβλημάτων στον κόμβο ΤΧ1 μέσω νέων μελετών και επείγοντων έργων. Κρίσιμο ζητούμενο παραμένει η ολοκλήρωση των αντιπλημμυρικών παρεμβάσεων και η πλήρης επιχειρησιακή λειτουργία του συστήματος.</t>
-        </is>
-      </c>
-      <c r="O13" s="41" t="n"/>
-      <c r="P13" s="41" t="n"/>
-      <c r="Q13" s="41" t="n"/>
-      <c r="R13" s="8" t="n">
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>15.05.2026 (Ημερομηνία περαίωσης εργασιών)</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Η πράξη αφορά στην υλοποίηση της Β΄ Φάσης του έργου με αντικείμενο την εγκατάσταση του συστήματος σηματοδότησης και ETCS – Level 1 στη μονή σιδηροδρομική γραμμή Θεσσαλονίκη – Ειδομένη (μέσω της νέας παραλλαγής στο τμήμα Πολύκαστρο – Ειδομένη), σε μήκος περίπου 70,5 χλμ και αντικατάσταση 37 αλλαγών τροχιάς για τις ανάγκες της σηματοδότησης. 
+</t>
+        </is>
+      </c>
+      <c r="N13" s="37" t="inlineStr">
+        <is>
+          <t>Ολοκληρώθηκαν οι εργασίες.
+Εκκρεμεί η διενέργεια των απαιτούμενων δοκιμών και η διαδικασία προετοιμασίας φακέλου που θα υποβληθεί στη ΡΑΣ για την έγκριση θέσης σε λειτουργία του υποσυστήματος "Διαλειτουργικότητα".
+Εκκρεμεί η διασύνδεση με τη Βόρεια Μακεδονία.</t>
+        </is>
+      </c>
+      <c r="O13" s="34" t="n"/>
+      <c r="P13" s="34" t="n"/>
+      <c r="Q13" s="34" t="n"/>
+      <c r="R13" s="7" t="n">
         <v>6050857</v>
       </c>
-      <c r="S13" s="8" t="inlineStr">
-        <is>
-          <t>Σε εξέλιξη</t>
-        </is>
-      </c>
-      <c r="T13" s="44" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>Ολοκληρωμένο
+φυσικό αντικείμενο</t>
+        </is>
+      </c>
+      <c r="T13" s="37" t="inlineStr">
         <is>
           <t>Η πράξη αφορά στην υλοποίηση της Β΄ Φάσης του έργου με αντικείμενο την εγκατάσταση του συστήματος σηματοδότησης και ETCS – Level 1 στη μονή σιδηροδρομική γραμμή Θεσσαλονίκη – Ειδομένη (μέσω της νέας παραλλαγής στο τμήμα Πολύκαστρο – Ειδομένη) και αντικατάσταση 37 αλλαγών τροχιάς για τις ανάγκες της σηματοδότησης. 
 Η αρχή του έργου οριoθετείται στον Σ.Σ. ΤΧ1 (είσοδος από ΤΧ2) και το τέλος, στο σταθμό Ειδομένης (Χ.Θ. 77+521 - πέρας Σ.Σ. Ειδομένης). Στο τμήμα Πολύκαστρο – Ειδομένη ακολουθεί τη νέα παραλλαγή της γραμμής. Περιλαμβάνονται περιορισμένες παρεμβάσεις και στην παλαιά γραμμή οι οποίες καλύπτονται από εθνικούς πόρους.
@@ -2195,131 +2102,117 @@
 Εκκρεμεί η διασύνδεση με τη Βόρεια Μακεδονία.</t>
         </is>
       </c>
-      <c r="U13" s="44" t="inlineStr">
-        <is>
-          <t>- Διενέργεια απαιτούμενων δοκιμών και προετοιμασία φακέλου που θα υποβληθεί στη ΡΑΣ για έγκριση θέσης σε λειτουργία του υποσυστήματος "Διαλειτουργικότητα"
-- Διασύνδεση με τη Βόρεια Μακεδονία.</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>38.577.292,81 €</t>
-        </is>
-      </c>
-      <c r="W13" s="53" t="n">
-        <v>38399811.71</v>
-      </c>
-      <c r="X13" s="53" t="n">
-        <v>33095207.04</v>
-      </c>
-      <c r="Y13" s="8" t="inlineStr">
+      <c r="U13" s="37" t="inlineStr">
+        <is>
+          <t>1. Διενέργεια απαιτούμενων δοκιμών και προετοιμασία φακέλου που θα υποβληθεί στη ΡΑΣ για έγκριση θέσης σε λειτουργία του υποσυστήματος "Διαλειτουργικότητα"
+2. Διασύνδεση με τη Βόρεια Μακεδονία.</t>
+        </is>
+      </c>
+      <c r="V13" s="48" t="inlineStr">
         <is>
           <t>22.12.2025</t>
         </is>
       </c>
-      <c r="Z13" s="8" t="n"/>
-      <c r="AA13" s="41" t="n"/>
-      <c r="AB13" s="8" t="n"/>
-      <c r="AC13" s="8" t="n"/>
-      <c r="AD13" s="41" t="n">
+      <c r="W13" s="34" t="n">
         <v>41.11238311760676</v>
       </c>
-      <c r="AE13" s="41" t="n">
+      <c r="X13" s="34" t="n">
         <v>22.51968143610305</v>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1" s="35">
+    <row r="14" ht="60" customHeight="1" s="62">
       <c r="A14" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>ΜΕΤΑΦΟΡΕΣ</t>
         </is>
       </c>
-      <c r="C14" s="40" t="inlineStr">
-        <is>
-          <t>Παλαιοφάρσαλος-Καλαμπάκα</t>
-        </is>
-      </c>
-      <c r="D14" s="44" t="inlineStr">
-        <is>
-          <t>ΕΓΚΑΤΑΣΤΑΣΗ ΗΛΕΚΤΡΟΚΙΝΗΣΗΣ, ΣΗΜΑΤΟΔΟΤΗΣΗΣ – ΤΗΛΕΔΙΟΙΚΗΣΗΣ ΚΑΙ ETCS L1 ΣΤΗΝ ΥΦΙΣΤΑΜΕΝΗ ΜΟΝΗ ΣΙΔΗΡΟΔΡΟΜΙΚΗ ΓΡΑΜΜΗ ΠΑΛΑΙΟΦΑΡΣΑΛΟΣ – ΚΑΛΑΜΠΑΚΑ</t>
-        </is>
-      </c>
-      <c r="E14" s="41" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>ΠΑΛΑΙΟΦΑΡΣΑΛΟΣ - ΚΑΛΑΜΠΑΚΑ</t>
+        </is>
+      </c>
+      <c r="D14" s="37" t="inlineStr">
+        <is>
+          <t>ΕΓΚΑΤΑΣΤΑΣΗ ΗΛΕΚΤΡΟΚΙΝΗΣΗΣ, ΣΗΜΑΤΟΔΟΤΗΣΗΣ – ΤΗΛΕΔΙΟΙΚΗΣΗΣ ΚΑΙ ETCS L1 ΣΤΗΝ ΥΦΙΣΤΑΜΕΝΗ ΜΟΝΗ ΣΙΔΗΡΟΔΡΟΜΙΚΗ ΓΡΑΜΜΗ ΠΑΛΑΙΟΦΑΡΣΑΛΟΣ – ΚΑΛΑΜΠΑΚΑ - Β' ΦΑΣΗ</t>
+        </is>
+      </c>
+      <c r="E14" s="34" t="inlineStr">
         <is>
           <t>Κεντρικό (Core)</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.
-(ΕΡΓΟΣΕ ΑΕ)</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.
+</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>Πρόγραμμα «ΜΕΤΑΦΟΡΕΣ» 2021-2027</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>52.201.427 € (Ποσό σύμβασης)</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>52.201.427,17 €</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="H14" s="46" t="inlineStr">
+        <is>
+          <t>60.870.881,70€ (Συγχρηματοδοτούμενη Δημόσια Δαπάνη)</t>
+        </is>
+      </c>
+      <c r="I14" s="52" t="inlineStr">
+        <is>
+          <t>52.201.427,17€ 
+(χωρίς ΦΠΑ)</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>ΑΒΑΞ Α.Ε.</t>
         </is>
       </c>
-      <c r="K14" s="8" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>24.11.2022</t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr">
+      <c r="L14" s="7" t="inlineStr">
         <is>
           <t>24.11.2027 (Αιτούμενη παράταση)</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
-        <is>
-          <t>Εγκατάσταση συστημάτων σε υφιστάμενη γραμμή &amp; κατασκευή νέας παρακαμπτήριας Σ.Σ. Σοφάδων</t>
-        </is>
-      </c>
-      <c r="N14" s="44" t="inlineStr">
-        <is>
-          <t>Η πράξη Παλαιοφάρσαλος–Καλαμπάκα έχει ενταχθεί σε καθεστώς phasing από το ΕΠ ΥΜΕΠΕΡΑΑ 2014–2020 και βρίσκεται σε προχωρημένο στάδιο υλοποίησης, με ποσοστό ολοκλήρωσης περίπου 27,31% στο κύριο συμβατικό αντικείμενο. Παράλληλα εξελίσσεται συμπληρωματική σύμβαση αποκατάστασης ζημιών από τις θεομηνίες, με σημαντική πρόοδο και υψηλότερη απορρόφηση ~98,8% . Σημαντικές καθυστερήσεις εξακολουθούν να καταγράφονται στις μετατοπίσεις δικτύων ΟΚΩ (ΔΕΔΔΗΕ) και στις ηλεκτρικές διασυνδέσεις με τον ΑΔΜΗΕ, που επηρεάζουν το συνολικό χρονοδιάγραμμα. Συνολικά, το έργο βρίσκεται σε φάση ενεργής κατασκευής με αυξημένη τεχνική και διαχειριστική πολυπλοκότητα.</t>
-        </is>
-      </c>
-      <c r="O14" s="41" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>Η πράξη αφορά στην υλοποίηση της Β΄ Φάσης του έργου με αντικείμενο την εγκατάσταση συστημάτων σηματοδότησης, ETCS και ηλεκτροκίνησης στην υφιστάμενη μονή γραμμή Παλαιοφαρσάλου - Καλαμπάκας (μήκους 80,4 χλμ), καθώς και την κατασκευή παρακαμπτηρίου γραμμής (μήκους 650μ) στο Σ.Σ. Σοφάδων.</t>
+        </is>
+      </c>
+      <c r="N14" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Η σύμβαση παρουσιάζει ποσοστό υλοποίησης περίπου 27,3%. 
+Παράλληλα υλοποιείται από την ΕΥΔΕ/ΚΣΣΥ σύμβαση αποκατάστασης ζημιών σε εντοπισμένα τμήματα της γραμμής, μετά τις θεομηνίες "Daniel" και "Elias", με ανάδοχο τον Ο.Φ. "ΑΒΑΞ Α.Ε.", συνολικό ποσό 55.295.940 € (με ΦΠΑ), διάρκεια 15 μηνών και ποσοστό οικονομικής απορρόφησης: ~98,8%.
+</t>
+        </is>
+      </c>
+      <c r="O14" s="34" t="inlineStr">
         <is>
           <t>Α.Σ.: 2514/2022</t>
         </is>
       </c>
-      <c r="P14" s="41" t="inlineStr">
+      <c r="P14" s="34" t="inlineStr">
         <is>
           <t>DANIEL &amp; ELIAS</t>
         </is>
       </c>
-      <c r="Q14" s="41" t="n"/>
-      <c r="R14" s="8" t="inlineStr">
-        <is>
-          <t>- (Υπό ένταξη/Phasing)</t>
-        </is>
-      </c>
-      <c r="S14" s="8" t="inlineStr">
+      <c r="Q14" s="34" t="n"/>
+      <c r="R14" s="7" t="n">
+        <v>6053306</v>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>Σε εξέλιξη</t>
         </is>
       </c>
-      <c r="T14" s="44" t="inlineStr">
+      <c r="T14" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">Η πράξη περιλαμβάνει την υλοποίηση του συνολικού έργου (Α΄ και Β΄ Φάση) που αφορά στην εγκατάσταση συστημάτων σηματοδότησης, ETCS και ηλεκτροκίνησης της υφιστάμενης μονής γραμμής Παλαιοφαρσάλου - Καλαμπάκας. Πιο συγκεκριμένα, με την ολοκλήρωση του συνολικού έργου (Α΄και Β΄ Φάσεις) θα παραδοθούν:
 - 80,4χλμ μονής σιδηροδρομικής γραμμής στα οποία θα έχει εγκατασταθεί σύστημα Ηλεκτροκίνησης, σύστημα Σηματοδότησης και σύστημα ETCS-Level 1.
@@ -2352,7 +2245,7 @@
                                                                                                                                                                                                        </t>
         </is>
       </c>
-      <c r="U14" s="44" t="inlineStr">
+      <c r="U14" s="37" t="inlineStr">
         <is>
           <t>- Προέγκριση παράτασης από Δ.Α.
 -  Έγκριση παράτασης της συνολικής προθεσμίας περαίωσης του έργου
@@ -2360,114 +2253,107 @@
 - Ανάθεση της κατασκευής της νέας διασυνδετήριας Γραμμής Μεταφοράς και της κατασκευής του Τμήματος Σύνδεσης του Yποσταθμού του ΟΣΕ με το Σύστημα μεταφοράς Ηλεκτρικής Ενέργειας της ΑΔΜΗΕ</t>
         </is>
       </c>
-      <c r="V14" s="53" t="n">
-        <v>60870881.7</v>
-      </c>
-      <c r="W14" s="53" t="n">
-        <v>56066935.58</v>
-      </c>
-      <c r="X14" s="53" t="n">
-        <v>12165505.3</v>
-      </c>
-      <c r="Y14" s="8" t="n"/>
-      <c r="Z14" s="8" t="n"/>
-      <c r="AA14" s="41" t="n"/>
-      <c r="AB14" s="8" t="n"/>
-      <c r="AC14" s="8" t="n"/>
-      <c r="AD14" s="41" t="n">
+      <c r="V14" s="50" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="W14" s="34" t="n">
         <v>39.61973531979313</v>
       </c>
-      <c r="AE14" s="41" t="n">
+      <c r="X14" s="34" t="n">
         <v>21.70577420544953</v>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1" s="35">
-      <c r="A15" s="9" t="n">
+    <row r="15" ht="60" customHeight="1" s="62">
+      <c r="A15" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>ΜΕΤΑΦΟΡΕΣ</t>
         </is>
       </c>
-      <c r="C15" s="42" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>ΛΑΡΙΣΑ - ΒΟΛΟΣ</t>
         </is>
       </c>
-      <c r="D15" s="46" t="inlineStr">
+      <c r="D15" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">ΗΛΕΚΤΡΟΚΙΝΗΣΗ, ΣΗΜΑΤΟΔΟΤΗΣΗ - ΤΗΛΕΔΙΟΙΚΗΣΗ, ΤΗΛΕΠΙΚΟΙΝΩΝΙΕΣ ΚΑΙ ETCS L1 ΣΤΗΝ ΥΦΙΣΤΑΜΕΝΗ ΜΟΝΗ ΣΙΔΗΡΟΔΡΟΜΙΚΗ ΓΡΑΜΜΗ ΛΑΡΙΣΑ - ΒΟΛΟΣ ΜΕ ΑΝΑΒΑΘΜΙΣΗ ΤΗΣ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΓΡΑΜΜΗΣ ΣΤΟ ΤΜΗΜΑ ΣΣ ΛΑΤΟΜΕΙΟΥ - ΒΙΠΕ - ΣΣ ΒΟΛΟΥ </t>
         </is>
       </c>
-      <c r="E15" s="43" t="inlineStr">
+      <c r="E15" s="36" t="inlineStr">
         <is>
           <t>Συνολικό (Comprehensive)</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε. 
-(ΕΡΓΟΣΕ ΑΕ)</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>Πρόγραμμα «ΜΕΤΑΦΟΡΕΣ» 2021-2027 (Προτεινόμενο ΤΠΑ)</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>63.540.100 € (Απαιτούμενο ποσό για ολοκλήρωση)</t>
-        </is>
-      </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>42.391.239,69 €</t>
-        </is>
-      </c>
-      <c r="J15" s="10" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.
+</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>Πρόγραμμα «ΜΕΤΑΦΟΡΕΣ» 2021-2027 (Μεταφερόμενο)</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Δεν έχει υποβληθεί αίτημα χρηματοδότησης </t>
+        </is>
+      </c>
+      <c r="I15" s="53" t="inlineStr">
+        <is>
+          <t>42.391.239,69 €
+(χωρίς Φ.Π.Α.)</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>INTRAKAT</t>
         </is>
       </c>
-      <c r="K15" s="10" t="inlineStr">
+      <c r="K15" s="9" t="inlineStr">
         <is>
           <t>04.05.2022</t>
         </is>
       </c>
-      <c r="L15" s="10" t="inlineStr">
-        <is>
-          <t>20.05.2028 (Αιτούμενη παράταση)</t>
-        </is>
-      </c>
-      <c r="M15" s="46" t="inlineStr">
-        <is>
-          <t>Το έργο αφορά α) στην εγκατάσταση συστημάτων Σηματοδότησης-Τηλεδιοίκησης, Ευρωπαϊκού Συστήματος Ελέγχου Τραίνων (ETCS L1) και Ηλεκτροκίνησης τύπου trolley στη μονή σιδηροδρομική γραμμή στο τμήμα "Λάρισα – Βόλος", μήκους 61,5 χλμ περίπου και β) στην αναβάθμιση της υφιστάμενης μονής μετρικής γραμμής σε κανονικού εύρους στο τμήμα" Σιδηροδρομικός Σταθμός Λατομείου - Βιομηχανική Περιοχή - Σιδηροδρομικός Σταθμός Βόλου".</t>
-        </is>
-      </c>
-      <c r="N15" s="46" t="inlineStr">
-        <is>
-          <t>Το έργο Λάρισα–Βόλος βρίσκεται σε ιδιαίτερα κρίσιμη φάση, καθώς έχει υποστεί ανατροπή χρηματοδότησης με ανάκληση της ένταξης από το ΕΠ ΥΜΕΠΕΡΑΑ λόγω σημαντικών καθυστερήσεων και ζημιών από τις θεομηνίες Daniel και Elias. Η κύρια εργολαβία παραμένει ουσιαστικά ανενεργή με πολύ χαμηλή πρόοδο (~3,82%) και σε καθεστώς εμπλοκής, ενώ παράλληλα υλοποιείται ξεχωριστή σύμβαση αποκατάστασης της γραμμής με σημαντικό ποσοστό απορρόφησης (~38,5%). Εκκρεμούν κρίσιμες αποφάσεις για τον υποσταθμό Ριζόμυλου, τις απαλλοτριώσεις και τη λύση σύνδεσης με το σύστημα ηλεκτροκίνησης, με εμπλοκή και του ΑΔΜΗΕ. Συνολικά, το έργο έχει μεταφερθεί σε νέα χρηματοδοτική περίοδο (ΤΠΑ 2026–2030) για να διασφαλιστεί η ολοκλήρωσή του.</t>
-        </is>
-      </c>
-      <c r="O15" s="43" t="inlineStr">
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>17.05.2028 (Εγκεκριμένη παράταση)</t>
+        </is>
+      </c>
+      <c r="M15" s="39" t="inlineStr">
+        <is>
+          <t>Η πράξη αφορά στην εγκατάσταση συστημάτων Σηματοδότησης-Τηλεδιοίκησης, ETCS L1 και Ηλεκτροκίνησης τύπου trolley στη μονή σιδηροδρομική γραμμή Λάρισα – Βόλος, μήκους 61,5χλμ περίπου, καθώς και στην αναβάθμιση της υφιστάμενης μονής μετρικής γραμμής σε κανονικού εύρους στο τμήμα Σ.Σ. Λατομείου - ΒΙ.ΠΕ. - Σ.Σ.Βόλου.</t>
+        </is>
+      </c>
+      <c r="N15" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Λόγω της κακοκαιρίας "DANIEL" έχουν σημειωθεί σοβαρές ζημιές τόσο στην υφιστάμενη γραμμή όσο και στις εργασίες της εν λόγω σύμβασης με αποτέλεσμα έως και σήμερα να μην πραγματοποιούνται εργασίες. Ποσοστό υλοποίησης: ~3,82%. 
+Παράλληλα, υλοποιείται από την ΕΥΔΕ/ΚΣΣΥ η από 28.04.2025 σύμβαση της αποκατάστασης της  σιδηροδρομικής γραμμής Λάρισας – Βόλου μετά τις θεομηνίες "Daniel" και "Elias", με ανάδοχο τον Ο.Φ. "ΆΚΤΩΡ ΑΤΕ", συνολικό ποσό 174.393.600,00 € (με ΦΠΑ), διάρκεια 15 μηνών και ποσοστό οικονομικής απορρόφησης: ~38,5% </t>
+        </is>
+      </c>
+      <c r="O15" s="36" t="inlineStr">
         <is>
           <t>Α.Σ.: 736/2022</t>
         </is>
       </c>
-      <c r="P15" s="43" t="inlineStr">
+      <c r="P15" s="36" t="inlineStr">
         <is>
           <t>DANIEL &amp; ELIAS</t>
         </is>
       </c>
-      <c r="Q15" s="43" t="n"/>
-      <c r="R15" s="10" t="n"/>
-      <c r="S15" s="10" t="n"/>
-      <c r="T15" s="46" t="inlineStr">
+      <c r="Q15" s="36" t="n"/>
+      <c r="R15" s="9" t="n"/>
+      <c r="S15" s="9" t="n"/>
+      <c r="T15" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">Μεταφερόμενο από το ΕΠ ΥΜΕΠΕΡΑΑ 2014-2020
-Αντικείμενο: Το έργο αφορά α) στην εγκατάσταση συστημάτων Σηματοδότησης-Τηλεδιοίκησης, Ευρωπαϊκού Συστήματος Ελέγχου Τραίνων (ETCS L1) και Ηλεκτροκίνησης τύπου trolley στη μονή σιδηροδρομική γραμμή στο τμήμα "Λάρισα – Βόλος", μήκους 61,5 χλμ περίπου και β) στην αναβάθμιση της υφιστάμενης μονής μετρικής γραμμής σε κανονικού εύρους στο τμήμα" Σιδηροδρομικός Σταθμός Λατομείου - Βιομηχανική Περιοχή - Σιδηροδρομικός Σταθμός Βόλου".
+Το έργο αφορά στην εγκατάσταση συστημάτων Σηματοδότησης-Τηλεδιοίκησης, ETCS L1 και Ηλεκτροκίνησης τύπου trolley στη μονή σιδηροδρομική γραμμή Λάρισα – Βόλος, μήκους 61,5χλμ περίπου, καθώς και στην αναβάθμιση της υφιστάμενης μονής μετρικής γραμμής σε κανονικού εύρους στο τμήμα Σ.Σ. Λατομείου - ΒΙ.ΠΕ. - Σ.Σ.Βόλου.
 Σύμβαση: "ΚΑΤΑΣΚΕΥΗ ΗΛΕΚΤΡΟΚΙΝΗΣΗΣ, ΣΗΜΑΤΟΔΟΤΗΣΗΣ - ΤΗΛΕΔΙΟΙΚΗΣΗΣ, ΤΗΛΕΠΙΚΟΙΝΩΝΙΩΝ ΚΑΙ ΣΥΣΤΗΜΑΤΟΣ ETCS L1 ΣΤΗΝ ΥΦΙΣΤΑΜΕΝΗ ΜΟΝΗ ΣΙΔΗΡΟΔΡΟΜΙΚΗ ΓΡΑΜΜΗ ΛΑΡΙΣΑ - ΒΟΛΟΣ ΜΕ ΑΝΑΒΑΘΜΙΣΗ ΤΗΣ ΣΙΔ/ΚΗΣ ΓΡΑΜΜΗΣ ΣΤΟ ΤΜΗΜΑ Σ.Σ. ΛΑΤΟΜΕΙΟΥ - ΒΙΠΕ ΒΟΛΟΣ" (Α.Σ.: 736/22)
 Ανάδοχος: INTRAKAT
 Ημερομηνία υπογραφής σύμβασης: 4/5/2022
@@ -2482,106 +2368,109 @@
 Στις 28.04.2026 εκδόθηκε η ΥΑ ένταξης του έργου στο ΤΠΑ ΥΠΥΜΕ 2026-2030 με συνολική επιλέξιμη δαπάνη 51.414.090,32€.   </t>
         </is>
       </c>
-      <c r="U15" s="10" t="n"/>
-      <c r="V15" s="10" t="n"/>
-      <c r="W15" s="10" t="n"/>
-      <c r="X15" s="10" t="n"/>
-      <c r="Y15" s="10" t="n"/>
-      <c r="Z15" s="10" t="n"/>
-      <c r="AA15" s="43" t="n"/>
-      <c r="AB15" s="10" t="n"/>
-      <c r="AC15" s="10" t="n"/>
-      <c r="AD15" s="43" t="n">
+      <c r="U15" s="9" t="n"/>
+      <c r="V15" s="49" t="n"/>
+      <c r="W15" s="36" t="n">
         <v>39.55180497462751</v>
       </c>
-      <c r="AE15" s="43" t="n">
+      <c r="X15" s="36" t="n">
         <v>22.60732981752406</v>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1" s="35">
+    <row r="16" ht="60" customHeight="1" s="62">
       <c r="A16" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>ΜΕΤΑΦΟΡΕΣ</t>
         </is>
       </c>
-      <c r="C16" s="40" t="inlineStr">
-        <is>
-          <t>Κιάτο-Ροδοδάφνη</t>
-        </is>
-      </c>
-      <c r="D16" s="44" t="inlineStr">
+      <c r="C16" s="51" t="inlineStr">
+        <is>
+          <t>ΚΙΑΤΟ - ΡΟΔΟΔΑΦΝΗ</t>
+        </is>
+      </c>
+      <c r="D16" s="37" t="inlineStr">
         <is>
           <t>ΗΛΕΚΤΡΟΚΙΝΗΣΗ ΝΕΑΣ ΔΙΠΛΗΣ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΓΡΑΜΜΗΣ ΣΤΟ ΤΜΗΜΑ ΚΙΑΤΟ-ΡΟΔΟΔΑΦΝΗ – Β΄ΦΑΣΗ</t>
         </is>
       </c>
-      <c r="E16" s="41" t="inlineStr">
+      <c r="E16" s="34" t="inlineStr">
         <is>
           <t>Κεντρικό (Core)</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.
-(ΕΡΓΟΣΕ ΑΕ)</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.
+</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>Πρόγραμμα «ΜΕΤΑΦΟΡΕΣ» 2021-2027 (Phasing)</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>59.114.503,51 € (Συγχρηματοδοτούμενη δαπάνη)</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>55.366.115,92 €</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>59.114.503,51 € (Συγχρηματοδοτούμενη Δημόσια Δαπάνη)</t>
+        </is>
+      </c>
+      <c r="I16" s="52" t="inlineStr">
+        <is>
+          <t>55.366.115,92 €
+(χωρίς Φ.Π.Α.)</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>Κ/Ξ ΤΕΡΝΑ Α.Ε. - ΜΕΤΚΑ Α.Τ.Ε.</t>
         </is>
       </c>
-      <c r="K16" s="8" t="inlineStr">
+      <c r="K16" s="7" t="inlineStr">
         <is>
           <t>06.07.2022</t>
         </is>
       </c>
-      <c r="L16" s="8" t="inlineStr">
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>28.12.2026</t>
         </is>
       </c>
-      <c r="M16" s="8" t="inlineStr">
-        <is>
-          <t>Ηλεκτροκίνηση 70,6χλμ, αντιθορυβικά ηχοπετάσματα, περιβαλλοντική αποκατάσταση Υ/Σ</t>
-        </is>
-      </c>
-      <c r="N16" s="44" t="inlineStr">
-        <is>
-          <t>Το έργο Κιάτο–Ροδοδάφνη έχει ενταχθεί σε καθεστώς phasing από το ΕΠ ΥΜΕΠΕΡΑΑ 2014–2020 και βρίσκεται σε προχωρημένο στάδιο υλοποίησης, με ποσοστό ολοκλήρωσης περίπου 74,13%. Η κύρια σύμβαση για ηλεκτροκίνηση και ηχοπετάσματα εξελίσσεται κανονικά, με σημαντική πρόοδο και επικαιροποιημένο χρονοδιάγραμμα ολοκλήρωσης έως το 2026. Παράλληλα έχουν ενεργοποιηθεί κρίσιμες διαδικασίες για τη σύνδεση των υποσταθμών Ξυλοκάστρου και Αιγίου με το σύστημα ΑΔΜΗΕ μέσω νέων διασυνδετήριων γραμμών. Συνολικά, το έργο βρίσκεται σε φάση προχωρημένης κατασκευής με υψηλή τεχνική ωριμότητα και περιορισμένες πλέον κρίσιμες εκκρεμότητες.</t>
-        </is>
-      </c>
-      <c r="O16" s="41" t="n"/>
-      <c r="P16" s="41" t="n"/>
-      <c r="Q16" s="41" t="n"/>
-      <c r="R16" s="8" t="n">
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>Η πράξη αφορά στην υλοποίηση της Β΄ Φάσης του έργου με αντικείμενο την ηλεκτροκίνηση του τμήματος Κιάτο – Ροδοδάφνη της Νέας Διπλής Σιδηροδρομικής Γραμμής Υψηλών Ταχυτήτων (ΝΔΣΓΥΤ) του σιδηροδρομικού δικτύου Πειραιάς – Αθήνα – Κιάτο – Πάτρα</t>
+        </is>
+      </c>
+      <c r="N16" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Η σύμβαση για την ηλεκτροκίνηση του τμήματος Κιάτο–Ροδοδάφνη παρουσιάζει ποσοστό υλοποίησης περίπου 74,1%. </t>
+        </is>
+      </c>
+      <c r="O16" s="34" t="n"/>
+      <c r="P16" s="34" t="n"/>
+      <c r="Q16" s="34" t="n"/>
+      <c r="R16" s="7" t="n">
         <v>6050820</v>
       </c>
-      <c r="S16" s="8" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>Σε εξέλιξη</t>
         </is>
       </c>
-      <c r="T16" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Phasing από το ΕΠ ΥΜΕΠΕΡΑΑ 2014-2020 (Συγχρηματοδοτούμενη Δημόσια Δαπάνη της Α΄ Φάσης της πράξης 13.644.744,82 €, σύμφωνα με την από 23.01.2026 απόφαση ολοκλήρωσης της Α΄ Φάσης της πράξης)        
+      <c r="T16" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Η πράξη αφορά στην ηλεκτροκίνηση του τμήματος ΚΙΑΤΟ – ΡΟΔΟΔΑΦΝΗ της Νέας Διπλής Σιδηροδρομικής Γραμμής Υψηλών Ταχυτήτων (ΝΔΣΓΥΤ) του σιδηροδρομικού δικτύου Πειραιάς – Αθήνα – Κιάτο – Πάτρα
+Η πράξη αφορά στην Β' φάση του έργου και περιλαμβάνει τις κάτωθι εργασίες:
+Υποέργο 1: Oι εργασίες και τα υλικά που θα πιστοποιηθούν μετά τον 11ο λογαριασμό και αντιστοιχούν στο 80,49% του οικονομικού αντικειμένου της σύμβασης κατασκευής
+Υποέργο 2 &amp; Υποέργο 7: Το 100% του οικονομικού αντικειμένου των υπηρεσιών ΑΔΜΗΕ (έλεγχος μελετών, επίβλεψη, προμήθεια κλπ) των Υ/Σ στην περιοχή του Ξυλοκάστρου και του Αιγίου με το δίκτυο μεταφοράς ενέργειας
+Υποέργο 3: Το οικονομικό αντικείμενο των απαιτούμενων απαλλοτριώσεων της Β’ Φάσης, το οποίο αφορά σε τυχόν επιπλέον δαπάνη αποζημίωσης μετά την αναμενόμενη Απόφαση Εφετείου για προσδιορισμό οριστικής τιμής μονάδος για την απαλλοτρίωση του υποσταθμού έλξης Αιγίου.
+Υποέργο 4: Το οικονομικό αντικείμενο των απαιτούμενων μετατοπίσεων/ υπερυψώσεων /αναβαθμίσεων και νέων συνδέσεων δικτύων ΟΚΩ της Β’ Φάσης, ήτοι από 29/03/24 και μετά.
+Υποέργο 5: Το 100% του φυσικού και οικονομικού αντικειμένου των Αρχαιολογικών εργασιών και ερευνών στην περιοχή της Κορινθίας
+Υποέργο 6: Το 100% του φυσικού και οικονομικού αντικειμένου των Αρχαιολογικών εργασιών και ερευνών στην περιοχή της Αχαΐας
+Οι εργασίες για την κατασκευή της εναέριας ΓΜ οι οποίες είναι απαραίτητες για την εξασφάλιση λειτουργικότητας της πράξης, καθώς και οι υπηρεσίες του ΑΔΜΗΕ για τις εργασίες αυτές, δεν περιλαμβάνονται στο φυσικό αντικείμενο των Υ/Ε 2 και 7. Οι εργασίες θα υλοποιηθούν με διαφορετική σύμβαση κατασκευής και το κόστος αυτών καθώς και των υπηρεσιών του ΑΔΜΗΕ θα καλυφθεί από τον τακτικό προϋπολογισμό του Δικαιούχου. Αντίστοιχα, το κόστος των απαλλοτριώσεων για τη ΓΜ, δεν περιλαμβάνεται στο φυσικό αντικείμενο του Υ/Ε 3 και θα καλυφθεί από τον Τακτικό Π/Υ του Δικαιούχου.
+Phasing από το ΕΠ ΥΜΕΠΕΡΑΑ 2014-2020 (Συγχρηματοδοτούμενη Δημόσια Δαπάνη της Α΄ Φάσης της πράξης 13.644.744,82 €, σύμφωνα με την από 23.01.2026 απόφαση ολοκλήρωσης της Α΄ Φάσης της πράξης)        
 Σύμβαση: "ΚΑΤΑΣΚΕΥΗ ΣΥΣΤΗΜΑΤΟΣ ΗΛΕΚΤΡΟΚΙΝΗΣΗΣ ΚΑΙ ΑΝΤΙΘΟΡΥΒΙΚΩΝ ΗΧΟΠΕΤΑΣΜΑΤΩΝ ΣΤΟ ΤΜΗΜΑ ΚΙΑΤΟ - ΡΟΔΟΔΑΦΝΗ" (Α.Σ.: 1511/22)
 Ανάδοχος: Κ/Ξ ΤΕΡΝΑ Α.Ε. - ΜΕΤΚΑ Α.Τ.Ε.
 Ημερομηνία υπογραφής σύμβασης: 6/7/2022
@@ -2599,124 +2488,107 @@
 Στις 10.06.2026 εκδόθηκε η Απόφαση ανάληψης υποχρέωσης ποσού  € 4.990.000,00 (χωρίς ΦΠΑ)  για την πληρωμή ισόποσης δαπάνης σε βάρος της πίστωσης του Τακτικού προϋπολογισμού εξόδων της Σ.Ε. Μ.Α.Ε. οικονομικού έτους 2026 για την κατασκευή των διασυνδετήριων Γραμμών Μεταφοράς των Υ/Σ Έλξης Ξυλοκάστρου και Αιγίου.                                                                                                                                                                                  </t>
         </is>
       </c>
-      <c r="U16" s="54" t="inlineStr">
+      <c r="U16" s="45" t="inlineStr">
         <is>
           <t>Ανάθεση της κατασκευής των διασυνδετήριων Γραμμών Μεταφοράς των Υ/Σ Έλξης</t>
         </is>
       </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>59.114.503,51 €</t>
-        </is>
-      </c>
-      <c r="W16" s="53" t="n">
-        <v>56132357.51</v>
-      </c>
-      <c r="X16" s="53" t="n">
-        <v>32787953.42</v>
-      </c>
-      <c r="Y16" s="8" t="inlineStr">
+      <c r="V16" s="48" t="inlineStr">
         <is>
           <t>22.12.2025</t>
         </is>
       </c>
-      <c r="Z16" s="8" t="n"/>
-      <c r="AA16" s="41" t="n"/>
-      <c r="AB16" s="8" t="n"/>
-      <c r="AC16" s="8" t="n"/>
-      <c r="AD16" s="41" t="n">
+      <c r="W16" s="34" t="n">
         <v>38.11046337537685</v>
       </c>
-      <c r="AE16" s="41" t="n">
+      <c r="X16" s="34" t="n">
         <v>22.52442504372862</v>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1" s="35">
-      <c r="A17" s="9" t="n">
+    <row r="17" ht="60" customHeight="1" s="62">
+      <c r="A17" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>ΜΕΤΑΦΟΡΕΣ</t>
         </is>
       </c>
-      <c r="C17" s="51" t="inlineStr">
-        <is>
-          <t>Ροδοδάφνη-Ρίο</t>
-        </is>
-      </c>
-      <c r="D17" s="46" t="inlineStr">
+      <c r="C17" s="44" t="inlineStr">
+        <is>
+          <t>ΡΟΔΟΔΑΦΝΗ - ΡΙΟ</t>
+        </is>
+      </c>
+      <c r="D17" s="39" t="inlineStr">
         <is>
           <t>ΟΛΟΚΛΗΡΩΣΗ ΤΗΣ ΝΕΑΣ ΔΙΠΛΗΣ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΓΡΑΜΜΗΣ ΣΤΟ ΤΜΗΜΑ ΡΟΔΟΔΑΦΝΗ ΕΩΣ ΡΙΟ – Β΄ΦΑΣΗ</t>
         </is>
       </c>
-      <c r="E17" s="43" t="inlineStr">
+      <c r="E17" s="36" t="inlineStr">
         <is>
           <t>Κεντρικό (Core)</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε. 
-(ΕΡΓΟΣΕ ΑΕ)</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.
+</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>Πρόγραμμα «ΜΕΤΑΦΟΡΕΣ» 2021-2027</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>Πρόγραμμα «ΜΕΤΑΦΟΡΕΣ» 2021-2027 (Phasing)</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>59.114.503,51 € (Δημόσια δαπάνη ένταξης)</t>
-        </is>
-      </c>
-      <c r="J17" s="10" t="inlineStr">
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Δεν έχει υποβληθεί αίτημα χρηματοδότησης </t>
+        </is>
+      </c>
+      <c r="I17" s="53" t="inlineStr">
+        <is>
+          <t>129.533.055,57 €
+(χωρίς Φ.Π.Α.)</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>Κ/Ξ ΤΕΡΝΑ Α.Ε. – ΜΕΤΚΑ Α.Τ.Ε.</t>
         </is>
       </c>
-      <c r="K17" s="10" t="inlineStr">
+      <c r="K17" s="9" t="inlineStr">
         <is>
           <t>22.11.2022</t>
         </is>
       </c>
-      <c r="L17" s="10" t="inlineStr">
-        <is>
-          <t>01.12.2026</t>
-        </is>
-      </c>
-      <c r="M17" s="10" t="inlineStr">
-        <is>
-          <t>Επιδομή, ηλεκτροκίνηση, σηματοδότηση, τηλεδιοίκηση, Σ.Σ. &amp; Η/Μ σήραγγας Παναγοπούλας</t>
-        </is>
-      </c>
-      <c r="N17" s="46" t="inlineStr">
-        <is>
-          <t>Το έργο Ροδοδάφνη–Ρίο (Κιάτο–Πάτρα) βρίσκεται σε προχωρημένο στάδιο υλοποίησης με ποσοστό ολοκλήρωσης περίπου 51,43% και χρηματοδοτείται μέσω phasing από το ΕΠ ΥΜΕΠΕΡΑΑ 2014–2020. Η κύρια σύμβαση εξελίσσεται κανονικά, αλλά έχει προκύψει ανασχεδιασμός με αποκοπή του τμήματος Αραχωβίτικα–Ρίο και προγραμματισμό νέας εργολαβίας για την ολοκλήρωσή του. Παράλληλα βρίσκονται σε εξέλιξη οι διοικητικές διαδικασίες έγκρισης του 2ου ΑΠΕ και προετοιμασίας των νέων τευχών δημοπράτησης. Συνολικά, το έργο παραμένει σε φάση ενεργής κατασκευής με κρίσιμη μεταβατική φάση αναδιάρθρωσης του αντικειμένου.</t>
-        </is>
-      </c>
-      <c r="O17" s="43" t="n"/>
-      <c r="P17" s="43" t="n"/>
-      <c r="Q17" s="43" t="n"/>
-      <c r="R17" s="10" t="inlineStr">
-        <is>
-          <t>Phasing από το ΕΠ ΥΜΕΠΕΡΑΑ 2014-2020</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>01.12.2026 (Εγκεκριμένη παράταση)</t>
+        </is>
+      </c>
+      <c r="M17" s="53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Η πράξη αφορά στην ολοκλήρωση του τμήματος από την είσοδο του ΣΣ Ροδοδάφνης (Χ.Θ. 193+950) έως την περιοχή μετά το cover &amp; cut του Ρίου (Χ.Θ. 222+750), μήκους 28,8 χλμ της νέας σιδηροδρομικής γραμμής Κιάτο – Πάτρα. Οι εργασίες αφορούν στην επιδομή, την ηλεκτροκίνηση, την σηματοδότηση / ETCS καθώς και τους σταθμούς και στάσεις του εν λόγω τμήματος. </t>
+        </is>
+      </c>
+      <c r="N17" s="39" t="inlineStr">
+        <is>
+          <t>Η εργολαβία ολοκλήρωσης του τμήματος Ροδοδάφνη–Ρίο παρουσιάζει ποσοστό υλοποίησης περίπου 51,4%. Οι εργασίες προγραμματιζόταν να εκτελεστούν επί ήδη κατασκευασμένης υποδομής στο πλαίσιο προηγούμενων εργολαβιών. Η εργολαβία Α.Σ. 716 διαλύθηκε τον Σεπτέμβριο 2023 με συνέπεια η υποδομή να έχει μείνει ημιτελής στο τμήμα Αραχωβίτικα - Ρίο, μήκους ~7χλμ. Δρομολογείται η αποκοπή των εργασιών του τμήματος Αραχωβίτικα - Ρίο (π/ΰ~ 20εκ.€) από τη σύμβαση (2ος ΑΠΕ) και η επαναδημοπράτηση του συνολικού φυσικού αντικειμένου του εν λόγω τμήματος (υπολειπόμενες εργασίες υποδομής, επιδομή, Σ.Σ., ηλεκτροκίνηση, σηματοδότηση) ως ξεχωριστή σύμβαση.</t>
+        </is>
+      </c>
+      <c r="O17" s="36" t="n"/>
+      <c r="P17" s="36" t="n"/>
+      <c r="Q17" s="36" t="n"/>
+      <c r="R17" s="9" t="n"/>
+      <c r="S17" s="9" t="inlineStr">
         <is>
           <t>Σε εξέλιξη</t>
         </is>
       </c>
-      <c r="T17" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Phasing από το ΕΠ ΥΜΕΠΕΡΑΑ 2014-2020 (Συγχρηματοδοτούμενη Δημόσια Δαπάνη της Α΄ Φάσης της πράξης 11.416.093,51 €, σύμφωνα με την από 10.02.2026 απόφαση ολοκλήρωσης της Α΄ Φάσης της πράξης)        
+      <c r="T17" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Στο φυσικό αντικείμενο του έργου περιλαμβάνονται εργασίες για την ολοκλήρωση του τμήματος από την είσοδο του ΣΣ Ροδοδάφνης (Χ.Θ. 193+950) έως την περιοχή μετά το cover &amp; cut του Ρίου (Χ.Θ. 222+750), μήκους 28,8 χλμ, της νέας σιδηροδρομικής γραμμής Κιάτο – Πάτρα. Οι εργασίες αφορούν την επιδομή, την ηλεκτροκίνηση, την σηματοδότηση / ETCS καθώς και τους σταθμούς και στάσεις του τμήματος. Οι εργασίες αυτές προγραμματιζόταν να εκτελεστούν επί ήδη κατασκευασμένης υποδομής στο πλαίσιο προηγούμενων εργολαβιών, πλην μικρού τμήματος στην περιοχή της στάσης Αγ. Βασιλείου που θα κατασκευαστεί στο πλαίσιο του έργου και του τμήματος Ψαθόπυργου - Ρίου, μήκους ~7χλμ, όπου η υποδομή έχει μείνει ημιτελής λόγω διάλυσης της σύμβασης με την οποία υλοποιείτο (Α.Σ. 716) τον Σεπ 2023.
+Phasing από το ΕΠ ΥΜΕΠΕΡΑΑ 2014-2020 (Συγχρηματοδοτούμενη Δημόσια Δαπάνη της Α΄ Φάσης της πράξης 11.416.093,51 €, σύμφωνα με την από 10.02.2026 απόφαση ολοκλήρωσης της Α΄ Φάσης της πράξης)        
 Σύμβαση: "ΚΑΤΑΣΚΕΥΗ ΣΙΔΗΡΟΔΡΟΜΙΚΩΝ ΣΤΑΘΜΩΝ ΚΑΙ ΣΤΑΣΕΩΝ (ΚΤΙΡΙΑ, ΑΠΟΒΑΘΡΕΣ, ΣΤΕΓΑΣΤΡΑ ΚΑΙ ΠΕΡΙΒΑΛΛΩΝ ΧΩΡΟΣ), ΕΠΙΔΟΜΗΣ, ΗΛΕΚΤΡΟΚΙΝΗΣΗΣ, ΣΗΜΑΤΟΔΟΤΗΣΗΣ – ΤΗΛΕΔΙΟΙΚΗΣΗΣ, ETCS, ΤΗΛΕΠΙΚΟΙΝΩΝΙΩΝ ΚΑΙ Η/Μ ΕΓΚΑΤΑΣΤΑΣΕΩΝ ΣΗΡΑΓΓΑΣ ΠΑΝΑΓΟΠΟΥΛΑΣ ΓΙΑ ΤΗ Ν.Σ.Γ. ΚΙΑΤΟ – ΠΑΤΡΑ ΣΤΟ ΤΜΗΜΑ ΡΟΔΟΔΑΦΝΗ – ΡΙΟ»" (Α.Σ.: 1510/2022)
 Ανάδοχος:  Κ/Ξ ΤΕΡΝΑ Α.Ε. – ΜΕΤΚΑ Α.Τ.Ε.
 Ημερομηνία υπογραφής σύμβασης:  22/11/2022
@@ -2729,7 +2601,7 @@
 Μετά την προέγκριση του 2ου ΑΠΕ από τη Δ.Α. και την έγκρισή του από το Δ.Σ. της ΣΕΜΑΕ πρέπει να συνταχθούν τα τεύχη δημοπράτησης της νέας εργολαβίας, να προεγκριθούν από τη Διαχειριστική Αρχή και να προκηρυχθεί ο διαγωνισμός. Ο χρόνος υλοποίησης της νέας εργολαβίας θα οριστεί σε 14 μήνες.                                                                                                                                                                               </t>
         </is>
       </c>
-      <c r="U17" s="46" t="inlineStr">
+      <c r="U17" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">- Προέγκριση 2ου ΑΠΕ από Δ.Α.
 - Έγκριση 2ου ΑΠΕ 
@@ -2737,107 +2609,97 @@
 - Δημοπράτηση νέας εργολαβίας κατασκευής του τμήματος Αραχωβίτικα – Ρίο (υπολειπόμενες εργασίες υποδομής, επιδομή, Σ.Σ., ηλεκτροκίνηση, σηματοδότηση) </t>
         </is>
       </c>
-      <c r="V17" s="10" t="n"/>
-      <c r="W17" s="10" t="n"/>
-      <c r="X17" s="10" t="n"/>
-      <c r="Y17" s="10" t="n"/>
-      <c r="Z17" s="10" t="n"/>
-      <c r="AA17" s="43" t="n"/>
-      <c r="AB17" s="10" t="n"/>
-      <c r="AC17" s="10" t="n"/>
-      <c r="AD17" s="43" t="n">
+      <c r="V17" s="49" t="n"/>
+      <c r="W17" s="36" t="n">
         <v>38.31421419408351</v>
       </c>
-      <c r="AE17" s="43" t="n">
+      <c r="X17" s="36" t="n">
         <v>21.98132827943259</v>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1" s="35">
+    <row r="18" ht="60" customHeight="1" s="62">
       <c r="A18" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>ΜΕΤΑΦΟΡΕΣ</t>
         </is>
       </c>
-      <c r="C18" s="40" t="inlineStr">
-        <is>
-          <t>ΣΣ Κρυονέρι</t>
-        </is>
-      </c>
-      <c r="D18" s="44" t="inlineStr">
+      <c r="C18" s="51" t="inlineStr">
+        <is>
+          <t>ΣΣ ΚΡΥΟΝΕΡΙ</t>
+        </is>
+      </c>
+      <c r="D18" s="37" t="inlineStr">
         <is>
           <t>ΚΑΤΑΣΚΕΥΗ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΣΤΑΣΗΣ ΣΤΟ ΚΡΥΟΝΕΡΙ ΑΤΤΙΚΗΣ</t>
         </is>
       </c>
-      <c r="E18" s="41" t="inlineStr">
+      <c r="E18" s="34" t="inlineStr">
         <is>
           <t>Κεντρικό (Core)</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.
-(ΕΡΓΟΣΕ ΑΕ)</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΟΣ Μ.Α.Ε.
+</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>Πρόγραμμα «ΜΕΤΑΦΟΡΕΣ» 2021-2027</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>- (Απαιτείται νέα απόφαση ένταξης)</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>5.804.254,88 €</t>
-        </is>
-      </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Δεν έχει υποβληθεί αίτημα χρηματοδότησης </t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>5.804.254,88 € (χωρίς Φ.Π.Α.)</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>ΑΒΑΞ Α.Ε.</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="K18" s="7" t="inlineStr">
         <is>
           <t>15.12.2023</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
-      <c r="M18" s="8" t="inlineStr">
-        <is>
-          <t>Κατασκευή νέας προαστιακής στάσης, αποβάθρες, αντιστήριξη &amp; επιδομή</t>
-        </is>
-      </c>
-      <c r="N18" s="44" t="inlineStr">
-        <is>
-          <t>Η κατασκευή της Σιδηροδρομικής Στάσης Κρυονερίου Αττικής βρίσκεται σε αρχικό–μέσο στάδιο υλοποίησης, με πρόοδο περίπου 12,52% και εργασίες ήδη σε εξέλιξη στην αποβάθρα και στην επιδομή της γραμμής. Το έργο έχει μεταφερθεί από το ΕΠ ΥΜΕΠΕΡΑΑ 2014–2020 και χαρακτηρίζεται ως «εν δυνάμει μεταφερόμενο» στο νέο Πρόγραμμα Μεταφορών 2021–2027. Παρά την τεχνική πρόοδο σε επιμέρους εργασίες, η χρηματοδοτική συνέχεια δεν έχει ακόμη οριστικοποιηθεί και εκκρεμεί η ολοκλήρωση της ΑΚΟ για την ένταξη στο νέο πρόγραμμα. Συνολικά, το έργο βρίσκεται σε φάση ενεργής κατασκευής με διοικητική εκκρεμότητα χρηματοδότησης.</t>
-        </is>
-      </c>
-      <c r="O18" s="41" t="n"/>
-      <c r="P18" s="41" t="n"/>
-      <c r="Q18" s="41" t="n"/>
-      <c r="R18" s="8" t="inlineStr">
-        <is>
-          <t>Μεταφερόμενο από το ΕΠ ΥΜΕΠΕΡΑΑ 2014-2020</t>
-        </is>
-      </c>
-      <c r="S18" s="8" t="inlineStr">
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>12.10.2026 (Εγκεκριμένη παράταση)</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>Η Πράξη αφορά στις εργασίες για την κατασκευή της νέας Σιδηροδρομικής Στάσης Κρυονερίου Αττικής, που αναπτύσσεται μεταξύ των Σιδηροδρομικών Σταθμών (Σ.Σ.) Δεκελείας και Αγίου Στεφάνου, από τη Χ.Θ. 30+075 έως τη Χ.Θ. 30+225 της Σιδηροδρομικής Γραμμής (Σ.Γ.) Πειραιά – Αθήνας – Θεσσαλονίκης – Ειδομένης.</t>
+        </is>
+      </c>
+      <c r="N18" s="37" t="inlineStr">
+        <is>
+          <t>Η εργολαβία παρουσιάζει ποσοστό υλοποίησης περίπου 12,5%.</t>
+        </is>
+      </c>
+      <c r="O18" s="34" t="n"/>
+      <c r="P18" s="34" t="n"/>
+      <c r="Q18" s="34" t="n"/>
+      <c r="R18" s="7" t="n"/>
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>Σε εξέλιξη</t>
         </is>
       </c>
-      <c r="T18" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Μεταφερόμενο από το ΕΠ ΥΜΕΠΕΡΑΑ 2014-2020  
+      <c r="T18" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Η Πράξη αφορά στις εργασίες για την κατασκευή της νέας Σιδηροδρομικής Στάσης Κρυονερίου Αττικής, που αναπτύσσεται μεταξύ των Σιδηροδρομικών Σταθμών (Σ.Σ.) Δεκελείας και Αγίου Στεφάνου, από τη Χ.Θ. 30+075 έως τη Χ.Θ. 30+225 της Σιδηροδρομικής Γραμμής (Σ.Γ.) Πειραιά – Αθήνας – Θεσσαλονίκης – Ειδομένης.
+Μεταφερόμενο από το ΕΠ ΥΜΕΠΕΡΑΑ 2014-2020  
 Σύμβαση: "ΚΑΤΑΣΚΕΥΗ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΣΤΑΣΗΣ ΣΤΟ ΚΡΥΟΝΕΡΙ ΑΤΤΙΚΗΣ" (Α.Σ.: 2512/2023) 
 Ανάδοχος: ΑΒΑΞ Α.Ε.
 Ημερομηνία υπογραφής σύμβασης: 15/12/2023
@@ -2849,124 +2711,122 @@
 Εκκρεμεί η ολοκλήρωση της ΑΚΟ προκειμένου να είναι δυνατή η υποβολή αιτήματος χρηματοδότησης από το Πρόγραμμα "ΜΕΤΑΦΟΡΕΣ" 2021-2027                                                                                                                                                                                                                      </t>
         </is>
       </c>
-      <c r="U18" s="48" t="inlineStr">
+      <c r="U18" s="41" t="inlineStr">
         <is>
           <t>- Ολοκλήρωση ΑΚΟ
 - Υποβολή αιτήματος χρηματοδότησης από το Πρόγραμμα "ΜΕΤΑΦΟΡΕΣ" 2021-2027</t>
         </is>
       </c>
-      <c r="V18" s="8" t="n"/>
-      <c r="W18" s="8" t="n"/>
-      <c r="X18" s="8" t="n"/>
-      <c r="Y18" s="8" t="n"/>
-      <c r="Z18" s="8" t="n"/>
-      <c r="AA18" s="41" t="n"/>
-      <c r="AB18" s="8" t="n"/>
-      <c r="AC18" s="8" t="n"/>
-      <c r="AD18" s="41" t="n">
+      <c r="V18" s="48" t="n"/>
+      <c r="W18" s="34" t="n">
         <v>38.13134439444153</v>
       </c>
-      <c r="AE18" s="41" t="n">
+      <c r="X18" s="34" t="n">
         <v>23.84422214253571</v>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1" s="35">
-      <c r="A19" s="9" t="n">
+    <row r="19" ht="60" customHeight="1" s="62">
+      <c r="A19" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>CEF 14 20</t>
-        </is>
-      </c>
-      <c r="C19" s="42" t="inlineStr">
-        <is>
-          <t>ΣΣΑ – Τρεις Γέφυρες</t>
-        </is>
-      </c>
-      <c r="D19" s="46" t="inlineStr">
+      <c r="B19" s="55" t="inlineStr">
+        <is>
+          <t>CEF 2014-2020</t>
+        </is>
+      </c>
+      <c r="C19" s="60" t="inlineStr">
+        <is>
+          <t>ΣΣΑ – ΤΡΕΙΣ ΓΕΦΥΡΕΣ</t>
+        </is>
+      </c>
+      <c r="D19" s="39" t="inlineStr">
         <is>
           <t>ΚΑΤΑΣΚΕΥΗ ΤΕΤΡΑΠΛΟΥ ΣΙΔΗΡΟΔΡΟΜΙΚΟΥ ΔΙΑΔΡΟΜΟΥ ΣΤΟ ΤΜΗΜΑ ΕΞΟΔΟΣ Σ.Σ. ΑΘΗΝΩΝ–ΤΡΕΙΣ ΓΕΦΥΡΕΣ, ΜΕ ΥΠΟΓΕΙΟΠΟΙΗΣΗ ΣΤΗΝ ΠΕΡΙΟΧΗ ΣΕΠΟΛΙΩΝ</t>
         </is>
       </c>
-      <c r="E19" s="43" t="inlineStr">
+      <c r="E19" s="36" t="inlineStr">
         <is>
           <t>Κεντρικό</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΑΣ Μ.Α.Ε.
 (ΕΡΓΟΣΕ ΑΕ)</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>CEF 2014-2020</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>56.278.931,00 € (Συγχρηματοδοτούμενη δαπάνη)</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>99.844.041,18 € (Αθροιστικά συμβάσεις 2507, 2507-1, 2507-2)</t>
-        </is>
-      </c>
-      <c r="J19" s="10" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57.667.104,04 € (Συγχρηματοδοτούμενη Δημόσια Δαπάνη)
+(Ημερ. Έναρξης GA: 16.05.2017
+Ημερ. Ολοκλ. GA: 31.12.2024)  
+</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>99.844.041,18 € (Αρχική Σύμβαση και δυο Σ.Σ.Ε.)</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>Κ/Ξ ΙΝΤΡΑΚΑΤ - ΣΙΔΗΡΟΔΡΟΜΙΚΑ ΕΡΓΑ ΑΤΕ</t>
         </is>
       </c>
-      <c r="K19" s="10" t="inlineStr">
-        <is>
-          <t>15.11.2018 (Αρχική)</t>
-        </is>
-      </c>
-      <c r="L19" s="10" t="inlineStr">
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>15.11.2018</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
         <is>
           <t>06.02.2028</t>
         </is>
       </c>
-      <c r="M19" s="10" t="inlineStr">
-        <is>
-          <t>Τετραπλός διάδρομος 2,36χλμ, υπογειοποίηση 1,33χλμ, διαχωρισμός προαστιακής/υπεραστικής κίνησης</t>
-        </is>
-      </c>
-      <c r="N19" s="10" t="inlineStr">
-        <is>
-          <t>Το έργο του τετραπλού σιδηροδρομικού διαδρόμου Σεπολίων–Τρεις Γέφυρες βρίσκεται σε προχωρημένη φάση υλοποίησης με συνολική πρόοδο περίπου 35,7% στο κύριο αντικείμενο και υψηλότερη πρόοδο στα συμπληρωματικά υποέργα. Πρόκειται για ιδιαίτερα σύνθετο τεχνικά έργο υπογειοποίησης, με σημαντικές τεχνικές προκλήσεις λόγω διασταύρωσης με το Μετρό και εκτεταμένων μετατοπίσεων δικτύων ΟΚΩ και αρχαιολογικών εργασιών. Η διάρκεια υλοποίησης έχει ήδη παραταθεί έως το 2028, ενώ συνεχίζονται κρίσιμες τεχνικές αξιολογήσεις για τη λύση στη ζώνη διασταύρωσης με τη σήραγγα του Μετρό. Συνολικά, το έργο βρίσκεται σε φάση ενεργής κατασκευής με υψηλή τεχνική πολυπλοκότητα και ευρωπαϊκή παρακολούθηση ολοκλήρωσης.</t>
-        </is>
-      </c>
-      <c r="O19" s="43" t="inlineStr">
+      <c r="M19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Η δράση αφορούσε στην κατασκευή τετραπλού σιδηροδρομικού διαδρόμου συνολικού μήκους 2,36χλμ, εκ των οποίων ~1,33χλμ είναι πλήρως υπογειοποιημένο. Ο ανατολικός διάδρομος θα εξυπηρετεί την κίνηση των προαστιακών συρμών, ενώ ο δυτικός την κίνηση των υπεραστικών συρμών. </t>
+        </is>
+      </c>
+      <c r="N19" s="53" t="inlineStr">
+        <is>
+          <t>Στις 31.12.2024 έληξε το Grant Agreement και το έργο δεν έχει ολοκληρωθεί (ποσοστό υλοποίησης Αρχικής Σύμβασης ~36,0%, 1ης Σ.Σ.Ε. ~71,1% και 2ης Σ.Σ.Ε. ~21%).
+Σημαντικές καθυστερήσεις στην υλοποίηση του έργου προκλήθηκαν λόγω αρχαιολογικών εργασιών που εκτελούνται με αυτεπιστασία, μετατόπισης πυκνού δικτύου ΟΚΩ από τους αρμόδιους φορείς (ΕΥΔΑΠ, ΔΕΔΔΗΕ και ΕΔΑ), καθώς και διασταύρωσης του διαδρόμου με τη σήραγγα του μετρό.
+Στις 20.05.2026 διαβιβάστηκε στην ΕΥΣΕ η Τελική Έκθεση της Δράσης με όλα απαιτούμενα συνημμένα προκειμένου να διαβιβαστούν στη CINEA.</t>
+        </is>
+      </c>
+      <c r="O19" s="36" t="inlineStr">
         <is>
           <t>Σ.2507/2018</t>
         </is>
       </c>
-      <c r="P19" s="43" t="inlineStr">
+      <c r="P19" s="36" t="inlineStr">
         <is>
           <t>Σ.2507-1/2021</t>
         </is>
       </c>
-      <c r="Q19" s="43" t="inlineStr">
+      <c r="Q19" s="36" t="inlineStr">
         <is>
           <t>Σ.2507-2/2023</t>
         </is>
       </c>
-      <c r="R19" s="10" t="inlineStr">
+      <c r="R19" s="9" t="inlineStr">
         <is>
           <t>2016-EL-TMC-0288-W
 (κωδ. ΟΠΣ 5021452)</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="9" t="inlineStr">
         <is>
           <t>Σε εξέλιξη</t>
         </is>
       </c>
-      <c r="T19" s="46" t="inlineStr">
+      <c r="T19" s="39" t="inlineStr">
         <is>
           <t>Αντικείμενο: Κατασκευή τετραπλού σιδηροδρομικού διαδρόμου συνολικού μήκους 2,36χλμ, εκ των οποίων ~1,33χλμ είναι πλήρως υπογειοποιημένο. Ο ανατολικός διάδρομος θα εξυπηρετεί την κίνηση των προαστιακών συρμών, ενώ ο δυτικός την κίνηση των υπεραστικών συρμών. Το έργο είναι ιδιαίτερα απαιτητικό τεχνικά, καθώς  η σήραγγα  που ξεκινά από την οδό Σεπολίων και καταλήγει στην οδό Σιώκου με ενδιάμεση την οδό Αγίου Μελετίου, θα έχει μέγιστο βάθος 19μ κάτω από το έδαφος. Έχει προβλεφθεί ειδική αντιστήριξη στο τμήμα που συναντά τη γραμμή 2 του Μετρό στο τμήμα Σεπόλια – Αττική. Άνωθεν του τεχνικού υπογειοποίησης θα αποκατασταθεί η επικοινωνία 9 καθέτων οδών, που σήμερα διακόπτονται λόγω του επίγειου σιδ/κού διαδρόμου. Προβλέπεται διαμόρφωση του τοπίου με κάλυψη του τεχνικού με πράσινο και δημιουργία ελεύθερων χώρων αναψυχής.
 Σύμβαση Σ.2507/2018: «ΚΑΤΑΣΚΕΥΗ ΤΕΤΡΑΠΛΟΥ ΣΙΔΗΡΟΔΡΟΜΙΚΟΥ ΔΙΑΔΡΟΜΟΥ ΣΤΟ ΤΜΗΜΑ ΕΞΟΔΟΣ Σ.Σ. ΑΘΗΝΩΝ (ΣΣΑ) – ΤΡΕΙΣ ΓΕΦΥΡΕΣ ΜΕ ΥΠΟΓΕΙΟΠΟΙΗΣΗ ΣΤΗΝ ΠΕΡΙΟΧΗ ΣΕΠΟΛΙΩΝ» 
@@ -2980,127 +2840,102 @@
 Στις 20.05.2026 διαβιβάστηκε στην ΕΥΣΕ η Τελική Έκθεση της Δράσης με όλα απαιτούμενα συνημμένα προκειμένου να διαβιβαστούν στη CINEA.</t>
         </is>
       </c>
-      <c r="U19" s="10" t="n"/>
-      <c r="V19" s="10" t="inlineStr">
-        <is>
-          <t>56.278.931,00 €</t>
-        </is>
-      </c>
-      <c r="W19" s="10" t="inlineStr">
-        <is>
-          <t>56.253.931,00 €</t>
-        </is>
-      </c>
-      <c r="X19" s="10" t="inlineStr">
-        <is>
-          <t>48705401.68</t>
-        </is>
-      </c>
-      <c r="Y19" s="10" t="n"/>
-      <c r="Z19" s="10" t="inlineStr">
-        <is>
-          <t>31.12.2024</t>
-        </is>
-      </c>
-      <c r="AA19" s="43" t="inlineStr">
-        <is>
-          <t>71,7%</t>
-        </is>
-      </c>
-      <c r="AB19" s="10" t="n"/>
-      <c r="AC19" s="10" t="n"/>
-      <c r="AD19" s="43" t="n">
+      <c r="U19" s="9" t="n"/>
+      <c r="V19" s="9" t="n"/>
+      <c r="W19" s="36" t="n">
         <v>37.99420572709171</v>
       </c>
-      <c r="AE19" s="43" t="n">
+      <c r="X19" s="36" t="n">
         <v>23.7204717163873</v>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1" s="35">
-      <c r="A20" s="9" t="n">
+    <row r="20" ht="60" customHeight="1" s="62">
+      <c r="A20" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>CEF 14 20</t>
-        </is>
-      </c>
-      <c r="C20" s="42" t="inlineStr">
-        <is>
-          <t>Κατασκευή της υποδομής Ψαθόπυργος - Πατρα (Ριο)</t>
-        </is>
-      </c>
-      <c r="D20" s="46" t="inlineStr">
+      <c r="B20" s="55" t="inlineStr">
+        <is>
+          <t>CEF 2014-2020</t>
+        </is>
+      </c>
+      <c r="C20" s="60" t="inlineStr">
+        <is>
+          <t>ΥΠΟΔΟΜΗ ΨΑΘΟΠΥΡΓΟΣ - ΡΙΟ</t>
+        </is>
+      </c>
+      <c r="D20" s="39" t="inlineStr">
         <is>
           <t>ΚΑΤΑΣΚΕΥΗ ΤΗΣ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΥΠΟΔΟΜHΣ ΣΤΟ ΤΜΗΜΑ ΨΑΘΟΠΥΡΓΟΣ - ΠΑΤΡΑ (ΡΙΟ) ΤΟΥ ΑΞΟΝΑ ΑΘΗΝΑ – ΠΑΤΡΑ, ΤΜΗΜΑ ΤΟΥ ΔΙΑΔΡΟΜΟΥ ΟΕΜ</t>
         </is>
       </c>
-      <c r="E20" s="43" t="inlineStr">
+      <c r="E20" s="36" t="inlineStr">
         <is>
           <t>Κεντρικό</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΑΣ Μ.Α.Ε. 
 (ΕΡΓΟΣΕ ΑΕ)</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>CEF 2014-2020</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>57.667.104,04 € (Συγχρ. Δημόσια Δαπάνη)</t>
-        </is>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
-        <is>
-          <t>716/2017 &amp; 716.1/2022 (Διαλυμένες)</t>
-        </is>
-      </c>
-      <c r="J20" s="10" t="inlineStr">
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57.667.104,04 € (Συγχρηματοδοτούμενη Δημόσια Δαπάνη)
+(Ημερ. Έναρξης GA: 16.02.2016
+Ημερ. Ολοκλ. GA: 31.12.2024)  </t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Διαλύθηκε η Σύμβαση.
+62.372.466,21 € (4ος  ΑΠΕ μειωτικός)
+</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>GD INFRASTRUTTURE</t>
         </is>
       </c>
-      <c r="K20" s="10" t="inlineStr">
-        <is>
-          <t>4-8-2017 (αρχική) / 20-7-2022 (συμπληρωματική)</t>
-        </is>
-      </c>
-      <c r="L20" s="10" t="inlineStr">
-        <is>
-          <t>15-9-2023 (Διάλυση συμβάσεων)</t>
-        </is>
-      </c>
-      <c r="M20" s="10" t="inlineStr">
-        <is>
-          <t>Κατασκευή υποδομής νέας διπλής σιδ/κής γραμμής 10,5 χλμ (2 Cover&amp;Cut, 10 ανισόπεδες διαβάσεις, 4 γέφυρες). Έργο σε διάλυση συμβάσεων.</t>
-        </is>
-      </c>
-      <c r="N20" s="46" t="inlineStr">
-        <is>
-          <t>Το έργο αφορά την κατασκευή της υποδομής της νέας διπλής σιδηροδρομικής γραμμής στο τμήμα Ψαθόπυργος–Ρίο, συνολικού μήκους 10,5 χλμ., καθώς και σημαντικών τεχνικών έργων, όπως δύο Cut &amp; Cover συνολικού μήκους περίπου 1 χλμ., 10 ανισόπεδες διαβάσεις, 4 σιδηροδρομικές γέφυρες, οδοποιία και υδραυλικά έργα.
-Η αρχική σύμβαση Σ.716/2017, προϋπολογισμού περίπου 96,05 εκατ. € χωρίς ΦΠΑ και αναθεώρηση, και η συμπληρωματική Σ.716-1/2022, ύψους περίπου 10,47 εκατ. €, ανατέθηκαν στην GD INFRASTRUTTURE. Η φυσική πρόοδος κατά τη διακοπή των εργασιών ανερχόταν σε 61,3% για την αρχική σύμβαση και 31,6% για τη συμπληρωματική.
-Οι συμβάσεις διαλύθηκαν οριστικά στις 15.9.2023, με αποτέλεσμα το έργο να παραμείνει ημιτελές. Η εξέλιξη αυτή επηρεάζει άμεσα την υλοποίηση της επόμενης σύμβασης Σ.1510/2022, καθώς η ολοκλήρωση της υποδομής αποτελεί προαπαιτούμενο για την κατασκευή της επιδομής, των σταθμών και στάσεων, της ηλεκτροκίνησης, της σηματοδότησης και των λοιπών συστημάτων στο τμήμα Ροδοδάφνη–Ρίο.
-Μετά τη διάλυση των συμβάσεων, εγκρίθηκε στις 19.2.2025 ο 4ος ΑΠΕ και το 4ο ΠΚΤΜΝΕ, συνολικής δαπάνης 62,37 εκατ. €, με σημαντικές μειώσεις σε σχέση με το αρχικό συμβατικό αντικείμενο. Παράλληλα, δρομολογείται η απόσχιση του τμήματος Αραχωβίτικα–Ρίο, προϋπολογισμού περίπου 20 εκατ. €, από τη σύμβαση 1510/2022 και η επαναδημοπράτηση του συνόλου των υπολειπόμενων εργασιών ως αυτοτελούς σύμβασης.
-Σε επίπεδο συγχρηματοδότησης, η δράση ολοκληρώθηκε διοικητικά με την αποδοχή από τη CINEA, στις 7.7.2026, του υλοποιηθέντος φυσικού αντικειμένου ως ημιτελούς. Ωστόσο, σε οικονομικό επίπεδο προκύπτει υποχρέωση επιστροφής κοινοτικής χρηματοδότησης ύψους 4.688.964,40 €.</t>
-        </is>
-      </c>
-      <c r="O20" s="43" t="n"/>
-      <c r="P20" s="43" t="n"/>
-      <c r="Q20" s="43" t="n"/>
-      <c r="R20" s="10" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>04.08.2017</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>Διάλυση σύμβασης: 15.09.2023</t>
+        </is>
+      </c>
+      <c r="M20" s="9" t="inlineStr">
+        <is>
+          <t>Η δράση αφορούσε στην κατασκευή της υποδομής της νέας διπλής σιδ/κής γραμμής, μήκους 10,5 χλμ και τεχνικών έργων εκ των οποίων τα σημαντικότερα: 2  Cover &amp; Cut , ένα στην περιοχή Αγ. Βασιλείου μήκους ~626 μ. και ένα στην περιοχή του Ρίου μήκους ~392 μ., 10 ανισόπεδες διαβάσεις συνολικού μήκους 170 μ, 4 Σιδ/κές Γέφυρες συνολικού μήκους 60μ, παράπλευρη και κάθετη οδοποιία και υδραυλικά έργα.</t>
+        </is>
+      </c>
+      <c r="N20" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Με την από 15.09.2023 απόφαση του Δ.Σ. της ΕΡΓΟΣΕ αποφασίστηκε η οριστική διακοπή των εργασιών και η διάλυση της σύμβασης (ποσοστό υλοποίησης Αρχικής Σύμβασης: ~61,3%, 1ης Σ.Σ.Ε.: 31,6%).
+Στις 15.04.2026 διαβιβάστηκε στην ΕΥΣΕ η Τελική Έκθεση της Δράσης με όλα απαιτούμενα συνημμένα προκειμένου να διαβιβαστούν στη CINEA.
+Στις 07.07.2026 κονοποιήθηκε στη ΣΕ ΜΑΕ από τη CINEA η ολοκλήρωση της αξιολόγησης (Closure Letter) με αποδοχή του φυσικού αντικειμένου που υλοποιήθηκε, καίτοι ημιτελές. Αναφορικά με τις δαπάνες θα πρέπει να επιστραφεί το ποσό των €4,688,964.40. </t>
+        </is>
+      </c>
+      <c r="O20" s="36" t="n"/>
+      <c r="P20" s="36" t="n"/>
+      <c r="Q20" s="36" t="n"/>
+      <c r="R20" s="9" t="inlineStr">
         <is>
           <t>2015-EL-TM-0253-W
 (κωδ. ΟΠΣ 5006728)</t>
         </is>
       </c>
-      <c r="S20" s="10" t="n"/>
-      <c r="T20" s="46" t="inlineStr">
+      <c r="S20" s="9" t="n"/>
+      <c r="T20" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">Αντικείμενο: Κατασκευή της υποδομής (καταστρώματος) της νέας διπλής σιδ/κής γραμμής, μήκους 10,5 χλμ και τεχνικών έργων εκ των οποίων τα σημαντικότερα είναι: 2 Cover &amp; Cut, ένα στην περιοχή Αγ. Βασιλείου μήκους ~626 μ. και ένα στην περιοχή του Ρίου μήκους ~392 μ., 10 ανισόπεδες διαβάσεις συνολικού μήκους 170 μ, 4 Σιδ/κές Γέφυρες συνολικού μήκους 60μ, παράπλευρη και κάθετη οδοποιία και υδραυλικά έργα.
 Σύμβαση:  Σ.716/2017:   «ΚΑΤΑΣΚΕΥΗ ΕΡΓΩΝ ΥΠΟΔΟΜΗΣ ΤΗΣ ΝΕΑΣ ΔΙΠΛΗΣ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΓΡΑΜΜΗΣ ΑΠΟ Χ.Θ. 113+000 – 123+500 ΣΤΟ ΤΜΗΜΑ ΨΑΘΟΠΥΡΓΟΣ-ΠΕΡΙΟΧΗ ΡΙΟΥ» Ανάδοχος:  GD INFRASTRUTTURE
@@ -3118,124 +2953,101 @@
 Στις 07.07.2026 κονοποιήθηκε στη ΣΕ ΜΑΕ από τη CINEA η ολοκλήρωση της αξιολόγησης (Closure Letter) με αποδοχή του φυσικού αντικειμένου που υλοποιήθηκε, καίτοι ημιτελές. Αναφορικά με τις δαπάνες θα πρέπει να επιστραφεί το ποσό των €4,688,964.40. </t>
         </is>
       </c>
-      <c r="U20" s="10" t="n"/>
-      <c r="V20" s="10" t="inlineStr">
-        <is>
-          <t>57.667.104,04 €</t>
-        </is>
-      </c>
-      <c r="W20" s="10" t="inlineStr">
-        <is>
-          <t>50.834.761,98 €</t>
-        </is>
-      </c>
-      <c r="X20" s="10" t="inlineStr">
-        <is>
-          <t>57.667.104,04 €</t>
-        </is>
-      </c>
-      <c r="Y20" s="10" t="n"/>
-      <c r="Z20" s="10" t="inlineStr">
-        <is>
-          <t>31.12.2024</t>
-        </is>
-      </c>
-      <c r="AA20" s="43" t="inlineStr">
-        <is>
-          <t>70,1%</t>
-        </is>
-      </c>
-      <c r="AB20" s="10" t="n"/>
-      <c r="AC20" s="10" t="n"/>
-      <c r="AD20" s="43" t="n">
+      <c r="U20" s="9" t="n"/>
+      <c r="V20" s="9" t="n"/>
+      <c r="W20" s="36" t="n">
         <v>38.3156482804225</v>
       </c>
-      <c r="AE20" s="43" t="n">
+      <c r="X20" s="36" t="n">
         <v>21.82687164443523</v>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1" s="35">
+    <row r="21" ht="60" customHeight="1" s="62">
       <c r="A21" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>CEF 21 27</t>
-        </is>
-      </c>
-      <c r="C21" s="40" t="inlineStr">
-        <is>
-          <t>Πύθιο-Ορμένιο</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="B21" s="54" t="inlineStr">
+        <is>
+          <t>CEF 2021-2027</t>
+        </is>
+      </c>
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>ΠΥΘΙΟ - ΟΡΜΕΝΙΟ</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>ΑΝΑΒΑΘΜΙΣΗ ΥΦΙΣΤΑΜΕΝΗΣ ΜΟΝΗΣ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΓΡΑΜΜΗΣ ΣΤΟ ΤΜΗΜΑ ΠΥΘΙΟ-ΟΡΜΕΝΙΟ</t>
         </is>
       </c>
-      <c r="E21" s="41" t="inlineStr">
+      <c r="E21" s="34" t="inlineStr">
         <is>
           <t>Extended Core (Εκτεταμένο Κεντρικό)</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΑΣ Μ.Α.Ε.
-(ΕΡΓΟΣΕ ΑΕ)</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="F21" s="52" t="inlineStr">
+        <is>
+          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΑΣ Μ.Α.Ε.</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>CEF 2021-2027</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>219.609.315,00€</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>~720.000.000 € (βέλτιστη λύση ολόκληρου του άξονα)</t>
-        </is>
-      </c>
-      <c r="J21" s="8" t="n"/>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>Grant Agreement: 16/10/2024</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t>H ολοκλήρωση του διαγωνισμού εκτιμάται στο 3ο τρίμηνο του 2026, με εκτιμώμενη διάρκεια κατασκευής 4 έτη.</t>
-        </is>
-      </c>
-      <c r="M21" s="44" t="inlineStr">
-        <is>
-          <t>Η υπό ανάθεση εργολαβία αποτελείται από 2 τμήματα Αλεξ/πολη-Πύθιο (111χλμ) &amp; Πύθιο-Ορμένιο (64χλμ) περιλαμβάνει την κατασκευή υποδομής για διπλή γραμμή και επιδομής μονής γραμμής σε μήκος ~67 χλμ στο πρώτο τμήμα και ~ 47 χλμ στο δεύτερο. Και τα δύο τμήματα εντάχθηκαν στο CEF 2021-2027 (υπογραφή Grant Agreement για το τμήμα Πύθιο – Ορμένιο: 16-10-2024 και για το τμήμα Αλεξανδρούπολη – Πύθιο: 15-10-2025).</t>
-        </is>
-      </c>
-      <c r="N21" s="8" t="inlineStr">
-        <is>
-          <t>Επανυποβολή στην ΕΥΔ ΜΕΤΑΦΟΡΕΣ</t>
-        </is>
-      </c>
-      <c r="O21" s="41" t="n"/>
-      <c r="P21" s="41" t="n"/>
-      <c r="Q21" s="41" t="n"/>
-      <c r="R21" s="44" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219.609.315,00€
+(Επιλέξιμη Δημόσια Δαπάνη)
+(Ημερ. Έναρξης GA: 30.01.2024 
+Ημερ. Ολοκλ. GA: 29.11.2028)  </t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>~720.000.000 € (π/ϋ οριστικής λύσης Β.Ι Φάσης Ανταγωνιστικού διαλόγου για το σύνολο του έργου Αλεξανδρούπολη - Πύθιο - Ορμένιο)</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="n"/>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Εκτίμηση: τέλη Φεβρουαρίου 2027</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>4 έτη από την υπογραφή της σύμβασης</t>
+        </is>
+      </c>
+      <c r="M21" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Η δράση αφορά στις εργασίες αναβάθμισης της υποδομής και επιδομής της μονής σιδηροδρομικής γραμμής στο τμήμα Πύθιο - Ορμένιο σε μήκος ~ 47 χλμ. 
+</t>
+        </is>
+      </c>
+      <c r="N21" s="52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Το αντικείμενο περιλαμβάνεται στην υπό ανάθεση σύμβαση «Μελέτη – Κατασκευή» του έργου «ΑΝΑΒΑΘΜΙΣΗ ΜΕ ΔΙΠΛΑΣΙΑΣΜΟ ΤΗΣ ΥΦΙΣΤΑΜΕΝΗΣ ΜΟΝΗΣ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΓΡΑΜΜΗΣ ΑΛΕΞΑΝΔΡΟΥΠΟΛΗ – ΠΥΘΙΟ – ΟΡΜΕΝΙΟ», η οποία βρίσκεται σε φάση δημοπράτησης με τη διαδικασία του Ανταγωνιστικού Διαλόγου.
+Η Φάση Β.Ι του Ανταγωνιστικού Διαλόγου ολοκληρώθηκε στις 5-12-2024. Στις 27-1-2025 εγκρίθηκε η βέλτιστη λύση (π/ϋ 720 εκ €) και απεστάλησαν στη Διαχειριστική Αρχή για προέγκριση τα Τεύχη για τη Β.ΙΙ Φάση. Η Δ.Α. έχει αποστείλει έγγραφο με παρατηρήσεις και αναμένεται η επανυποβολή των Τευχών από τη ΣΕ ΜΑΕ.  </t>
+        </is>
+      </c>
+      <c r="O21" s="34" t="n"/>
+      <c r="P21" s="34" t="n"/>
+      <c r="Q21" s="34" t="n"/>
+      <c r="R21" s="37" t="inlineStr">
         <is>
           <t>Project ID:
 101175617 — 23-EL-TC-SPYTHORM
 (ΟΠΣ: 6034729)</t>
         </is>
       </c>
-      <c r="S21" s="8" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>Σε διαδικασία ανάθεσης</t>
         </is>
       </c>
-      <c r="T21" s="44" t="inlineStr">
+      <c r="T21" s="37" t="inlineStr">
         <is>
           <t>Υπογραφή Grant Agreement: 16-10-2024. Επιλέξιμη Δημόσια Δαπάνη Πράξης:  219.609.315,00 €. 
 Η δράση αφορά στις εργασίες αναβάθμισης της υποδομής και επιδομής της μονής σιδηροδρομικής γραμμής στο τμήμα Πύθιο - Ορμένιο σε μήκος ~ 47 χλμ. 
@@ -3254,127 +3066,111 @@
 H υπογραφή της σύμβασης εκτιμάται τέλη Φεβρουαρίου 2027, με εκτιμώμενη διάρκεια κατασκευής 4 έτη.</t>
         </is>
       </c>
-      <c r="U21" s="54" t="inlineStr">
+      <c r="U21" s="45" t="inlineStr">
         <is>
           <t>Ένταξη στο ΑΠΔΕ 2026-2030
 Επανυποβολή στην ΕΥΔ ΜΕΤΑΦΟΡΕΣ και έγκριση τευχών Β.ΙΙ σταδίου
 Έναρξη σταδίου Β.ΙΙ.</t>
         </is>
       </c>
-      <c r="V21" s="8" t="n"/>
-      <c r="W21" s="8" t="n"/>
-      <c r="X21" s="8" t="n"/>
-      <c r="Y21" s="8" t="n"/>
-      <c r="Z21" s="8" t="inlineStr">
-        <is>
-          <t>11/29/2028</t>
-        </is>
-      </c>
-      <c r="AA21" s="41" t="inlineStr">
-        <is>
-          <t>CEF 
-85%</t>
-        </is>
-      </c>
-      <c r="AB21" s="8" t="inlineStr">
-        <is>
-          <t>CEF-T-2023-COMPCOEN</t>
-        </is>
-      </c>
-      <c r="AC21" s="8" t="n"/>
-      <c r="AD21" s="41" t="n">
+      <c r="V21" s="7" t="n"/>
+      <c r="W21" s="34" t="n">
         <v>41.56568122753145</v>
       </c>
-      <c r="AE21" s="41" t="n">
+      <c r="X21" s="34" t="n">
         <v>26.53478011452405</v>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1" s="35">
-      <c r="A22" s="9" t="n">
+    <row r="22" ht="60" customHeight="1" s="62">
+      <c r="A22" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>CEF 21 27</t>
-        </is>
-      </c>
-      <c r="C22" s="42" t="inlineStr">
-        <is>
-          <t>Αλεξανδρούπολη-Πύθιο</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>Αναβάθμιση Μονής ΣΔ Γραμμής Τμήμα Αλεξανδρούπολη–Πύθιο</t>
-        </is>
-      </c>
-      <c r="E22" s="43" t="inlineStr">
+      <c r="B22" s="54" t="inlineStr">
+        <is>
+          <t>CEF 2021-2027</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="inlineStr">
+        <is>
+          <t>ΑΛΕΞΑΝΔΡΟΥΠΟΛΗ - ΠΥΘΙΟ</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>ΑΝΑΒΑΘΜΙΣΗ ΥΦΙΣΤΑΜΕΝΗΣ ΜΟΝΗΣ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΓΡΑΜΜΗΣ ΣΤΟ ΤΜΗΜΑ ΑΛΕΞΑΝΔΡΟΥΠΟΛΗ-ΠΥΘΙΟ</t>
+        </is>
+      </c>
+      <c r="E22" s="36" t="inlineStr">
         <is>
           <t>Κεντρικό (Core)</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΑΣ Μ.Α.Ε.
-(ΕΡΓΟΣΕ ΑΕ)</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="F22" s="52" t="inlineStr">
+        <is>
+          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΑΣ Μ.Α.Ε.</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
         <is>
           <t>CEF 2021-2027</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>325.891.827 €</t>
-        </is>
-      </c>
-      <c r="I22" s="10" t="inlineStr">
-        <is>
-          <t>~720.000.000 € (βέλτιστη λύση ολόκληρου του άξονα)</t>
-        </is>
-      </c>
-      <c r="J22" s="10" t="inlineStr">
-        <is>
-          <t>Σε εξέλιξη Ανταγωνιστικός Διάλογος</t>
-        </is>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t>Grant Agreement: 15/10/2025</t>
-        </is>
-      </c>
-      <c r="L22" s="10" t="inlineStr">
-        <is>
-          <t>Η υπογραφή της σύμβασης εκτιμάται τον Ιανουάριο 2027</t>
-        </is>
-      </c>
-      <c r="M22" s="10" t="inlineStr">
-        <is>
-          <t>Αναβάθμιση μονής ΣΔ γραμμής Αλεξ/πολη–Πύθιο (111 χλμ): υποδομή διπλής + επιδομή μονής (~67 χλμ).</t>
-        </is>
-      </c>
-      <c r="N22" s="46" t="inlineStr">
-        <is>
-          <t>Η διαδικασία δημοπράτησης μέσω Ανταγωνιστικού Διαλόγου βρίσκεται σε εξέλιξη, με εκκρεμότητα την ολοκλήρωση του Β.ΙΙ σταδίου και την έγκριση των τευχών δημοπράτησης. Παράλληλα, προχωρούν οι διαδικασίες απαλλοτριώσεων και η ένταξη του έργου στο ΠΔΕ. Η υπογραφή της σύμβασης εκτιμάται τέλη Φεβρουαρίου 2027, ενώ απαιτείται ξεχωριστή χρηματοδότηση για τα συστήματα ηλεκτροκίνησης και σηματοδότησης.</t>
-        </is>
-      </c>
-      <c r="O22" s="43" t="n"/>
-      <c r="P22" s="43" t="n"/>
-      <c r="Q22" s="43" t="n"/>
-      <c r="R22" s="46" t="inlineStr">
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">325.891.827 €
+(Επιλέξιμη Δημόσια Δαπάνη)
+(Ημερ. Έναρξης GA: 31.01.2025
+Ημερ. Ολοκλ. GA: 29.11.2029)  </t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>~720.000.000 € (π/ϋ οριστικής λύσης Β.Ι Φάσης Ανταγωνιστικού διαλόγου για το σύνολο του έργου Αλεξανδρούπολη - Πύθιο - Ορμένιο)</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>Εκτίμηση: τέλη Φεβρουαρίου 2027</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>4 έτη από την υπογραφή της σύμβασης</t>
+        </is>
+      </c>
+      <c r="M22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Η δράση αφορά στις εργασίες αναβάθμισης της υποδομής και επιδομής της μονής σιδηροδρομικής γραμμής στο τμήμα Αλεξανδρούπολη - Πύθιο σε μήκος ~ 68 χλμ. 
+</t>
+        </is>
+      </c>
+      <c r="N22" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Το αντικείμενο περιλαμβάνεται στην υπό ανάθεση σύμβαση «Μελέτη – Κατασκευή» του έργου «ΑΝΑΒΑΘΜΙΣΗ ΜΕ ΔΙΠΛΑΣΙΑΣΜΟ ΤΗΣ ΥΦΙΣΤΑΜΕΝΗΣ ΜΟΝΗΣ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΓΡΑΜΜΗΣ ΑΛΕΞΑΝΔΡΟΥΠΟΛΗ – ΠΥΘΙΟ – ΟΡΜΕΝΙΟ», η οποία βρίσκεται σε φάση δημοπράτησης με τη διαδικασία του Ανταγωνιστικού Διαλόγου.
+Η Φάση Β.Ι του Ανταγωνιστικού Διαλόγου ολοκληρώθηκε στις 5-12-2024. Στις 27-1-2025 εγκρίθηκε η βέλτιστη λύση (π/ϋ 720 εκ €) και απεστάλησαν στη Διαχειριστική Αρχή για προέγκριση τα Τεύχη για τη Β.ΙΙ Φάση. Η Δ.Α. έχει αποστείλει έγγραφο με παρατηρήσεις και αναμένεται η επανυποβολή των Τευχών από τη ΣΕ ΜΑΕ.  </t>
+        </is>
+      </c>
+      <c r="O22" s="36" t="n"/>
+      <c r="P22" s="36" t="n"/>
+      <c r="Q22" s="36" t="n"/>
+      <c r="R22" s="39" t="inlineStr">
         <is>
           <t>Project ID:
 101233049 — 24-EL-TC-ALPY
 (ΟΠΣ: ….......)</t>
         </is>
       </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="S22" s="9" t="inlineStr">
         <is>
           <t>Σε διαδικασία ανάθεσης</t>
         </is>
       </c>
-      <c r="T22" s="46" t="inlineStr">
+      <c r="T22" s="39" t="inlineStr">
         <is>
           <t>Υπογραφή Grant Agreement: 15.10.2025. Επιλέξιμη Δημόσια Δαπάνη Πράξης: 325.891.827,00 €. 
 Η δράση αφορά στις εργασίες αναβάθμισης της υποδομής και επιδομής της μονής σιδηροδρομικής γραμμής στο τμήμα Αλεξ/πολη-Πύθιο σε μήκος ~ 68 χλμ. 
@@ -3393,114 +3189,98 @@
 Η υπογραφή της σύμβασης εκτιμάται τέλη Φεβρουαρίου 2027, με εκτιμώμενη διάρκεια κατασκευής 4 έτη.</t>
         </is>
       </c>
-      <c r="U22" s="55" t="inlineStr">
+      <c r="U22" s="57" t="inlineStr">
         <is>
           <t>Ένταξη στο ΑΠΔΕ 2026-2030
 Επανυποβολή στην ΕΥΔ ΜΕΤΑΦΟΡΕΣ και έγκριση τευχών Β.ΙΙ σταδίου
 Έναρξη σταδίου Β.ΙΙ.</t>
         </is>
       </c>
-      <c r="V22" s="10" t="n"/>
-      <c r="W22" s="10" t="n"/>
-      <c r="X22" s="10" t="n"/>
-      <c r="Y22" s="10" t="n"/>
-      <c r="Z22" s="10" t="inlineStr">
-        <is>
-          <t>29.11.2029</t>
-        </is>
-      </c>
-      <c r="AA22" s="43" t="inlineStr">
-        <is>
-          <t>[max 85%]</t>
-        </is>
-      </c>
-      <c r="AB22" s="10" t="inlineStr">
-        <is>
-          <t>CEF-T-2024-CORECOEN-RAIL-WORKS</t>
-        </is>
-      </c>
-      <c r="AC22" s="10" t="n"/>
-      <c r="AD22" s="43" t="n">
+      <c r="V22" s="9" t="n"/>
+      <c r="W22" s="36" t="n">
         <v>40.90148099342407</v>
       </c>
-      <c r="AE22" s="43" t="n">
+      <c r="X22" s="36" t="n">
         <v>26.19688718758239</v>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1" s="35">
-      <c r="A23" s="9" t="n">
+    <row r="23" ht="60" customHeight="1" s="62">
+      <c r="A23" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>CEF 21 27</t>
-        </is>
-      </c>
-      <c r="C23" s="42" t="inlineStr">
-        <is>
-          <t>Νέα Καρβάλη - Τοξότες &amp; Σύνδεση Λιμένα Καβάλας</t>
-        </is>
-      </c>
-      <c r="D23" s="46" t="inlineStr">
+      <c r="B23" s="54" t="inlineStr">
+        <is>
+          <t>CEF 2021-2027</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="inlineStr">
+        <is>
+          <t>ΝΕΑ ΚΑΡΒΑΛΗ - ΤΟΞΟΤΕΣ</t>
+        </is>
+      </c>
+      <c r="D23" s="39" t="inlineStr">
         <is>
           <t>ΚΑΤΑΣΚΕΥΗ ΝΕΑΣ ΜΟΝΗΣ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΓΡΑΜΜΗΣ, ΤΜΗΜΑ: ΝΕΑ ΚΑΡΒΑΛΗ - ΤΟΞΟΤΕΣ</t>
         </is>
       </c>
-      <c r="E23" s="43" t="inlineStr">
+      <c r="E23" s="36" t="inlineStr">
         <is>
           <t>Κεντρικό (Core)</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΑΣ Μ.Α.Ε.
-(ΕΡΓΟΣΕ ΑΕ)</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="F23" s="52" t="inlineStr">
+        <is>
+          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΑΣ Μ.Α.Ε.</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>CEF 2021-2027</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>212.725.000 € (επιλέξιμη δημόσια δαπάνη)</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>140.597.827,77 € (ποσό προσφοράς αναδόχου)</t>
-        </is>
-      </c>
-      <c r="J23" s="10" t="inlineStr">
-        <is>
-          <t>ΤΕΡΝΑ Α.Ε.</t>
-        </is>
-      </c>
-      <c r="K23" s="10" t="inlineStr">
-        <is>
-          <t>Εκτίμηση: 31.05.2026</t>
-        </is>
-      </c>
-      <c r="L23" s="10" t="inlineStr">
-        <is>
-          <t>02.12.2026 (λήξη Grant Agreement - απαιτείται παράταση)</t>
-        </is>
-      </c>
-      <c r="M23" s="10" t="inlineStr">
-        <is>
-          <t>Κατασκευή γραμμής ~31,7χλμ &amp; σύνδεση Λιμένα 5,3χλμ (υποδομή/επιδομή)</t>
-        </is>
-      </c>
-      <c r="N23" s="46" t="inlineStr">
-        <is>
-          <t>Το έργο Νέα Καρβάλη–Τοξότες έχει ολοκληρώσει τη διαγωνιστική διαδικασία και έχει αναδειχθεί ανάδοχος, αλλά η υπογραφή της σύμβασης έχει ανασταλεί λόγω εκκρεμοτήτων στο Ελεγκτικό Συνέδριο. Παράλληλα υπάρχουν δικαστικές εμπλοκές για απαλλοτριώσεις και ζητήματα ασφάλειας στη ΒΙΠΕ, που έχουν επηρεάσει την ωρίμανση. Η περιβαλλοντική αδειοδότηση έχει αποκατασταθεί με τροποποιήσεις και πρόσθετα μέτρα. Κρίσιμη προϋπόθεση παραμένει η άρση των νομικών εμποδίων ώστε να προχωρήσει η συμβασιοποίηση.</t>
-        </is>
-      </c>
-      <c r="O23" s="43" t="n"/>
-      <c r="P23" s="43" t="n"/>
-      <c r="Q23" s="43" t="n"/>
-      <c r="R23" s="10" t="inlineStr">
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212.725.000 € (Επιλέξιμη Δημόσια Δαπάνη)
+(Ημερ. Έναρξης GA: 03.12.2021
+Ημερ. Ολοκλ. GA: 02.12.2026)  </t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>140.597.827,77 € (δεν έχει υπογραφεί η σύμβαση)</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>ΤΕΡΝΑ Α.Ε.
+(δεν έχει υπογραφεί η σύμβαση)</t>
+        </is>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>3,5 έτη από την υπογραφή της σύμβασης</t>
+        </is>
+      </c>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>H δράση αφορά στην κατασκευή της νέας μονής σιδηροδρομικής γραμμής (εργασίες υποδομής/επιδομής και σταθμών/στάσεων) στο τμήμα Νέα Καρβάλη - Τοξότες, μήκους ~31,7 χλμ. και στο τμήμα σύνδεσης Νέα Καρβάλη  - Εμπορευματικός Λιμένας Καβάλας, μήκους 5,3 χλμ..</t>
+        </is>
+      </c>
+      <c r="N23" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Στην παρούσα φάση είναι σε εξελιξη ο προσυμβατικός έλεγχος από το Ελ. Συν. Εκδόθηκε η υπ' αριθμ. 183/2026 Πράξη του Ε΄ Κλιμακίου του Ελ. Συν., σύμφωνα με την οποία κωλύεται η υπογραφή της σύμβασης. Τον Μάιο κατατέθηκε Προσφυγή Ανάκλησης ενώπιον του αρμόδιου Τμήματος του Ελεγκτικού Συνεδρίου, η οποία επίσης απορρίφθηκε. Έχει κατατεθεί Προσφυγή Αναθεώρησης η οποία θα εκδικαστεί από την Ολομέλεια του ΕλΣυν.
+</t>
+        </is>
+      </c>
+      <c r="O23" s="36" t="n"/>
+      <c r="P23" s="36" t="n"/>
+      <c r="Q23" s="36" t="n"/>
+      <c r="R23" s="9" t="inlineStr">
         <is>
           <t>Project ID: 101079623
   21-EL-TC-KARTOXRAIL
@@ -3508,12 +3288,12 @@
 6010609)</t>
         </is>
       </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="9" t="inlineStr">
         <is>
           <t>Σε διαδικασία αναθεσης</t>
         </is>
       </c>
-      <c r="T23" s="46" t="inlineStr">
+      <c r="T23" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">Υπογραφή Grant Agreement: 13-10-2022.  Επιλέξιμη Δημόσια Δαπάνη Πράξης: 212.725.000,00 €. 
 Το έργο περιλαμβάνει την κατασκευή της νέας μονής σιδηροδρομικής γραμμής (εργασίες υποδομής/επιδομής και σταθμών/στάσεων) στο τμήμα Νέα Καρβάλη - Τοξότες, μήκους ~31,7 χλμ. και στο τμήμα σύνδεσης Νέα Καρβάλη  - Εμπορευματικός Λιμένας Καβάλας, μήκους 5,3 χλμ., καθώς και τις απαραίτητες για την κατασκευή του έργου απαλλοτριώσεις και τις αναγκαίες μετατοπίσεις των δικτύων ΟΚΩ.
@@ -3522,123 +3302,97 @@
  Έχουν εκδοθεί οι δικαστικές αποφάσεις για συντέλεση απαλλοτριώσεων με το άρθρο 7Α και εκκρεμεί η κατάθεση των αποζημιώσεων ώστε να αποκτηθεί πρόσβαση στις εκτάσεις, λόγω των ακόλουθων δικαστικών εμπλοκών.
 Προέκυψε πρόβλημα με κατάθεση αιτήσεων ακύρωσης των αποφάσεων κήρυξης απαλλοτριώσεων σε τμήματα όμορα της ΒΦΛ. Εκδόθηκε Απόφαση του ΣτΕ επί αίτησης αναστολής εκτέλεσης των εν λόγω αποφάσεων, η οποία αποδέχτηκε μερικώς το αίτημα της ΒΦΛ και ζήτησε την εκπόνηση μελέτης επικινδυνότητας στη βιομηχανική περιοχή χωρίς να αναστέλει τη διαδικασία απαλλοτριώσεων. Στις 10-7-2025 υπεγράφη η σύμβαση εκπόνησης της εν λόγω μελέτης, η οποία ολοκληρώθηκε και γνωστοποιήθηκε τόσο στο ΣτΕ όσο και στο Ελεγκτικό Συνέδριο ώστε να επαναξιολογηθεί ο φάκελος ανάθεσης. Η ΒΦΛ προσέφυγε στο ΣτΕ και κατά της μελέτης επικινδυνότητας. Επίσης, ασκήθηκε προσφυγή στο ΣτΕ για την ανάκληση της ΑΕΠΟ του έργου, η οποία συζητήθηκε στις 19.05.2025.
 Στις 19.08.2025 η ΔΙΠΑ/ΥΠΕΝ εξέδωσε απόφαση προσωρινής αναστολής ισχύος της ΑΕΠΟ προκειμένου να ολοκληρωθεί η διερεύνηση των ζητημάτων ασφάλειας και η ένταξη των κατάλληλων μέτρων που θα εξαλείφουν τους πιθανούς κινδύνους. Την 18.02.2026 εκδόθηκε από τη ΔΙΠΑ Απόφαση Ανάκλησης της προσωρινής αναστολής της ΑΕΠΟ του έργου όπως ίσχυε και τροποποίηση της ίδιας ΑΕΠΟ για (α) την ενσωμάτωση στον σχεδιασμό του έργου των διαφοροποιήσεων του Σταθμού Διαλογής που αφορούν σε μέτρα αντιμετώπισης κινδύνων, με τους αντίστοιχους περιβαλλοντικούς όρους και (β) την επικαιροποίηση του περιεχομένου της ΑΕΠΟ με βάση το νεότερο κανονιστικό πλαίσιο (αναθεώρηση Σχεδίων Διαχείρισης Λεκανών Απορροής Ποταμών / Κινδύνου Πλημμύρας, συμμόρφωση με το άρθρο 18 του Εθνικού Κλιματικού Νόμου [ν.4936/2022]) κ.ά.
-Αναμένεται η απόσυρση της μιας εναπομείνασας προδικαστικής προσφυγής. Εκδόθηκε η υπ' αριθμ. 183/2026 Πράξη του Ε΄ Κλιμακίου του Ελεγκτικού Συνεδρίου, σύμφωνα με την οποία κωλύεται η υπογραφή της σύμβασης. Τον Μάιο κατατέθηκε Προσφυγή Ανάκλησης ενώπιον του αρμόδιου Τμήματος του Ελεγκτικού Συνεδρίου, η οποία επίσης απορρίφθηκε. Αναμένεται η κατάθεση Προσφυγής Αναθεώρησης η οποία θα εκδικαστεί από την Ολομέλεια του ΕλΣυν. Για την υπογραφή της σύμβασης απαιτείται η προέγκριση συμβασιοποίησης από τη Διαχειριστική Αρχή, ενημέρωση της Βουλής και πρόσκληση στον ανάδοχο για προσκόμιση δικαιολογητικών και οψιγενών μεταβολών.
+Αναμένεται η απόσυρση της μιας εναπομείνασας προδικαστικής προσφυγής. Εκδόθηκε η υπ' αριθμ. 183/2026 Πράξη του Ε΄ Κλιμακίου του Ελεγκτικού Συνεδρίου, σύμφωνα με την οποία κωλύεται η υπογραφή της σύμβασης. Τον Μάιο κατατέθηκε Προσφυγή Ανάκλησης ενώπιον του αρμόδιου Τμήματος του Ελεγκτικού Συνεδρίου, η οποία επίσης απορρίφθηκε.Έχει κατατεθεί Προσφυγή Αναθεώρησης η οποία θα εκδικαστεί από την Ολομέλεια του ΕλΣυν. Για την υπογραφή της σύμβασης απαιτείται η προέγκριση συμβασιοποίησης από τη Διαχειριστική Αρχή, ενημέρωση της Βουλής και πρόσκληση στον ανάδοχο για προσκόμιση δικαιολογητικών και οψιγενών μεταβολών.
 Στις 22-5-2026 διαβιβάστηκε στη ΣΕ ΜΑΕ αρμοδίως υπογεγραμμένο από το Υπουργείο Υποδομών και Μεταφορών το Τεχνικό Δελτίο Έργων (ΤΔΕ), όπως αυτό παράγεται από το eΠΔΕ και στις 28-5-2026 διαβιβάστηκε στην ΕΥΔ «ΜΕΤΑΦΟΡΕΣ» και στην  Ειδική Υπηρεσία Συντονισμού της Εφαρμογής (ΕΥΣΕ) για τις καθ΄ αρμοδιότητα ενέργειές τους για την ένταξη του έργου στη ΣΑΕ 079/7 του ΑΠΔΕ 2026, με συνολικό  π/ϋ 268.747.800,00 €. 
  </t>
         </is>
       </c>
-      <c r="U23" s="46" t="inlineStr">
+      <c r="U23" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">Εξαιτίας των δικαστικών εμπλοκών και των μεγάλων καθυστερήσεων για την υπογραφή της σύμβασης έχει τεθεί σε κίνδυνο η χρηματοδότηση του έργου. 
 Στη συνάντηση που πραγματοποιήθηκε στη Θεσσαλονίκη στις 18.06.2026 τα στελέχη της CINEA δέχτηκαν να αναμένουν την έκδοση της Απόφασης του Ελεγκτικού Συνεδρίου και προγραμματίστηκε τηλεδιάσκεψη την πρώτη εβδομάδα του Σεπτεμβρίου για τη λήψη αποφάσεων για τη χρηματοδότηση της δράσης. </t>
         </is>
       </c>
-      <c r="V23" s="10" t="inlineStr">
-        <is>
-          <t>212.725.000,00 €</t>
-        </is>
-      </c>
-      <c r="W23" s="10" t="inlineStr">
-        <is>
-          <t>21.159.000,00 €</t>
-        </is>
-      </c>
-      <c r="X23" s="10" t="n"/>
-      <c r="Y23" s="10" t="n"/>
-      <c r="Z23" s="10" t="inlineStr">
-        <is>
-          <t>02.12.2026</t>
-        </is>
-      </c>
-      <c r="AA23" s="43" t="inlineStr">
-        <is>
-          <t>CEF 
-72,32%</t>
-        </is>
-      </c>
-      <c r="AB23" s="10" t="inlineStr">
-        <is>
-          <t>CEF-T-2021-CORECOEN</t>
-        </is>
-      </c>
-      <c r="AC23" s="10" t="inlineStr">
-        <is>
-          <t>212.725.000,00 €</t>
-        </is>
-      </c>
-      <c r="AD23" s="43" t="n">
+      <c r="V23" s="9" t="n"/>
+      <c r="W23" s="36" t="n">
         <v>40.98726712266368</v>
       </c>
-      <c r="AE23" s="43" t="n">
+      <c r="X23" s="36" t="n">
         <v>24.56639068329006</v>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1" s="35">
+    <row r="24" ht="60" customHeight="1" s="62">
       <c r="A24" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>CEF 21 27</t>
-        </is>
-      </c>
-      <c r="C24" s="47" t="inlineStr">
-        <is>
-          <t>Μουριές-Προμαχώνας</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Αναβάθμιση Σιδ. Γραμμής Θεσ/νίκη-Προμαχώνας (Τμήμα Μουριές-Προμαχώνας) για Ηλεκτροκίνηση</t>
-        </is>
-      </c>
-      <c r="E24" s="41" t="inlineStr">
+      <c r="B24" s="54" t="inlineStr">
+        <is>
+          <t>CEF 2021-2027</t>
+        </is>
+      </c>
+      <c r="C24" s="40" t="inlineStr">
+        <is>
+          <t>ΜΟΥΡΙΕΣ - ΠΡΟΜΑΧΩΝΑΣ</t>
+        </is>
+      </c>
+      <c r="D24" s="52" t="inlineStr">
+        <is>
+          <t>ΑΝΑΒΑΘΜΙΣΗ ΤΗΣ ΥΦΙΣΤΑΜΕΝΗΣ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΓΡΑΜΜΗΣ ΘΕΣΣΑΛΟΝΙΚΗ-ΠΡΟΜΑΧΩΝΑΣ (ΤΜΗΜΑ ΜΟΥΡΙΕΣ-ΠΡΟΜΑΧΩΝΑΣ) ΓΙΑ ΤΗΝ ΕΓΚΑΤΑΣΤΑΣΗ ΗΛΕΚΤΡΟΚΙΝΗΣΗΣ</t>
+        </is>
+      </c>
+      <c r="E24" s="34" t="inlineStr">
         <is>
           <t>Κεντρικό (Core)</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΑΣ Μ.Α.Ε.
-(ΟΣΕ ΑΕ)</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="F24" s="52" t="inlineStr">
+        <is>
+          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΑΣ Μ.Α.Ε.</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>CEF 2021-2027</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>144.000.000 € (επιλέξιμη δημόσια δαπάνη)</t>
-        </is>
-      </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>- (Υπό προετοιμασία ωρίμανσης/δημοπράτησης)</t>
-        </is>
-      </c>
-      <c r="J24" s="8" t="n"/>
-      <c r="K24" s="8" t="n"/>
-      <c r="L24" s="8" t="inlineStr">
-        <is>
-          <t>31.05.2028</t>
-        </is>
-      </c>
-      <c r="M24" s="8" t="inlineStr">
-        <is>
-          <t>Αναβάθμιση 53χλμ γραμμής, υποδομή/επιδομή, και μελέτες ηλεκτροκίνησης για το σύνολο των 142,4χλμ</t>
-        </is>
-      </c>
-      <c r="N24" s="8" t="inlineStr">
-        <is>
-          <t>Το έργο Θεσσαλονίκη–Στρυμώνας–Προμαχώνας έχει εξασφαλισμένη χρηματοδότηση CEF και αφορά εκτεταμένη αναβάθμιση της γραμμής και προπαρασκευαστικές μελέτες για μελλοντική ηλεκτροκίνηση και διαλειτουργικότητα. Βρίσκεται σε φάση ωρίμανσης μέσω της ΕΕΣΥΠ και έχουν ήδη ολοκληρωθεί κρίσιμες τεχνικές μελέτες ασφάλειας. Παράλληλα έχει προχωρήσει η διοικητική ένταξη στο εθνικό πρόγραμμα χρηματοδότησης και η διαχείριση των απαραίτητων συμβάσεων ωρίμανσης. Κρίσιμο ζητούμενο είναι η ολοκλήρωση των μελετών και η προετοιμασία για τη δημοπράτηση των έργων κατασκευής.</t>
-        </is>
-      </c>
-      <c r="O24" s="41" t="n"/>
-      <c r="P24" s="41" t="n"/>
-      <c r="Q24" s="41" t="n"/>
-      <c r="R24" s="8" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144.000.000 € (Επιλέξιμη Δημόσια Δαπάνη)
+(Ημερ. Έναρξης GA: 01.03.2024
+Ημερ. Ολοκλ. GA: 31.05.2028)  </t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="n"/>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>Εκτίμηση: τέλη Μαΐου 2027</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>Η δράση αφορά στην αναβάθμιση της υφιστάμενης μονής  σιδηροδρομικής γραμμής Θεσσαλονίκης - Στρυμώνα - Προμαχώνα (στο τμήμα Μουριές έως Προμαχώνα, μήκους ~53 χλμ.) και στις μελέτες για τη 2η φάση του έργου, ώστε να μπορεί να εγκατασταθεί μελλοντικά το συστήμα ηλεκτροκίνησης σε ολόκληρη τη σιδηροδρομική γραμμή Θεσσαλονίκης – Προμαχώνα, μήκους ~142,4 km, με μέγιστη ταχύτητα 120 km/h</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr">
+        <is>
+          <t>Το έργο εντάχθηκε στο Αναπτυξιακό Πρόγραμμα Συμβάσεων Στρατηγικής Σημασίας του Ν.4799/2021 και έχει περιέλθει στις αρμοδιότητες της Ελληνικής Εταιρείας Συμμετοχών και Περιουσίας (ΕΕΣΥΠ) ΑΕ , η οποία μέσω της Μονάδας Συμβάσεων Στρατηγικής Σημασίας, σύμφωνα με τον Κανονισμό Αναθέσεων ΤΑΙΠΕΔ θα προβεί σε όλες τις απαραίτητες ενέργειες για την ανάθεση των απαραίτητων συμβάσεων, μελετών και παροχής υπηρεσιών για την ωρίμανση του έργου. 
+ Έχει υπογραφεί η σχετική  Σύμβαση μεταξύ του ΥΠΥΜΕ, της ΣΕΜΑΕ και της ΕΕΣΥΠ ΑΕ.</t>
+        </is>
+      </c>
+      <c r="O24" s="34" t="n"/>
+      <c r="P24" s="34" t="n"/>
+      <c r="Q24" s="34" t="n"/>
+      <c r="R24" s="7" t="inlineStr">
         <is>
           <t>Project ID 101175710
 23-EL-TC-
@@ -3646,12 +3400,12 @@
 (ΟΠΣ: 6028774)</t>
         </is>
       </c>
-      <c r="S24" s="8" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>Σε ωρίμανση</t>
         </is>
       </c>
-      <c r="T24" s="44" t="inlineStr">
+      <c r="T24" s="37" t="inlineStr">
         <is>
           <t>Υπογραφή Grant Agreement : 15-10-2024.  Επιλέξιμη Δημόσια Δαπάνη Πράξης: 144.000.000,00 €.                                                                      
 Το έργο αφορά στην αναβάθμιση της υφιστάμενης μονής  Σ.Γ. Θεσσαλονίκης - Στρυμώνα - Προμαχώνα (στο τμήμα Μουριές έως Προμαχώνα, μήκους ~53 χλμ.) και στις μελέτες για τη 2η φάση του έργου, ώστε να μπορεί να εγκατασταθεί μελλοντικά το συστήμα ηλεκτροκίνησης σε ολόκληρη τη Σ.Γ. Θεσσαλονίκης – Προμαχώνα μήκους ~142,4 km, με μέγιστη ταχύτητα 120 km/h
@@ -3673,7 +3427,7 @@
 Η υπογραφή της σύμβασης εκτιμάται στα τέλη Μαΐου 2027.</t>
         </is>
       </c>
-      <c r="U24" s="44" t="inlineStr">
+      <c r="U24" s="37" t="inlineStr">
         <is>
           <t>1.Ένταξη στο ΑΠΔΕ 2026
 2. Υποβολή στο ΟΠΣ του Τεχνικού Δελτίου Πράξης και έγκριση από Δ.Α.             
@@ -3682,107 +3436,90 @@
 5. Δημοπράτηση έργου</t>
         </is>
       </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>144.000.000,00 €</t>
-        </is>
-      </c>
-      <c r="W24" s="8" t="n"/>
-      <c r="X24" s="8" t="n"/>
-      <c r="Y24" s="8" t="n"/>
-      <c r="Z24" s="8" t="inlineStr">
-        <is>
-          <t>31.05.2028</t>
-        </is>
-      </c>
-      <c r="AA24" s="41" t="inlineStr">
-        <is>
-          <t>85,0%</t>
-        </is>
-      </c>
-      <c r="AB24" s="8" t="inlineStr">
-        <is>
-          <t>CEF-T-2023-CORECOEN-RAIL-WORKS</t>
-        </is>
-      </c>
-      <c r="AC24" s="8" t="inlineStr">
-        <is>
-          <t>144.000.000,00 €</t>
-        </is>
-      </c>
-      <c r="AD24" s="41" t="n">
+      <c r="V24" s="7" t="n"/>
+      <c r="W24" s="34" t="n">
         <v>41.32619960867055</v>
       </c>
-      <c r="AE24" s="41" t="n">
+      <c r="X24" s="34" t="n">
         <v>23.35024303680261</v>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1" s="35">
-      <c r="A25" s="9" t="n">
+    <row r="25" ht="60" customHeight="1" s="62">
+      <c r="A25" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>CEF 21 27</t>
-        </is>
-      </c>
-      <c r="C25" s="42" t="inlineStr">
-        <is>
-          <t>ΣΚΑ-Κιάτο</t>
-        </is>
-      </c>
-      <c r="D25" s="46" t="inlineStr">
-        <is>
-          <t>Εγκατάσταση νέου συστήματος σηματοδότησης με τηλεδιοίκηση &amp; ETCS L1, ΣΚΑ-Κιάτο</t>
-        </is>
-      </c>
-      <c r="E25" s="43" t="inlineStr">
+      <c r="B25" s="54" t="inlineStr">
+        <is>
+          <t>CEF 2021-2027</t>
+        </is>
+      </c>
+      <c r="C25" s="35" t="inlineStr">
+        <is>
+          <t>ΣΚΑ - ΚΙΑΤΟ</t>
+        </is>
+      </c>
+      <c r="D25" s="39" t="inlineStr">
+        <is>
+          <t>ΕΓΚΑΤΑΣΤΑΣΗ ΝΕΟΥ ΣΥΣΤΗΜΑΤΟΣ ΣΗΜΑΤΟΔΟΤΗΣΗΣ ΜΕ ΤΗΛΕΔΙΟΙΚΗΣΗ, ETCS L1 ΓΙΑ ΤΗΝ ΔΙΠΛΗ ΣΙΔΗΡΟΔΡΟΜΙΚΗ ΓΡΑΜΜΗ ΣΚΑ-ΚΙΑΤΟ</t>
+        </is>
+      </c>
+      <c r="E25" s="36" t="inlineStr">
         <is>
           <t>Κεντρικό (Core)</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΑΣ Μ.Α.Ε.
-(ΟΣΕ ΑΕ)</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="F25" s="52" t="inlineStr">
+        <is>
+          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΑΣ Μ.Α.Ε.</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>CEF 2021-2027</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>27.979.200 € (Επιλέξιμη δημόσια δαπάνη)</t>
-        </is>
-      </c>
-      <c r="I25" s="10" t="inlineStr">
-        <is>
-          <t>27.979.200 €</t>
-        </is>
-      </c>
-      <c r="J25" s="10" t="n"/>
-      <c r="K25" s="10" t="n"/>
-      <c r="L25" s="10" t="inlineStr">
-        <is>
-          <t>30.04.2028</t>
-        </is>
-      </c>
-      <c r="M25" s="10" t="inlineStr">
-        <is>
-          <t>Ανάπτυξη ETCS L1 &amp; τηλεδιοίκησης σε 85,46χλμ (ΣΚΑ-Κιάτο) &amp; 6,7χλμ (Ισθμός-Λουτράκι)</t>
-        </is>
-      </c>
-      <c r="N25" s="46" t="inlineStr">
-        <is>
-          <t>Το έργο αφορά την εγκατάσταση ETCS L1 και συστήματος τηλεδιοίκησης στο άξονα ΣΚΑ–Κιάτο και στη διακλάδωση Ισθμός–Λουτράκι, με στόχο την αναβάθμιση της σηματοδότησης και τη διαλειτουργικότητα με υπάρχοντα και μελλοντικά συστήματα. Έχει εξασφαλισμένη χρηματοδότηση από το CEF και έχει ενταχθεί σε μηχανισμό ωρίμανσης μέσω της ΕΕΣΥΠ για την προετοιμασία των συμβάσεων. Βρίσκεται σε φάση διοικητικής προώθησης για ένταξη στο εθνικό πρόγραμμα χρηματοδότησης και υλοποίησης των απαραίτητων μελετών. Κρίσιμο ζητούμενο είναι η ολοκλήρωση της ωρίμανσης και η έναρξη των διαγωνιστικών διαδικασιών.</t>
-        </is>
-      </c>
-      <c r="O25" s="43" t="n"/>
-      <c r="P25" s="43" t="n"/>
-      <c r="Q25" s="43" t="n"/>
-      <c r="R25" s="10" t="inlineStr">
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27.979.200 € (Επιλέξιμη Δημόσια Δαπάνη)
+(Ημερ. Έναρξης GA: 01.05.2024
+Ημερ. Ολοκλ. GA: 30.04.2028)  </t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="n"/>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>Εκτίμηση: τέλη Μαΐου 2027</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M25" s="53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Η δράση αφορά στην ανάπτυξη ενός νέου συστήματος διασύνδεσης με γραμμή βάσης ETCS L1 baseline 4 v1.1 και τηλεδιοίκηση κατά μήκος:
+• της διπλής Σ.Γ. από Σιδηροδρομικό Κέντρο Αχαρνών [ΣΚΑ] (δεν περιλαμβάνεται) έως ΚΙΑΤΟ (εξαιρείται το τμήμα Ζευγολατιό – ΚΙΑΤΟ), συνολικού μήκους ~85,46 km 
+• της διακλάδωσης από τον σταθμό Ισθμού προς Λουτράκι (μονή Σ.Γ. συνολικού μήκους ~6,7 km)
+Η διαδρομή περιλαμβάνει  περιλαμβάνει 9 σιδηροδρομικούς σταθμούς.
+</t>
+        </is>
+      </c>
+      <c r="N25" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Το έργο εντάχθηκε στο Αναπτυξιακό Πρόγραμμα Συμβάσεων Στρατηγικής Σημασίας του Ν.4799/2021 και έχει περιέλθει στις αρμοδιότητες της Ελληνικής Εταιρείας Συμμετοχών και Περιουσίας (ΕΕΣΥΠ) ΑΕ , η οποία μέσω της Μονάδας Συμβάσεων Στρατηγικής Σημασίας, σύμφωνα με τον Κανονισμό Αναθέσεων ΤΑΙΠΕΔ θα προβεί σε όλες τις απαραίτητες ενέργειες για την ανάθεση των απαραίτητων συμβάσεων, μελετών και παροχής υπηρεσιών για την ωρίμανση του έργου. 
+</t>
+        </is>
+      </c>
+      <c r="O25" s="36" t="n"/>
+      <c r="P25" s="36" t="n"/>
+      <c r="Q25" s="36" t="n"/>
+      <c r="R25" s="9" t="inlineStr">
         <is>
           <t>Project ID 101175706
 23-EL-TC-
@@ -3790,12 +3527,12 @@
 (ΟΠΣ: 6053266)</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="S25" s="9" t="inlineStr">
         <is>
           <t>Σε ωρίμανση</t>
         </is>
       </c>
-      <c r="T25" s="46" t="inlineStr">
+      <c r="T25" s="39" t="inlineStr">
         <is>
           <t>Υπογραφή Grant Agreement : 8-10-2024. Επιλέξιμη Δημόσια Δαπάνη Πράξης: 27.979.200,00 €.         
  Το αντικείμενο του έργου αφορά την ανάπτυξη ενός νέου συστήματος διασύνδεσης με γραμμή βάσης ETCS L1 baseline 4 v1.1 και τηλεδιοίκηση κατά μήκος:
@@ -3808,7 +3545,7 @@
 Η υπογραφή της σύμβασης εκτιμάται στα τέλη Μαΐου 2027.</t>
         </is>
       </c>
-      <c r="U25" s="46" t="inlineStr">
+      <c r="U25" s="39" t="inlineStr">
         <is>
           <t>1.Σύναψη σύμβασης με την ΕΕΣΥΠ 
 2. Ένταξη στο ΑΠΔΕ 2026
@@ -3817,100 +3554,88 @@
 5. Δημοπράτηση έργου</t>
         </is>
       </c>
-      <c r="V25" s="10" t="n"/>
-      <c r="W25" s="10" t="n"/>
-      <c r="X25" s="10" t="n"/>
-      <c r="Y25" s="10" t="n"/>
-      <c r="Z25" s="10" t="inlineStr">
-        <is>
-          <t>30.04.2028</t>
-        </is>
-      </c>
-      <c r="AA25" s="43" t="inlineStr">
-        <is>
-          <t>unit contribution</t>
-        </is>
-      </c>
-      <c r="AB25" s="10" t="inlineStr">
-        <is>
-          <t>CEF-T-2023-SIMOBCOEN-ERTMS-UNITS</t>
-        </is>
-      </c>
-      <c r="AC25" s="10" t="n"/>
-      <c r="AD25" s="43" t="n">
+      <c r="V25" s="9" t="n"/>
+      <c r="W25" s="36" t="n">
         <v>38.08420445809669</v>
       </c>
-      <c r="AE25" s="43" t="n">
+      <c r="X25" s="36" t="n">
         <v>23.63799569120797</v>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1" s="35">
+    <row r="26" ht="60" customHeight="1" s="62">
       <c r="A26" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>CEF 21 27</t>
-        </is>
-      </c>
-      <c r="C26" s="40" t="inlineStr">
-        <is>
-          <t>Αναβάθμιση διπλής  ΣΓ Σκα-Οινόη &amp; ΣΣ Αλιαρτου</t>
-        </is>
-      </c>
-      <c r="D26" s="44" t="inlineStr">
+      <c r="B26" s="54" t="inlineStr">
+        <is>
+          <t>CEF 2021-2027</t>
+        </is>
+      </c>
+      <c r="C26" s="33" t="inlineStr">
+        <is>
+          <t>ΣΚΑ - ΟΙΝΟΗ</t>
+        </is>
+      </c>
+      <c r="D26" s="37" t="inlineStr">
         <is>
           <t>AΝΑΒΑΘΜΙΣΗ ΤΗΣ ΥΦΙΣΤΑΜΕΝΗΣ ΔΙΠΛΗΣ ΣΙΔΗΡΟΔΡΟΜΙΚΗΣ ΓΡΑΜΜΗΣ ΣΤΟ ΤΜΗΜΑ ΣΚΑ-ΟΙΝΟΗ ΚΑΙ ΣΙΔΗΡΟΔΡΟΜΙΚΟΥ ΣΤΑΘΜΟΥ ΑΛΙΑΡΤΟΥ</t>
         </is>
       </c>
-      <c r="E26" s="41" t="inlineStr">
+      <c r="E26" s="34" t="inlineStr">
         <is>
           <t>Κεντρικό (Core)</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΑΣ Μ.Α.Ε.
-(ΟΣΕ ΑΕ)</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="F26" s="52" t="inlineStr">
+        <is>
+          <t>ΣΙΔΗΡΟΔΡΟΜΟΙ ΕΛΛΑΔΑΣ Μ.Α.Ε.</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>CEF 2021-2027</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>Επιλέξιμη Δημόσια Δαπάνη Πράξης: 240.720.000,00€</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="n"/>
-      <c r="J26" s="8" t="n"/>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t>Ημερομηνία έναρξης Grant Agreement: 01.02.2024</t>
-        </is>
-      </c>
-      <c r="L26" s="8" t="inlineStr">
-        <is>
-          <t>Ημερομηνία λήξης Grant Agreement: 30.09.2028</t>
-        </is>
-      </c>
-      <c r="M26" s="8" t="inlineStr">
-        <is>
-          <t>Ανακαίνιση/Αναβάθμιση 52km γραμμής, σήραγγα Αγ. Στεφάνου, γέφυρες, αντιστηρίξεις, μετακίνηση Σ.Σ. Οινοφύτων, ανακαίνιση Σ.Σ. Οινόης &amp; Αλιάρτου. Το έργο εντάχθηκε στο Αναπτυξιακό Πρόγραμμα Συμβάσεων Στρατηγικής Σημασίας του Ν.4799/2021 και έχει περιέλθει στις αρμοδιότητες της Ελληνικής Εταιρείας Συμμετοχών και Περιουσίας (ΕΕΣΥΠ) ΑΕ</t>
-        </is>
-      </c>
-      <c r="N26" s="44" t="inlineStr">
-        <is>
-          <t>Το έργο αφορά την ανακαίνιση–αναβάθμιση υφιστάμενης διπλής σιδηροδρομικής γραμμής ~52 km με παρεμβάσεις σε σήραγγες, γέφυρες, επιχώματα, γραμμές και σταθμούς (μεταξύ αυτών Οινόφυτα, Αλίαρτος, Οινόη).
-Έχουν ολοκληρωθεί η Μελέτη Ανάλυσης Κινδύνου και η Έκθεση Εκτίμησης Ασφάλειας. Το έργο έχει ενταχθεί σε καθεστώς στρατηγικής σημασίας (Ν.4799/2021) και βρίσκεται σε φάση διοικητικής ωρίμανσης/ένταξης στη ΣΑΕ 079/7 με προϋπολογισμό 299.320.937 €.</t>
-        </is>
-      </c>
-      <c r="O26" s="41" t="n"/>
-      <c r="P26" s="41" t="n"/>
-      <c r="Q26" s="41" t="n"/>
-      <c r="R26" s="8" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 240.720.000,00€ 
+(Επιλέξιμη Δημόσια Δαπάνη)
+(Ημερ. Έναρξης GA: 01.02.2024
+Ημερ. Ολοκλ. GA: 30.09.2028)  </t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="n"/>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>Εκτίμηση: τέλη Μαΐου 2027</t>
+        </is>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Η δράση αφορά στην ανακαίνιση – αναβάθμιση υπό λειτουργία της υποδομής και επιδομής της υφιστάμενης  διπλής Σ.Γ μήκους ~52km και περιλαμβάνει ενισχύσεις/ανακατασκευές σηράγγων, γεφυρών, οδικών υπόγειων διαβάσεων, σιδηροδρομικών γραμμών, μετακίνηση του Σ.Σ. Οινοφύτων και ανακαίνιση του Σ.Σ. Οινόης και Σ. Στάσης Αλιάρτου
+ </t>
+        </is>
+      </c>
+      <c r="N26" s="37" t="inlineStr">
+        <is>
+          <t>Το έργο εντάχθηκε στο Αναπτυξιακό Πρόγραμμα Συμβάσεων Στρατηγικής Σημασίας του Ν.4799/2021 και έχει περιέλθει στις αρμοδιότητες της Ελληνικής Εταιρείας Συμμετοχών και Περιουσίας (ΕΕΣΥΠ) ΑΕ , η οποία μέσω της Μονάδας Συμβάσεων Στρατηγικής Σημασίας, σύμφωνα με τον Κανονισμό Αναθέσεων ΤΑΙΠΕΔ θα προβεί σε όλες τις απαραίτητες ενέργειες για την ανάθεση των απαραίτητων συμβάσεων, μελετών και παροχής υπηρεσιών για την ωρίμανση του έργου. 
+ Έχει υπογραφεί η σχετική  Σύμβαση μεταξύ του ΥΠΥΜΕ, της ΣΕΜΑΕ και της ΕΕΣΥΠ ΑΕ.</t>
+        </is>
+      </c>
+      <c r="O26" s="34" t="n"/>
+      <c r="P26" s="34" t="n"/>
+      <c r="Q26" s="34" t="n"/>
+      <c r="R26" s="7" t="inlineStr">
         <is>
           <t>Project ID 101175704
 23-EL-TC-
@@ -3918,12 +3643,12 @@
 (ΟΠΣ: 6029747)</t>
         </is>
       </c>
-      <c r="S26" s="8" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>Σε ωρίμανση</t>
         </is>
       </c>
-      <c r="T26" s="44" t="inlineStr">
+      <c r="T26" s="37" t="inlineStr">
         <is>
           <t>Υπογραφή Grant Agreement : 15-10-2024.  Επιλέξιμη Δημόσια Δαπάνη Πράξης: 240.720.000,00 €.                                                         
 ΑΝΤΙΚΕΙΜΕΝΟ ΤΟΥ ΕΡΓΟΥ: 
@@ -3942,7 +3667,7 @@
 Η υπογραφή της σύμβασης εκτιμάται στα τέλη Μαΐου 2027.</t>
         </is>
       </c>
-      <c r="U26" s="44" t="inlineStr">
+      <c r="U26" s="37" t="inlineStr">
         <is>
           <t>1. Ένταξη στο ΑΠΔΕ 2026
 2. Υποβολή στο ΟΠΣ του Τεχνικού Δελτίου Πράξης και έγκριση από Δ.Α.              
@@ -3951,38 +3676,11 @@
 5. Δημοπράτηση έργου</t>
         </is>
       </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>240.720.000,00 €</t>
-        </is>
-      </c>
-      <c r="W26" s="8" t="n"/>
-      <c r="X26" s="8" t="n"/>
-      <c r="Y26" s="8" t="n"/>
-      <c r="Z26" s="8" t="inlineStr">
-        <is>
-          <t>30.09.2028</t>
-        </is>
-      </c>
-      <c r="AA26" s="41" t="inlineStr">
-        <is>
-          <t>85,0%</t>
-        </is>
-      </c>
-      <c r="AB26" s="8" t="inlineStr">
-        <is>
-          <t>CEF-T-2023-CORECOEN-RAIL-WORKS</t>
-        </is>
-      </c>
-      <c r="AC26" s="8" t="inlineStr">
-        <is>
-          <t>240.720.000,00 €</t>
-        </is>
-      </c>
-      <c r="AD26" s="41" t="n">
+      <c r="V26" s="7" t="n"/>
+      <c r="W26" s="34" t="n">
         <v>38.3153533311327</v>
       </c>
-      <c r="AE26" s="41" t="n">
+      <c r="X26" s="34" t="n">
         <v>23.62183292980047</v>
       </c>
     </row>
@@ -3990,9 +3688,9 @@
   <autoFilter ref="A3:AE26"/>
   <mergeCells count="4">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="R2:AC2"/>
+    <mergeCell ref="R2:V2"/>
     <mergeCell ref="G2:Q2"/>
-    <mergeCell ref="AD2:AE2"/>
+    <mergeCell ref="W2:X2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
@@ -4006,195 +3704,195 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="22" customWidth="1" style="35" min="1" max="1"/>
-    <col width="80" customWidth="1" style="35" min="2" max="2"/>
+    <col width="22" customWidth="1" style="62" min="1" max="1"/>
+    <col width="80" customWidth="1" style="62" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="35">
-      <c r="A1" s="14" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="62">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>ΕΝΟΠΟΙΗΜΕΝΗ ΒΑΣΗ ΕΡΓΩΝ – ΟΔΗΓΙΕΣ ΧΡΗΣΗΣ</t>
         </is>
       </c>
-      <c r="B1" s="14" t="n"/>
-    </row>
-    <row r="2" ht="8.1" customHeight="1" s="35">
-      <c r="A2" s="15" t="n"/>
-      <c r="B2" s="15" t="n"/>
-    </row>
-    <row r="3" ht="15.95" customHeight="1" s="35">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="B1" s="12" t="n"/>
+    </row>
+    <row r="2" ht="8.1" customHeight="1" s="62">
+      <c r="A2" s="13" t="n"/>
+      <c r="B2" s="13" t="n"/>
+    </row>
+    <row r="3" ht="15.9" customHeight="1" s="62">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>ΔΟΜΗ ΑΡΧΕΙΟΥ</t>
         </is>
       </c>
-      <c r="B3" s="14" t="n"/>
-    </row>
-    <row r="4" ht="14.1" customHeight="1" s="35">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="B3" s="12" t="n"/>
+    </row>
+    <row r="4" ht="14.1" customHeight="1" s="62">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Sheet «ΒΑΣΗ ΕΡΓΩΝ»</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Ενοποιεί τα δεδομένα και των δύο JS αρχείων σε ένα μέρος.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" s="35">
-      <c r="A5" s="15" t="n"/>
-      <c r="B5" s="15" t="n"/>
-    </row>
-    <row r="6" ht="15.95" customHeight="1" s="35">
-      <c r="A6" s="16" t="inlineStr">
+    <row r="5" ht="6" customHeight="1" s="62">
+      <c r="A5" s="13" t="n"/>
+      <c r="B5" s="13" t="n"/>
+    </row>
+    <row r="6" ht="15.9" customHeight="1" s="62">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>ΧΡΩΜΑΤΙΣΜΟΣ ΣΤΗΛΩΝ</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n"/>
-    </row>
-    <row r="7" ht="14.1" customHeight="1" s="35">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="B6" s="14" t="n"/>
+    </row>
+    <row r="7" ht="14.1" customHeight="1" s="62">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>🟫 Καφέ (ΚΟΙΝΕΣ)</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Στήλες που χρησιμοποιούνται και στα δύο αρχεία εξόδου (ID, Τίτλος, ΔΕΔ-Μ, Δικαιούχος)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="14.1" customHeight="1" s="35">
-      <c r="A8" s="18" t="inlineStr">
+    <row r="8" ht="14.1" customHeight="1" s="62">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>🔵 Μπλε (ERGA_2)</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Στήλες που παράγουν το ERGA_2.js – σύντομα κείμενα για τον χάρτη</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="14.1" customHeight="1" s="35">
-      <c r="A9" s="19" t="inlineStr">
+    <row r="9" ht="14.1" customHeight="1" s="62">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>🟢 Πράσινο (DETAIL)</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Στήλες που παράγουν το detail_data.js – αναλυτικές πληροφορίες popup</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="14.1" customHeight="1" s="35">
-      <c r="A10" s="20" t="inlineStr">
+    <row r="10" ht="14.1" customHeight="1" s="62">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>🟣 Μοβ (ΓΕΩ)</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>Γεωγραφικές συντεταγμένες – ΜΗΝ αλλάζετε!</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" s="35">
-      <c r="A11" s="15" t="n"/>
-      <c r="B11" s="15" t="n"/>
-    </row>
-    <row r="12" ht="15.95" customHeight="1" s="35">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="11" ht="6" customHeight="1" s="62">
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="13" t="n"/>
+    </row>
+    <row r="12" ht="15.9" customHeight="1" s="62">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>ΠΩΣ ΝΑ ΕΝΗΜΕΡΩΣΕΤΕ ΔΕΔΟΜΕΝΑ</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
-    </row>
-    <row r="13" ht="14.1" customHeight="1" s="35">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="B12" s="14" t="n"/>
+    </row>
+    <row r="13" ht="14.1" customHeight="1" s="62">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Βήμα 1</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Ανοίξτε το sheet «ΒΑΣΗ ΕΡΓΩΝ' και επεξεργαστείτε τα πεδία που θέλετε</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="14.1" customHeight="1" s="35">
-      <c r="A14" s="15" t="inlineStr">
+    <row r="14" ht="14.1" customHeight="1" s="62">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Βήμα 2</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>Αποθηκεύστε το αρχείο</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="14.1" customHeight="1" s="35">
-      <c r="A15" s="15" t="inlineStr">
+    <row r="15" ht="14.1" customHeight="1" s="62">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Βήμα 3</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Ανοίξτε τον converter (HTML) – φορτώστε αυτό το αρχείο – κατεβάστε τα JS</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="6" customHeight="1" s="35">
-      <c r="A16" s="15" t="n"/>
-      <c r="B16" s="15" t="n"/>
-    </row>
-    <row r="17" ht="15.95" customHeight="1" s="35">
-      <c r="A17" s="21" t="inlineStr">
+    <row r="16" ht="6" customHeight="1" s="62">
+      <c r="A16" s="13" t="n"/>
+      <c r="B16" s="13" t="n"/>
+    </row>
+    <row r="17" ht="15.9" customHeight="1" s="62">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>ΣΗΜΑΝΤΙΚΟ</t>
         </is>
       </c>
-      <c r="B17" s="21" t="n"/>
-    </row>
-    <row r="18" ht="14.1" customHeight="1" s="35">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="B17" s="19" t="n"/>
+    </row>
+    <row r="18" ht="14.1" customHeight="1" s="62">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Στήλη «Κατάσταση / Ποσοστά %»</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>ΣΥΝΤΟΜΟ κείμενο για τον χάρτη (popup σύνοψη + ποσοστά). Το αναλυτικό κείμενο πηγαίνει στο «Αντικείμενο / Σχόλια».</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="14.1" customHeight="1" s="35">
-      <c r="A19" s="17" t="inlineStr">
+    <row r="19" ht="14.1" customHeight="1" s="62">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Γεωγρ. Πλάτος / Μήκος</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>ΜΗΝ ΑΛΛΑΖΕΤΕ τιμές – καθορίζουν θέση στον χάρτη!</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="14.1" customHeight="1" s="35">
-      <c r="A20" s="17" t="inlineStr">
+    <row r="20" ht="14.1" customHeight="1" s="62">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>ΜΗΝ ΑΛΛΑΖΕΤΕ – ο μοναδικός σύνδεσμος μεταξύ ERGA_2 και detail_data</t>
         </is>
@@ -4212,110 +3910,110 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="20" customWidth="1" style="35" min="1" max="1"/>
-    <col width="12" customWidth="1" style="35" min="2" max="2"/>
-    <col width="50" customWidth="1" style="35" min="3" max="3"/>
+    <col width="20" customWidth="1" style="62" min="1" max="1"/>
+    <col width="12" customWidth="1" style="62" min="2" max="2"/>
+    <col width="50" customWidth="1" style="62" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>Πρόγραμμα</t>
         </is>
       </c>
-      <c r="B1" s="22" t="inlineStr">
+      <c r="B1" s="20" t="inlineStr">
         <is>
           <t>Χρώμα</t>
         </is>
       </c>
-      <c r="C1" s="22" t="inlineStr">
+      <c r="C1" s="20" t="inlineStr">
         <is>
           <t>Sheets detail_data</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>ΕΠ ΥΜΕΠΕΡΑΑ</t>
         </is>
       </c>
-      <c r="B2" s="24" t="inlineStr">
+      <c r="B2" s="22" t="inlineStr">
         <is>
           <t>██</t>
         </is>
       </c>
-      <c r="C2" s="25" t="inlineStr">
+      <c r="C2" s="23" t="inlineStr">
         <is>
           <t>ΕΠ ΥΜΕΠΕΡΑΑ</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>ΜΕΤΑΦΟΡΕΣ</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>██</t>
         </is>
       </c>
-      <c r="C3" s="25" t="inlineStr">
+      <c r="C3" s="23" t="inlineStr">
         <is>
           <t>ΜΕΤΑΦΟΡΕΣ</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>CEF 14 20</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="27" t="inlineStr">
         <is>
           <t>██</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>CEF 14 20</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>CEF 21 27</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>██</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>CEF 21 27</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>ΠεΠ 2021-2027</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>██</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>ΠεΠ 2021-2027</t>
         </is>
